--- a/vspfiles/imports/steve-silver-volusion/steve_silver_game_dining_server_import.xlsx
+++ b/vspfiles/imports/steve-silver-volusion/steve_silver_game_dining_server_import.xlsx
@@ -7,10 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="all_products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="game_sets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="dining_and_servers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="servers_site_notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Volusion Import" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Game Table Sets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dining and Servers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +51,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,75 +422,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>productcode</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>productname</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>productprice</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>productweight</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>freeshipping</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>productdescription</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>techspecs</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>vendor_sku</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>volusion_images</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SS-VCM420WTN-C5PC-1</t>
+          <t>SS-VCM420WTN-C5PC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,13 +500,8 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-16" data-testid="conversation-turn-34" data-scroll-anchor="true" data-turn="assistant"&gt;
- Meet the Artemis 54-inch square marble counter set—where modern design feels easy and inviting. The double pedestal base brings bold architectural style, while the casual sand finish keeps the look relaxed and livable. A sleek white marble top adds just the right touch of elegance. Paired with plush brown velvet counter chairs, each designed with a perfect pitch for a comfortable seat, it’s made for gathering. At a comfortable 36″ height, it offers easy entry, lasting durability, and effortless everyday style.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 54″ White Marble Dining Table, Sand Finish and 4 Artemis Brown Velvet Side Chairs. Each item also sold separately.
@@ -529,26 +520,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>VCM420WTN-C5PC-1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-sand-finish-w-4-brown-velvet-counter-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SS-VCM420WTN-C5PC-1-1.jpg;SS-VCM420WTN-C5PC-1-altview1.jpg;SS-VCM420WTN-C5PC-1-altview2.jpg;SS-VCM420WTN-C5PC-1-altview3.jpg;SS-VCM420WTN-C5PC-1-altview4.jpg;SS-VCM420WTN-C5PC-1-altview5.jpg;SS-VCM420WTN-C5PC-1-altview6.jpg;SS-VCM420WTN-C5PC-1-altview7.jpg;SS-VCM420WTN-C5PC-1-altview8.jpg;SS-VCM420WTN-C5PC-1-altview9.jpg;SS-VCM420WTN-C5PC-1-altview10.jpg;SS-VCM420WTN-C5PC-1-altview11.jpg;SS-VCM420WTN-C5PC-1-altview12.jpg;SS-VCM420WTN-C5PC-1-altview13.jpg;SS-VCM420WTN-C5PC-1-altview14.jpg;SS-VCM420WTN-C5PC-1-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -573,13 +544,8 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-16" data-testid="conversation-turn-34" data-scroll-anchor="true" data-turn="assistant"&gt;
- Meet the Artemis 54-inch square marble counter set—where modern design feels easy and inviting. The double pedestal base brings bold architectural style, while the casual sand finish keeps the look relaxed and livable. A sleek white marble top adds just the right touch of elegance. Paired with plush green velvet counter chairs, each designed with a perfect pitch for a comfortable seat, it’s made for gathering. At a comfortable 36″ height, it offers easy entry, lasting durability, and effortless everyday style.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 54″ White Marble Counter Table, Sand Finish and 4 Artemis Green Velvet Counter Chairs. Each item also sold separately.
@@ -598,26 +564,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>VCM420WTE-C5PC</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-sand-finish-w-4-green-velvet-counter-chairs/</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SS-VCM420WTE-C5PC-1.jpg;SS-VCM420WTE-C5PC-altview1.jpg;SS-VCM420WTE-C5PC-altview2.jpg;SS-VCM420WTE-C5PC-altview3.jpg;SS-VCM420WTE-C5PC-altview4.jpg;SS-VCM420WTE-C5PC-altview5.jpg;SS-VCM420WTE-C5PC-altview6.jpg;SS-VCM420WTE-C5PC-altview7.jpg;SS-VCM420WTE-C5PC-altview8.jpg;SS-VCM420WTE-C5PC-altview9.jpg;SS-VCM420WTE-C5PC-altview10.jpg;SS-VCM420WTE-C5PC-altview11.jpg;SS-VCM420WTE-C5PC-altview12.jpg;SS-VCM420WTE-C5PC-altview13.jpg;SS-VCM420WTE-C5PC-altview14.jpg;SS-VCM420WTE-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -642,13 +588,8 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-15" data-testid="conversation-turn-32" data-scroll-anchor="true" data-turn="assistant"&gt;
- Sleek, sophisticated, and modern, the Artemis 54″ white marble 5-piece counter set delivers standout style with everyday versatility. The 54-inch square table seats up to eight while keeping conversation close and inviting. A substantial white marble top is beautifully softened by a sand finish double pedestal base for a relaxed yet elegant presentation. At a comfortable 36″ height, it’s perfect for dining, working, or gathering with easy entry and exit. Four beige chenille counter chairs add plush comfort, making it ideal for both daily living and entertaining.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 54″ White Marble Counter Table, Sand Finish and 4 Artemis Beige Chenille Counter Chairs. Each item also sold separately.
@@ -667,26 +608,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>VCM540WTT-C5PC</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-tan-finish-w-4-beige-chenille-counter-chairs/</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>SS-VCM540WTT-C5PC-1.jpg;SS-VCM540WTT-C5PC-altview1.jpg;SS-VCM540WTT-C5PC-altview2.jpg;SS-VCM540WTT-C5PC-altview3.jpg;SS-VCM540WTT-C5PC-altview4.jpg;SS-VCM540WTT-C5PC-altview5.jpg;SS-VCM540WTT-C5PC-altview6.jpg;SS-VCM540WTT-C5PC-altview7.jpg;SS-VCM540WTT-C5PC-altview8.jpg;SS-VCM540WTT-C5PC-altview9.jpg;SS-VCM540WTT-C5PC-altview10.jpg;SS-VCM540WTT-C5PC-altview11.jpg;SS-VCM540WTT-C5PC-altview12.jpg;SS-VCM540WTT-C5PC-altview13.jpg;SS-VCM540WTT-C5PC-altview14.jpg;SS-VCM540WTT-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -711,13 +632,8 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-12" data-testid="conversation-turn-26" data-scroll-anchor="true" data-turn="assistant"&gt;
- Sleek, sophisticated, and modern, the Artemis 54″ white marble 5-piece counter set delivers standout style and everyday function. The 54-inch square white marble table seats up to eight while keeping conversation close and inviting. A substantial 3″ marble-look top and bold black base create a high-end presence. Four black vegan leather counter chairs, accented with silver nailhead trim, add crisp contrast and tailored appeal, while supportive seating and sturdy construction ensure lasting comfort, durability, and performance for dining and entertaining alike.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>• Crafted with 8mm white marble veneered top, Birch veneers, Asian hardwood solids, engineered woods, 100% polyester cover and foam.
 • 5-piece set includes the Artemis 54″ Square White Marble Counter Table and 4 Artemis Black Vegan Leather Counter Chairs. Each item also sold separately.
@@ -736,26 +652,6 @@
 • The wood is hand-stained in a natural multi-step black finish</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>VCM540WKK-C5PC</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-with-4-artemis-black-vegan-leather-counter-chairs/</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>SS-VCM540WKK-C5PC-1.jpg;SS-VCM540WKK-C5PC-altview1.jpg;SS-VCM540WKK-C5PC-altview2.jpg;SS-VCM540WKK-C5PC-altview3.jpg;SS-VCM540WKK-C5PC-altview4.jpg;SS-VCM540WKK-C5PC-altview5.jpg;SS-VCM540WKK-C5PC-altview6.jpg;SS-VCM540WKK-C5PC-altview7.jpg;SS-VCM540WKK-C5PC-altview8.jpg;SS-VCM540WKK-C5PC-altview9.jpg;SS-VCM540WKK-C5PC-altview10.jpg;SS-VCM540WKK-C5PC-altview11.jpg;SS-VCM540WKK-C5PC-altview12.jpg;SS-VCM540WKK-C5PC-altview13.jpg;SS-VCM540WKK-C5PC-altview14.jpg;SS-VCM540WKK-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -780,13 +676,8 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-12" data-testid="conversation-turn-26" data-scroll-anchor="true" data-turn="assistant"&gt;
- Sleek, sophisticated, and modern, the Artemis 54″ White Marble 5-piece counter set delivers standout style and everyday function. The 54-inch square white marble table comfortably seats up to eight while keeping conversation close and inviting. A substantial 3″ marble-look top and bold black base create a high-end presence. Four white vegan leather counter chairs, accented with silver nailhead trim, add crisp contrast and tailored appeal, while supportive seating and sturdy construction ensure lasting comfort, durability, and performance for dining and entertaining alike.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>• Crafted with 8mm white marble veneered top, Birch veneers, Asian hardwood solids, engineered woods, 100% polyester cover and foam.
 • 5-piece set includes the Artemis 54″ Square White Marble Counter Table and 4 Artemis White Vegan Leather Counter Chairs. Each item also sold separately.
@@ -805,26 +696,6 @@
 • The wood is hand-stained in a natural multi-step black finish</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>VCM540WKW-C5PC</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-with-4-artemis-white-vegan-leather-counter-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SS-VCM540WKW-C5PC-1.jpg;SS-VCM540WKW-C5PC-altview1.jpg;SS-VCM540WKW-C5PC-altview2.jpg;SS-VCM540WKW-C5PC-altview3.jpg;SS-VCM540WKW-C5PC-altview4.jpg;SS-VCM540WKW-C5PC-altview5.jpg;SS-VCM540WKW-C5PC-altview6.jpg;SS-VCM540WKW-C5PC-altview7.jpg;SS-VCM540WKW-C5PC-altview8.jpg;SS-VCM540WKW-C5PC-altview9.jpg;SS-VCM540WKW-C5PC-altview10.jpg;SS-VCM540WKW-C5PC-altview11.jpg;SS-VCM540WKW-C5PC-altview12.jpg;SS-VCM540WKW-C5PC-altview13.jpg;SS-VCM540WKW-C5PC-altview14.jpg;SS-VCM540WKW-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -849,13 +720,8 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-12" data-testid="conversation-turn-26" data-scroll-anchor="true" data-turn="assistant"&gt;
- Sleek, sophisticated, and modern, the Artemis 54″ White Marble 5-piece counter set makes a striking statement. The 54-inch square white marble table seats up to eight comfortably while maintaining an intimate, conversation-friendly feel. A substantial 3″ marble-look top pairs seamlessly with a deep black wood base for bold appeal. Gray chenille counter chairs offer plush, supportive comfort with a perfectly pitched seat, while front and side stretchers add stability and a built-in footrest invites you to relax and stay awhile.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>• Crafted with 8mm white marble veneered top, Birch veneers, Asian hardwood solids, engineered woods, 100% polyester cover and foam.
 • 5-piece set includes the Artemis 54″ Square White Marble Counter Table and 4 Artemis Gray Counter Chairs. Each item also sold separately.
@@ -875,26 +741,6 @@
 • The wood is hand-stained in a natural multi-step black finish</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>VCM540WKG-C5PC</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-with-4-gray-chenille-counter-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SS-VCM540WKG-C5PC-1.jpg;SS-VCM540WKG-C5PC-altview1.jpg;SS-VCM540WKG-C5PC-altview2.jpg;SS-VCM540WKG-C5PC-altview3.jpg;SS-VCM540WKG-C5PC-altview4.jpg;SS-VCM540WKG-C5PC-altview5.jpg;SS-VCM540WKG-C5PC-altview6.jpg;SS-VCM540WKG-C5PC-altview7.jpg;SS-VCM540WKG-C5PC-altview8.jpg;SS-VCM540WKG-C5PC-altview9.jpg;SS-VCM540WKG-C5PC-altview10.jpg;SS-VCM540WKG-C5PC-altview11.jpg;SS-VCM540WKG-C5PC-altview12.jpg;SS-VCM540WKG-C5PC-altview13.jpg;SS-VCM540WKG-C5PC-altview14.jpg;SS-VCM540WKG-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -919,12 +765,12 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek gray marble top adds a refined touch. Paired with soft black vegan leather chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of gray marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 70″ Gray Marble Dining Table, Black Finish and 4 Artemis Black Vegan Leather Side Chairs. Each item also sold separately.
@@ -940,26 +786,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>VCM420GKK-D5PC</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-gray-marble-table-black-finish-w-4-black-vegan-leather-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>SS-VCM420GKK-D5PC-1.jpg;SS-VCM420GKK-D5PC-altview1.jpg;SS-VCM420GKK-D5PC-altview2.jpg;SS-VCM420GKK-D5PC-altview3.jpg;SS-VCM420GKK-D5PC-altview4.jpg;SS-VCM420GKK-D5PC-altview5.jpg;SS-VCM420GKK-D5PC-altview6.jpg;SS-VCM420GKK-D5PC-altview7.jpg;SS-VCM420GKK-D5PC-altview8.jpg;SS-VCM420GKK-D5PC-altview9.jpg;SS-VCM420GKK-D5PC-altview10.jpg;SS-VCM420GKK-D5PC-altview11.jpg;SS-VCM420GKK-D5PC-altview12.jpg;SS-VCM420GKK-D5PC-altview13.jpg;SS-VCM420GKK-D5PC-altview14.jpg;SS-VCM420GKK-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -984,12 +810,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek gray marble top adds a refined touch. Paired with soft gray chenille chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of gray marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 70″ Gray Marble Dining Table, Black Finish and 4 Artemis Gray Chenille Side Chairs. Each item also sold separately.
@@ -1005,26 +831,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>VCM420GKG-D5PC</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-gray-marble-table-black-finish-w-4-gray-chenille-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>SS-VCM420GKG-D5PC-1.jpg;SS-VCM420GKG-D5PC-altview1.jpg;SS-VCM420GKG-D5PC-altview2.jpg;SS-VCM420GKG-D5PC-altview3.jpg;SS-VCM420GKG-D5PC-altview4.jpg;SS-VCM420GKG-D5PC-altview5.jpg;SS-VCM420GKG-D5PC-altview6.jpg;SS-VCM420GKG-D5PC-altview7.jpg;SS-VCM420GKG-D5PC-altview8.jpg;SS-VCM420GKG-D5PC-altview9.jpg;SS-VCM420GKG-D5PC-altview10.jpg;SS-VCM420GKG-D5PC-altview11.jpg;SS-VCM420GKG-D5PC-altview12.jpg;SS-VCM420GKG-D5PC-altview13.jpg;SS-VCM420GKG-D5PC-altview14.jpg;SS-VCM420GKG-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1049,12 +855,12 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek gray marble top adds a refined touch. Paired with soft white vegan leather chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of gray marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 70″ Gray Marble Dining Table, Black Finish and 4 Artemis White Vegan Leather Side Chairs. Each item also sold separately.
@@ -1070,26 +876,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>VCM420GKW-D5PC</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-gray-marble-table-black-finish-w-4-white-vegan-leather-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>SS-VCM420GKW-D5PC-1.jpg;SS-VCM420GKW-D5PC-altview1.jpg;SS-VCM420GKW-D5PC-altview2.jpg;SS-VCM420GKW-D5PC-altview3.jpg;SS-VCM420GKW-D5PC-altview4.jpg;SS-VCM420GKW-D5PC-altview5.jpg;SS-VCM420GKW-D5PC-altview6.jpg;SS-VCM420GKW-D5PC-altview7.jpg;SS-VCM420GKW-D5PC-altview8.jpg;SS-VCM420GKW-D5PC-altview9.jpg;SS-VCM420GKW-D5PC-altview10.jpg;SS-VCM420GKW-D5PC-altview11.jpg;SS-VCM420GKW-D5PC-altview12.jpg;SS-VCM420GKW-D5PC-altview13.jpg;SS-VCM420GKW-D5PC-altview14.jpg;SS-VCM420GKW-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1114,12 +900,12 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek white marble top adds a refined touch. Paired with soft black vegan leather chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 70″ White Marble Dining Table, Black Finish and 4 Artemis Black Vegan Leather Side Chairs. Each item also sold separately.
@@ -1135,26 +921,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>VCM420KK-D5PC</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-black-finish-w-4-black-vegan-leather-chairs/</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>SS-VCM420KK-D5PC-1.jpg;SS-VCM420KK-D5PC-altview1.jpg;SS-VCM420KK-D5PC-altview2.jpg;SS-VCM420KK-D5PC-altview3.jpg;SS-VCM420KK-D5PC-altview4.jpg;SS-VCM420KK-D5PC-altview5.jpg;SS-VCM420KK-D5PC-altview6.jpg;SS-VCM420KK-D5PC-altview7.jpg;SS-VCM420KK-D5PC-altview8.jpg;SS-VCM420KK-D5PC-altview9.jpg;SS-VCM420KK-D5PC-altview10.jpg;SS-VCM420KK-D5PC-altview11.jpg;SS-VCM420KK-D5PC-altview12.jpg;SS-VCM420KK-D5PC-altview13.jpg;SS-VCM420KK-D5PC-altview14.jpg;SS-VCM420KK-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1179,12 +945,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek white marble top adds a refined touch. Paired with soft gray chenille chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 70″ White Marble Dining Table, Black Finish and 4 Artemis Gray Chenille Side Chairs. Each item also sold separately.
@@ -1200,26 +966,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>VCM420KG-D5PC</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-black-finish-w-4-gray-chenille-chairs/</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>SS-VCM420KG-D5PC-1.jpg;SS-VCM420KG-D5PC-altview1.jpg;SS-VCM420KG-D5PC-altview2.jpg;SS-VCM420KG-D5PC-altview3.jpg;SS-VCM420KG-D5PC-altview4.jpg;SS-VCM420KG-D5PC-altview5.jpg;SS-VCM420KG-D5PC-altview6.jpg;SS-VCM420KG-D5PC-altview7.jpg;SS-VCM420KG-D5PC-altview8.jpg;SS-VCM420KG-D5PC-altview9.jpg;SS-VCM420KG-D5PC-altview10.jpg;SS-VCM420KG-D5PC-altview11.jpg;SS-VCM420KG-D5PC-altview12.jpg;SS-VCM420KG-D5PC-altview13.jpg;SS-VCM420KG-D5PC-altview14.jpg;SS-VCM420KG-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1244,12 +990,12 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek white marble top adds a refined touch. Paired with soft white vegan leather chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 70″ White Marble Dining Table, Black Finish and 4 Artemis White Vegan LeatherSide Chairs. Each item also sold separately.
@@ -1265,26 +1011,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>VCM420KW-D5PC</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-black-finish-w-4-white-vegan-leather-chairs/</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>SS-VCM420KW-D5PC-1.jpg;SS-VCM420KW-D5PC-altview1.jpg;SS-VCM420KW-D5PC-altview2.jpg;SS-VCM420KW-D5PC-altview3.jpg;SS-VCM420KW-D5PC-altview4.jpg;SS-VCM420KW-D5PC-altview5.jpg;SS-VCM420KW-D5PC-altview6.jpg;SS-VCM420KW-D5PC-altview7.jpg;SS-VCM420KW-D5PC-altview8.jpg;SS-VCM420KW-D5PC-altview9.jpg;SS-VCM420KW-D5PC-altview10.jpg;SS-VCM420KW-D5PC-altview11.jpg;SS-VCM420KW-D5PC-altview12.jpg;SS-VCM420KW-D5PC-altview13.jpg;SS-VCM420KW-D5PC-altview14.jpg;SS-VCM420KW-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1309,12 +1035,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Meet the Artemis 70-inch marble top table—where modern design feels easy and inviting. The architectural base brings bold style, while the casual sand finish keeps the look relaxed and livable. A sleek white marble top adds just the right touch of elegance. Paired with soft beige chenille chairs, each designed with a perfect pitch for a comfortable seat, it’s made for gathering. With solid wood legs and screwed corner joints, this set delivers the durability you need with the style you want.</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 70″ White Marble Dining Table, Sand Finish and 4 Artemis Beige Chenille Side Chairs. Each item also sold separately.
@@ -1330,26 +1056,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>VCM420TT-D5PC</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-tan-finish-w-4-beige-chenille-chairs/</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>SS-VCM420TT-D5PC-1.jpg;SS-VCM420TT-D5PC-altview1.jpg;SS-VCM420TT-D5PC-altview2.jpg;SS-VCM420TT-D5PC-altview3.jpg;SS-VCM420TT-D5PC-altview4.jpg;SS-VCM420TT-D5PC-altview5.jpg;SS-VCM420TT-D5PC-altview6.jpg;SS-VCM420TT-D5PC-altview7.jpg;SS-VCM420TT-D5PC-altview8.jpg;SS-VCM420TT-D5PC-altview9.jpg;SS-VCM420TT-D5PC-altview10.jpg;SS-VCM420TT-D5PC-altview11.jpg;SS-VCM420TT-D5PC-altview12.jpg;SS-VCM420TT-D5PC-altview13.jpg;SS-VCM420TT-D5PC-altview14.jpg;SS-VCM420TT-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1374,13 +1080,8 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-16" data-testid="conversation-turn-34" data-scroll-anchor="true" data-turn="assistant"&gt;
- Meet the Artemis 54-inch square marble counter set—where modern design feels easy and inviting. The double pedestal base brings bold architectural style, while the casual sand finish keeps the look relaxed and livable. A sleek white marble top adds just the right touch of elegance. Paired with plush brown velvet counter chairs, each designed with a perfect pitch for a comfortable seat, it’s made for gathering. At a comfortable 36″ height, it offers easy entry, lasting durability, and effortless everyday style.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
 • 5-piece set includes the Artemis 54″ White Marble Dining Table, Sand Finish and 4 Artemis Brown Velvet Side Chairs. Each item also sold separately.
@@ -1399,26 +1100,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>VCM420WTN-C5PC</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-tan-finish-w-4-brown-velvet-chairs/</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SS-VCM420WTN-C5PC-1.jpg;SS-VCM420WTN-C5PC-altview1.jpg;SS-VCM420WTN-C5PC-altview2.jpg;SS-VCM420WTN-C5PC-altview3.jpg;SS-VCM420WTN-C5PC-altview4.jpg;SS-VCM420WTN-C5PC-altview5.jpg;SS-VCM420WTN-C5PC-altview6.jpg;SS-VCM420WTN-C5PC-altview7.jpg;SS-VCM420WTN-C5PC-altview8.jpg;SS-VCM420WTN-C5PC-altview9.jpg;SS-VCM420WTN-C5PC-altview10.jpg;SS-VCM420WTN-C5PC-altview11.jpg;SS-VCM420WTN-C5PC-altview12.jpg;SS-VCM420WTN-C5PC-altview13.jpg;SS-VCM420WTN-C5PC-altview14.jpg;SS-VCM420WTN-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1443,14 +1124,14 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Immerse yourself in the perfect blend of rustic charm and casual elegance with the 5-Piece Aubrey Dining Set. Crafted to perfection, this set seamlessly marries the rustic elements of Craftsman styling with the comfortable charm of cushioned sling side chairs, creating an inviting ambiance for memorable dining experiences.
  The 54-inch round Aubrey Black Dining Table exudes timeless appeal with its contrasting stretchers that offer a pop of color and coordinate effortlessly with the rest of the Aubrey collection. Supported by substantial canted 3-inch squared posts, the table hints at primitive styling while providing a sturdy foundation for your gatherings.
  Accompanied by four cushioned Black Side Chairs, this set offers both comfort and style.</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>• Set includes the Aubrey 54-inch Black Dining Table with Driftwood Stretchers and 4 Aubrey Gray Vegan Leather Side Chairs. Each item also sold separately.
 • Styling details include the dining table with substantial canted 3″ squared posts with contrasting stretchers and exposed tenons that match all the other pieces in the Aubrey collection. Mix and match finishes and pieces within the collection for a custom look.
@@ -1469,26 +1150,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ABR5454K-D5PC</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-5-piece-54-round-dining-table-set-copy/</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>SS-ABR5454K-D5PC-1.jpg;SS-ABR5454K-D5PC-altview1.jpg;SS-ABR5454K-D5PC-altview2.jpg;SS-ABR5454K-D5PC-altview3.jpg;SS-ABR5454K-D5PC-altview4.jpg;SS-ABR5454K-D5PC-altview5.jpg;SS-ABR5454K-D5PC-altview6.jpg;SS-ABR5454K-D5PC-altview7.jpg;SS-ABR5454K-D5PC-altview8.jpg;SS-ABR5454K-D5PC-altview9.jpg;SS-ABR5454K-D5PC-altview10.jpg;SS-ABR5454K-D5PC-altview11.jpg;SS-ABR5454K-D5PC-altview12.jpg;SS-ABR5454K-D5PC-altview13.jpg;SS-ABR5454K-D5PC-altview14.jpg;SS-ABR5454K-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1513,14 +1174,14 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Immerse yourself in the perfect blend of rustic charm and casual elegance with the 5-Piece Aubrey 54″ Round Driftwood Dining Set. Crafted to perfection, this set seamlessly marries the rustic elements of Craftsman styling with the sophistication of upholstered Parsons chairs, creating an inviting ambiance for memorable dining experiences.
  The centerpiece of this set is the 54-inch round Aubrey Driftwood Dining Table, exuding timeless appeal with its contrasting stretchers that offer a pop of color and coordinate effortlessly with the rest of the Aubrey collection. Supported by substantial canted 3-inch squared posts, the table hints at primitive styling while providing a sturdy foundation for your gatherings.
  Accompanied by four Eggshell upholstered Driftwood Parsons Chairs, this set offers both comfort and style. Gather around this exquisite dining set, where every detail is meticulously crafted to enhance your dining space with rustic allure and casual sophistication.</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>• Set includes the Aubrey 54-inch Driftwood Dining Table with Black Stretchers and 4 Aubrey Driftwood Parsons Chairs. Each item also sold separately.
 • Styling details include the dining table with substantial canted 3″ squared posts with contrasting stretchers and exposed tenons that match all the other pieces in the Aubrey collection. Mix and match finishes and pieces within the collection for a custom look.
@@ -1540,26 +1201,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ABR5454N-4US-D5PC</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-5-piece-54-round-dining-table-set-driftwood/</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>SS-ABR5454N-4US-D5PC-1.jpg;SS-ABR5454N-4US-D5PC-altview1.jpg;SS-ABR5454N-4US-D5PC-altview2.jpg;SS-ABR5454N-4US-D5PC-altview3.jpg;SS-ABR5454N-4US-D5PC-altview4.jpg;SS-ABR5454N-4US-D5PC-altview5.jpg;SS-ABR5454N-4US-D5PC-altview6.jpg;SS-ABR5454N-4US-D5PC-altview7.jpg;SS-ABR5454N-4US-D5PC-altview8.jpg;SS-ABR5454N-4US-D5PC-altview9.jpg;SS-ABR5454N-4US-D5PC-altview10.jpg;SS-ABR5454N-4US-D5PC-altview11.jpg;SS-ABR5454N-4US-D5PC-altview12.jpg;SS-ABR5454N-4US-D5PC-altview13.jpg;SS-ABR5454N-4US-D5PC-altview14.jpg;SS-ABR5454N-4US-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1584,14 +1225,14 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Immerse yourself in the perfect blend of rustic charm and casual elegance with the 5-Piece Aubrey Dining Set. Crafted to perfection, this set seamlessly marries the rustic elements of Craftsman styling with the sophistication of upholstered Parsons chairs, creating an inviting ambiance for memorable dining experiences.
  The 54-inch round Aubrey Black Dining Table exudes timeless appeal with its contrasting stretchers that offer a pop of color and coordinate effortlessly with the rest of the Aubrey collection. Supported by substantial canted 3-inch squared posts, the table hints at primitive styling while providing a sturdy foundation for your gatherings.
  Accompanied by four Eggshell upholstered Black Parsons Chairs, this set offers both comfort and style.</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>• Set includes the Aubrey 54-inch Black Dining Table with Driftwood Stretchers and 4 Aubrey Black Parsons Chairs. Each item also sold separately.
 • Styling details include the dining table with substantial canted 3″ squared posts with contrasting stretchers and exposed tenons that match all the other pieces in the Aubrey collection. Mix and match finishes and pieces within the collection for a custom look.
@@ -1611,26 +1252,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ABR5454K-4US-D5PC</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-5-piece-54-round-dining-table-set/</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>SS-ABR5454K-4US-D5PC-1.jpg;SS-ABR5454K-4US-D5PC-altview1.jpg;SS-ABR5454K-4US-D5PC-altview2.jpg;SS-ABR5454K-4US-D5PC-altview3.jpg;SS-ABR5454K-4US-D5PC-altview4.jpg;SS-ABR5454K-4US-D5PC-altview5.jpg;SS-ABR5454K-4US-D5PC-altview6.jpg;SS-ABR5454K-4US-D5PC-altview7.jpg;SS-ABR5454K-4US-D5PC-altview8.jpg;SS-ABR5454K-4US-D5PC-altview9.jpg;SS-ABR5454K-4US-D5PC-altview10.jpg;SS-ABR5454K-4US-D5PC-altview11.jpg;SS-ABR5454K-4US-D5PC-altview12.jpg;SS-ABR5454K-4US-D5PC-altview13.jpg;SS-ABR5454K-4US-D5PC-altview14.jpg;SS-ABR5454K-4US-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1655,12 +1276,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Bring modern lodge charm to your home with the Aubrey Driftwood 5-Piece Counter Dining Set. This stunning set features a 59.5-inch counter table with a robust 1.5-inch tabletop, canted square legs, and eye-catching exposed tenons in a lustrous driftwood finish complemented by black accents. The comfortable gray vegan leather counter chairs, designed for 36-inch counters, feature a 24-inch seat height, solid wood legs, and plush 5-inch cushioning for exceptional comfort. Seating up to six, this compact yet spacious set is ideal for small or medium-sized dining rooms, making for a casual, stylish addition to your home.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of acacia veneers, Asian hardwood solids and engineered woods
 • 5-piece set includes the Aubrey 59.5″ Black Counter Table with contrasting stretchers and 4 Black Counter Chairs in Camel Vegan Leather. Each item also sold separately.
@@ -1685,26 +1306,6 @@
 • Counter Chair: 23W x 19.5D x 41.75H</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ABR400N-C5PC</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-5-piece-59-5-counter-dining-set-driftwood-finish/</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>SS-ABR400N-C5PC-1.jpg;SS-ABR400N-C5PC-altview1.jpg;SS-ABR400N-C5PC-altview2.jpg;SS-ABR400N-C5PC-altview3.jpg;SS-ABR400N-C5PC-altview4.jpg;SS-ABR400N-C5PC-altview5.jpg;SS-ABR400N-C5PC-altview6.jpg;SS-ABR400N-C5PC-altview7.jpg;SS-ABR400N-C5PC-altview8.jpg;SS-ABR400N-C5PC-altview9.jpg;SS-ABR400N-C5PC-altview10.jpg;SS-ABR400N-C5PC-altview11.jpg;SS-ABR400N-C5PC-altview12.jpg;SS-ABR400N-C5PC-altview13.jpg;SS-ABR400N-C5PC-altview14.jpg;SS-ABR400N-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1729,13 +1330,13 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>A harmonious blend of elegant and rustic elements defines the Aubrey 7-piece 78-96″ dining set, tailored for today’s casual environments. Influenced by Craftsman designs, this set boasts a modern black finish, enhanced by waxed driftwood stretchers and hardware. This captivating combination offers endless mix-and-match possibilities with both black and waxed driftwood pieces across the collection.
  Combining sophisticated Parsons chairs for the captains’ seats with rustic vegan leather side chairs, this set presents a primitive yet upscale interpretation of rustic elegance. The versatile black table effortlessly transitions from intimate gatherings to inclusive feasts with the 18-inch leaf, accommodating up to 10 people comfortably. Experience the perfect fusion of style and functionality with the Aubrey dining set.</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of acacia veneers, Asian hardwood solids and engineered woods, 1.1 density foam and 100% polyester cover
 • 7-Piece Set includes the Aubrey Black 78-96″ Dining Table w/18-inch leaf, 2 Upholstered Parsons Chairs and 4 Vegan Leather Side Chairs. Each item also sold separately.
@@ -1756,26 +1357,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ABR500K-2US-D7PC</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-black-7-piece-dining-set/</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SS-ABR500K-2US-D7PC-1.jpg;SS-ABR500K-2US-D7PC-altview1.jpg;SS-ABR500K-2US-D7PC-altview2.jpg;SS-ABR500K-2US-D7PC-altview3.jpg;SS-ABR500K-2US-D7PC-altview4.jpg;SS-ABR500K-2US-D7PC-altview5.jpg;SS-ABR500K-2US-D7PC-altview6.jpg;SS-ABR500K-2US-D7PC-altview7.jpg;SS-ABR500K-2US-D7PC-altview8.jpg;SS-ABR500K-2US-D7PC-altview9.jpg;SS-ABR500K-2US-D7PC-altview10.jpg;SS-ABR500K-2US-D7PC-altview11.jpg;SS-ABR500K-2US-D7PC-altview12.jpg;SS-ABR500K-2US-D7PC-altview13.jpg;SS-ABR500K-2US-D7PC-altview14.jpg;SS-ABR500K-2US-D7PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1800,12 +1381,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>The Aubrey black-finished Server offers ample storage for all your dining essentials. With Craftsman styling, clean lines, and substantial proportions, it exudes a primitive design aesthetic. Two adjustable shelves enable you to customize your space precisely to your needs, while the contrasting driftwood wood pulls and driftwood interior facilitate mixing and matching with other driftwood dining items, especially those in the Aubrey collection.</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of acacia veneers, Asian hardwood solids and engineered woods
 • Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
@@ -1818,26 +1399,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ABR500KSV</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-server-black/</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>SS-ABR500KSV-1.jpg;SS-ABR500KSV-altview1.jpg;SS-ABR500KSV-altview2.jpg;SS-ABR500KSV-altview3.jpg;SS-ABR500KSV-altview4.jpg;SS-ABR500KSV-altview5.jpg;SS-ABR500KSV-altview6.jpg;SS-ABR500KSV-altview7.jpg;SS-ABR500KSV-altview8.jpg;SS-ABR500KSV-altview9.jpg;SS-ABR500KSV-altview10.jpg;SS-ABR500KSV-altview11.jpg;SS-ABR500KSV-altview12.jpg;SS-ABR500KSV-altview13.jpg;SS-ABR500KSV-altview14.jpg;SS-ABR500KSV-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1862,12 +1423,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>The Aubrey driftwood-finished Server offers ample storage for all your dining essentials. With Craftsman styling, clean lines, and substantial proportions, it exudes a primitive design aesthetic. Two adjustable shelves enable you to customize your space precisely to your needs, while the contrasting black wood pulls and black shelves interior facilitate mixing and matching with other black dining items, especially those in the Aubrey collection.</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of acacia veneers, Asian hardwood solids and engineered woods
 • Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
@@ -1880,26 +1441,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ABR500NSV</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-server-brown/</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>SS-ABR500NSV-1.jpg;SS-ABR500NSV-altview1.jpg;SS-ABR500NSV-altview2.jpg;SS-ABR500NSV-altview3.jpg;SS-ABR500NSV-altview4.jpg;SS-ABR500NSV-altview5.jpg;SS-ABR500NSV-altview6.jpg;SS-ABR500NSV-altview7.jpg;SS-ABR500NSV-altview8.jpg;SS-ABR500NSV-altview9.jpg;SS-ABR500NSV-altview10.jpg;SS-ABR500NSV-altview11.jpg;SS-ABR500NSV-altview12.jpg;SS-ABR500NSV-altview13.jpg;SS-ABR500NSV-altview14.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1924,13 +1465,13 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>A harmonious blend of elegant and rustic elements defines the Aubrey 7-piece 78-96″ dining set, tailored for today’s casual environments. Influenced by Craftsman designs, this set boasts a modern waxed driftwood finish, enhanced by ebony stretchers and hardware. This captivating combination offers endless mix-and-match possibilities with both black and waxed driftwood pieces across the collection.
  Combining sophisticated Parsons chairs for the captains’ seats with rustic gray vegan leather side chairs, this set presents a primitive yet upscale interpretation of rustic elegance. The versatile waxed driftwood table effortlessly transitions from intimate gatherings to inclusive feasts with the 18-inch leaf, accommodating up to 10 people comfortably. Experience the perfect fusion of style and functionality with the Aubrey dining set.</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of acacia veneers, Asian hardwood solids and engineered woods, 1.1 density foam and 100% polyester cover
 • 7-Piece Set includes the Aubrey Waxed Driftwood 78-96″ Dining Table w/18-inch leaf, 2 Upholstered Parsons Chairs and 4 Vegan Leather Side Chairs. Each item also sold separately.
@@ -1952,26 +1493,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ABR500N-2US-D7PC</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-waxed-driftwood-7-piece-78-96-dining-set/</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>SS-ABR500N-2US-D7PC-1.jpg;SS-ABR500N-2US-D7PC-altview1.jpg;SS-ABR500N-2US-D7PC-altview2.jpg;SS-ABR500N-2US-D7PC-altview3.jpg;SS-ABR500N-2US-D7PC-altview4.jpg;SS-ABR500N-2US-D7PC-altview5.jpg;SS-ABR500N-2US-D7PC-altview6.jpg;SS-ABR500N-2US-D7PC-altview7.jpg;SS-ABR500N-2US-D7PC-altview8.jpg;SS-ABR500N-2US-D7PC-altview9.jpg;SS-ABR500N-2US-D7PC-altview10.jpg;SS-ABR500N-2US-D7PC-altview11.jpg;SS-ABR500N-2US-D7PC-altview12.jpg;SS-ABR500N-2US-D7PC-altview13.jpg;SS-ABR500N-2US-D7PC-altview14.jpg;SS-ABR500N-2US-D7PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1996,12 +1517,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>The Cambridge 6-Piece Dining Set with Game Table Top is the perfect blend of style and versatility. Crafted from mango veneers and solid Asian hardwoods in a warm burnished chestnut finish, this set transforms effortlessly from dining to game night. The removable, foldable game top seats six, with each station featuring a cupholder and five chip slots for organized play. Four vegan leather-upholstered side chairs offer comfort and modern flair, making this set a stylish, space-smart solution for entertaining and everyday living.</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of mango veneers, solid Asian hardwoods, engineered woods, foam and vegan leather cover.
 • 6-Piece Set includes the Cambridge Folding, Removable Game Table Top, the Cambridge 47.25″ Round Dining Table (Top and Base) and 4 Cambridge Side Chairs. Each item also sold separately.
@@ -2018,26 +1539,6 @@
 • Experience leather-like luxury at an affordable price with the easy-care dark brown vegan leather cover on the chair</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>CBR500-GT-D6PC</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/cambridge-6-piece-dining-set-with-folding-removable-game-top/</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>SS-CBR500-GT-D6PC-1.jpg;SS-CBR500-GT-D6PC-altview1.jpg;SS-CBR500-GT-D6PC-altview2.jpg;SS-CBR500-GT-D6PC-altview3.jpg;SS-CBR500-GT-D6PC-altview4.jpg;SS-CBR500-GT-D6PC-altview5.jpg;SS-CBR500-GT-D6PC-altview6.jpg;SS-CBR500-GT-D6PC-altview7.jpg;SS-CBR500-GT-D6PC-altview8.jpg;SS-CBR500-GT-D6PC-altview9.jpg;SS-CBR500-GT-D6PC-altview10.jpg;SS-CBR500-GT-D6PC-altview11.jpg;SS-CBR500-GT-D6PC-altview12.jpg;SS-CBR500-GT-D6PC-altview13.jpg;SS-CBR500-GT-D6PC-altview14.jpg;SS-CBR500-GT-D6PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2062,13 +1563,13 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Add a touch of sophistication to your dining experience with the 52″ round Colvin white marble dining table and four Colvin black side chairs in this elegant five-piece set. The table features a lustrous white marble top with veins and marbling that accent the reeded black base, seating up to six and creating a welcoming ambiance. Inspired by Art Deco and Empire styling, it is finished in lustrous black over oak and mango veneers, radiating warmth and beauty.
  The Colvin Side Chair offers elegant comfort with an oatmeal polyester cover, a box seat, a shaped back, and black tapered legs. Built for lasting durability, these chairs ensure a stylish and sturdy addition to your home.</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>• Table Construction: 52″ round white marble veneer top with a 1.5″ thickness, reeded Art Deco-styled base.
 • Material: Expertly crafted with white marble, oak, mango veneers, Asian hardwood solids, and engineered woods.
@@ -2081,26 +1582,6 @@
 • Seating: Table seats up to six people.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>COL500KW-D5PC</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-5-piece-52-round-white-marble-dining-set-black-finish/</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>SS-COL500KW-D5PC-1.jpg;SS-COL500KW-D5PC-altview1.jpg;SS-COL500KW-D5PC-altview2.jpg;SS-COL500KW-D5PC-altview3.jpg;SS-COL500KW-D5PC-altview4.jpg;SS-COL500KW-D5PC-altview5.jpg;SS-COL500KW-D5PC-altview6.jpg;SS-COL500KW-D5PC-altview7.jpg;SS-COL500KW-D5PC-altview8.jpg;SS-COL500KW-D5PC-altview9.jpg;SS-COL500KW-D5PC-altview10.jpg;SS-COL500KW-D5PC-altview11.jpg;SS-COL500KW-D5PC-altview12.jpg;SS-COL500KW-D5PC-altview13.jpg;SS-COL500KW-D5PC-altview14.jpg;SS-COL500KW-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2125,13 +1606,13 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Add a touch of sophistication to your dining experience with the 52″ round Colvin white marble dining table and four Colvin toffee side chairs in this elegant five-piece set. The table features a lustrous white marble top with veins and marbling that accent the reeded toffee base, seating up to six and creating a welcoming ambiance. Inspired by Art Deco and Empire styling, it is finished in lustrous toffee over oak and mango veneers, radiating warmth and beauty.
  The Colvin Side Chair offers elegant comfort with an oatmeal polyester cover, a box seat, a shaped back, and black tapered legs. Built for lasting durability, these chairs ensure a stylish and sturdy addition to your home.</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>• Table Construction: 52″ round white marble veneer top with a 1.5″ thickness, reeded Art Deco-styled base.
 • Material: Expertly crafted with white marble, oak, mango veneers, Asian hardwood solids, and engineered woods.
@@ -2144,26 +1625,6 @@
 • Seating: Table seats up to six people.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>COL500NW-D5PC</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-5-piece-52-round-white-marble-dining-set-toffee-finish/</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>SS-COL500NW-D5PC-1.jpg;SS-COL500NW-D5PC-altview1.jpg;SS-COL500NW-D5PC-altview2.jpg;SS-COL500NW-D5PC-altview3.jpg;SS-COL500NW-D5PC-altview4.jpg;SS-COL500NW-D5PC-altview5.jpg;SS-COL500NW-D5PC-altview6.jpg;SS-COL500NW-D5PC-altview7.jpg;SS-COL500NW-D5PC-altview8.jpg;SS-COL500NW-D5PC-altview9.jpg;SS-COL500NW-D5PC-altview10.jpg;SS-COL500NW-D5PC-altview11.jpg;SS-COL500NW-D5PC-altview12.jpg;SS-COL500NW-D5PC-altview13.jpg;SS-COL500NW-D5PC-altview14.jpg;SS-COL500NW-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2188,12 +1649,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>The Colvin 5-piece 52″ Round Dining set brings a touch of Old Hollywood glamour right into your home. Combining elements of art deco and empire designs, this set radiates elegance and sophistication, transforming any dining room or kitchen area into a scene of luxury. The warm black finish and cane back chairs with cushioned seats strike the perfect balance between sophistication and casual styling, while the modern profile of the collection ensures a contemporary appeal. With Colvin, dining becomes a chic affair, seamlessly blending modern style with comfort and class.</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>• Set includes the Colvin 52″ Round Dining Table and 4 Colvin Black Cane Back Chairs. Each item also sold separately
 • The substantial 1.5″ thick table top rests atop a reeded art deco styled base
@@ -2204,26 +1665,6 @@
 • The chair is solidly constructed using solid wood legs reinforced with mortise-and-tenon joinery and corner blocks for exceptional stability, and elegance while ensuring the chair’s durability and reliable support for its 300 lb. weight capacity. The chair’s 2.5″ upholstered seat is cushioned with 1.2 lb. density foam to create a comfortable and delightful dining experience while the wood trimmed back provides a touch of timeless elegance while safeguarding against wear and tear. The 100% polyester fabric cover in a vanilla boucle weave provides a durable and easy-to-clean surface that resists stains and spills.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>COL500K-5PC</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-5-piece-dining-set-black/</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>SS-COL500K-5PC-1.jpg;SS-COL500K-5PC-altview1.jpg;SS-COL500K-5PC-altview2.jpg;SS-COL500K-5PC-altview3.jpg;SS-COL500K-5PC-altview4.jpg;SS-COL500K-5PC-altview5.jpg;SS-COL500K-5PC-altview6.jpg;SS-COL500K-5PC-altview7.jpg;SS-COL500K-5PC-altview8.jpg;SS-COL500K-5PC-altview9.jpg;SS-COL500K-5PC-altview10.jpg;SS-COL500K-5PC-altview11.jpg;SS-COL500K-5PC-altview12.jpg;SS-COL500K-5PC-altview13.jpg;SS-COL500K-5PC-altview14.jpg;SS-COL500K-5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2248,12 +1689,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>The Colvin 5-piece 52″ Round Dining set brings a touch of Old Hollywood glamour right into your home. Combining elements of art deco and empire designs, this set radiates elegance and sophistication, transforming any dining room or kitchen area into a scene of luxury. The warm toffee finish and cane back chairs with cushioned seats strike the perfect balance between sophistication and casual styling, while the modern profile of the collection ensures a contemporary appeal. With Colvin, dining becomes a chic affair, seamlessly blending modern style with comfort and class.</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>• Set includes the Colvin 52″ Round Dining Table and 4 Colvin Brown Cane Back Chairs. Each item also sold separately
 • The substantial 1.5″ thick table top rests atop a reeded art deco styled base
@@ -2270,26 +1711,6 @@
 • The chair’s 300 lb. weight capacity ensures durability and reliable support</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>COL500N-5PC</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-5-piece-dining-set-brown/</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>SS-COL500N-5PC-1.jpg;SS-COL500N-5PC-altview1.jpg;SS-COL500N-5PC-altview2.jpg;SS-COL500N-5PC-altview3.jpg;SS-COL500N-5PC-altview4.jpg;SS-COL500N-5PC-altview5.jpg;SS-COL500N-5PC-altview6.jpg;SS-COL500N-5PC-altview7.jpg;SS-COL500N-5PC-altview8.jpg;SS-COL500N-5PC-altview9.jpg;SS-COL500N-5PC-altview10.jpg;SS-COL500N-5PC-altview11.jpg;SS-COL500N-5PC-altview12.jpg;SS-COL500N-5PC-altview13.jpg;SS-COL500N-5PC-altview14.jpg;SS-COL500N-5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2314,12 +1735,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Experience the Colvin Black Server’s modern allure with gently rounded, reeded front doors, emanating elegance. This piece blends old Hollywood glamour with generous storage and European concealed hinges for a seamless aesthetic. Two adjustable shelves within offer practicality, while satin brass hardware accents add a touch of sophistication. Revel in its romantic charm while effortlessly concealing dining essentials.</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of oak veneers, Asian hardwood solids and engineered woods
 • Plastic glides help prevent scratches or mars to floors
@@ -2331,26 +1752,6 @@
 • 2000 lb. weight capacity ensures durability and reliable support.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>COL500KSV</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-server-black/</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>SS-COL500KSV-1.jpg;SS-COL500KSV-altview1.jpg;SS-COL500KSV-altview2.jpg;SS-COL500KSV-altview3.jpg;SS-COL500KSV-altview4.jpg;SS-COL500KSV-altview5.jpg;SS-COL500KSV-altview6.jpg;SS-COL500KSV-altview7.jpg;SS-COL500KSV-altview8.jpg;SS-COL500KSV-altview9.jpg;SS-COL500KSV-altview10.jpg;SS-COL500KSV-altview11.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2375,12 +1776,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Experience the Colvin Brown Server’s modern allure with gently rounded, reeded front doors, emanating elegance. This piece blends old Hollywood glamour with generous storage and European concealed hinges for a seamless aesthetic. Two adjustable shelves within offer practicality, while satin brass hardware accents add a touch of sophistication. Revel in its romantic charm while effortlessly concealing dining essentials.</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of oak veneers, Asian hardwood solids and engineered woods
 • Adjustable levelers add stability on uneven surfaces.
@@ -2392,26 +1793,6 @@
 • 2000 lb. weight capacity ensures durability and reliable support.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>COL500NSV</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-server-brown/</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>SS-COL500NSV-1.jpg;SS-COL500NSV-altview1.jpg;SS-COL500NSV-altview2.jpg;SS-COL500NSV-altview3.jpg;SS-COL500NSV-altview4.jpg;SS-COL500NSV-altview5.jpg;SS-COL500NSV-altview6.jpg;SS-COL500NSV-altview7.jpg;SS-COL500NSV-altview8.jpg;SS-COL500NSV-altview9.jpg;SS-COL500NSV-altview10.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2436,12 +1817,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>The Colvin Green Server adds a striking pop of color to any room, infusing the space with a tasteful blend of modern allure and old Hollywood glamor. Its gently rounded, reeded front doors create a softened, elegant profile, enhanced by European concealed hinges for a sleek, seamless aesthetic. Inside, two adjustable shelves provide practical storage for dining essentials, while satin brass hardware accents complete the look with refined sophistication. Perfect for adding both style and function, this server is a captivating piece that brings romantic charm and a touch of timeless elegance to any dining area.</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>• L500KSVExpertly crafted of oak veneers, Asian hardwood solids and engineered woods
 • Adjustable levelers add stability on uneven surfaces.
@@ -2453,26 +1834,6 @@
 • 200 lb. weight capacity ensures durability and reliable support.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>COL500ESV</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-server-green-finish/</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>SS-COL500ESV-1.jpg;SS-COL500ESV-altview1.jpg;SS-COL500ESV-altview2.jpg;SS-COL500ESV-altview3.jpg;SS-COL500ESV-altview4.jpg;SS-COL500ESV-altview5.jpg;SS-COL500ESV-altview6.jpg;SS-COL500ESV-altview7.jpg;SS-COL500ESV-altview8.jpg;SS-COL500ESV-altview9.jpg;SS-COL500ESV-altview10.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2497,12 +1858,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>The Colvin Ivory Server presents an exquisite dining accent piece, combining modern allure with hints of old Hollywood glamor. Its gently rounded, reeded front doors create an elegant, softened profile, while European concealed hinges add to its seamless aesthetic. Inside, two adjustable shelves offer practical storage space, perfect for organizing dining essentials, while the satin brass hardware adds a refined touch of sophistication. A captivating blend of style and function, this server brings romantic charm to any dining room.</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of oak veneers, Asian hardwood solids and engineered woods
 • Adjustable levelers add stability on uneven surfaces.
@@ -2514,26 +1875,6 @@
 • 200 lb. weight capacity ensures durability and reliable support.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>COL500WSV</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-server-white/</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>SS-COL500WSV-1.jpg;SS-COL500WSV-altview1.jpg;SS-COL500WSV-altview2.jpg;SS-COL500WSV-altview3.jpg;SS-COL500WSV-altview4.jpg;SS-COL500WSV-altview5.jpg;SS-COL500WSV-altview6.jpg;SS-COL500WSV-altview7.jpg;SS-COL500WSV-altview8.jpg;SS-COL500WSV-altview9.jpg;SS-COL500WSV-altview10.jpg;SS-COL500WSV-altview11.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2558,12 +1899,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>A Game Table and Chairs make both game night and dining night enjoyable! Enjoy both with the Tournament dual-purpose dining and game table. The 48-inch round table comes in a medium cherry finish and can accommodate four comfortably for dining. The dining table easily converts to a game table with the addition of the game table top that is available in brown faux-leather (as shown) or black leatherette. The game top folds and stores easily and the table goes back to a dining table. The upholstered.captain’s chair is castered for easy mobility and comes in a wide range of colors perfect for every decor.</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>• The Game Table and Chairs Set includes Table, Game Top and 4 Chairs as shown. Each item is also sold separately.
 • The 48-inch Dining Table seats four comfortably and has a pedestal base that features beaded and fluted design elements and scrolled bun feet that make it an attractive addition to any room.
@@ -2574,26 +1915,6 @@
 • Medium cherry finish</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>TU5050GTB500AG-5PC</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/game-table-and-chairs-tournament-6-piece-gray/</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>SS-TU5050GTB500AG-5PC-1.jpg;SS-TU5050GTB500AG-5PC-altview1.jpg;SS-TU5050GTB500AG-5PC-altview2.jpg;SS-TU5050GTB500AG-5PC-altview3.jpg;SS-TU5050GTB500AG-5PC-altview4.jpg;SS-TU5050GTB500AG-5PC-altview5.jpg;SS-TU5050GTB500AG-5PC-altview6.jpg;SS-TU5050GTB500AG-5PC-altview7.jpg;SS-TU5050GTB500AG-5PC-altview8.jpg;SS-TU5050GTB500AG-5PC-altview9.jpg;SS-TU5050GTB500AG-5PC-altview10.jpg;SS-TU5050GTB500AG-5PC-altview11.jpg;SS-TU5050GTB500AG-5PC-altview12.jpg;SS-TU5050GTB500AG-5PC-altview13.jpg;SS-TU5050GTB500AG-5PC-altview14.jpg;SS-TU5050GTB500AG-5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2618,12 +1939,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Enjoy both game night and dining night with this game table and chairs set. The 48-inch round table comes in a medium cherry finish and can accommodate four comfortably for dining. The game table easily converts to a game table with the addition of the game table top that is available in brown faux-leather (as shown) or black faux-leather. The game top folds and stores easily and the table goes back to a dining table. The upholstered Captain’s Chair is castered for easy mobility and comes in a wide range of colors perfect for every decor.</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>• The Game Table and Chairs Set includes Game Table, Brown Game Table Top and 4 Captains Chairs. Each item is also sold separately.
 • The Game Table is constructed of hardwood solids, cherry veneers, resin and engineered woods
@@ -2634,26 +1955,6 @@
 • Medium cherry finish</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>TU5050GTB500AT-5PC</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/game-table-and-chairs-tournament-6-piece-teal/</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>SS-TU5050GTB500AT-5PC-1.jpg;SS-TU5050GTB500AT-5PC-altview1.jpg;SS-TU5050GTB500AT-5PC-altview2.jpg;SS-TU5050GTB500AT-5PC-altview3.jpg;SS-TU5050GTB500AT-5PC-altview4.jpg;SS-TU5050GTB500AT-5PC-altview5.jpg;SS-TU5050GTB500AT-5PC-altview6.jpg;SS-TU5050GTB500AT-5PC-altview7.jpg;SS-TU5050GTB500AT-5PC-altview8.jpg;SS-TU5050GTB500AT-5PC-altview9.jpg;SS-TU5050GTB500AT-5PC-altview10.jpg;SS-TU5050GTB500AT-5PC-altview11.jpg;SS-TU5050GTB500AT-5PC-altview12.jpg;SS-TU5050GTB500AT-5PC-altview13.jpg;SS-TU5050GTB500AT-5PC-altview14.jpg;SS-TU5050GTB500AT-5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2678,12 +1979,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Sophisticated yet relaxed, the Garland Counter Height 5-Piece Dining Set brings a touch of California Casual style, perfect for coastal or lake-inspired spaces. A versatile greige finish enhances its modern profile, blending effortlessly with a breezy, laid-back aesthetic. The 36″ counter height table features a faux plank top with rasping and threading distressing for warmth and character. Four upholstered counter chairs in soft eggshell fabric with brushed brass-tone accents complete the look, balancing casual comfort with refined elegance. Crafted from oak, acacia veneers, and hardwood solids.</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>• Crafted of oak and acacia veneers; acacia, mango, Asian hardwood solids; and engineered woods
 • Set includes the Garland Counter Dining Table and four Garland Counter Chairs. Each item also sold separately.
@@ -2699,26 +2000,6 @@
 • Counter Chair: 19.5W x 23D x 41H</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>GA500T-C5PC</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-5-piece-counter-dining-set-greige-finish/</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>SS-GA500T-C5PC-1.jpg;SS-GA500T-C5PC-altview1.jpg;SS-GA500T-C5PC-altview2.jpg;SS-GA500T-C5PC-altview3.jpg;SS-GA500T-C5PC-altview4.jpg;SS-GA500T-C5PC-altview5.jpg;SS-GA500T-C5PC-altview6.jpg;SS-GA500T-C5PC-altview7.jpg;SS-GA500T-C5PC-altview8.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2743,12 +2024,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Sophisticated yet relaxed, the Garland Counter Height 5-Piece Dining Set is designed to shine in any space. A distressed toffee finish complements its modern profile, creating a seamless blend of casual elegance. The 36″ counter height table offers a comfortable setting for both dining and standing work, while its faux plank top, enhanced with rasping and threading distressing, adds character and warmth. Paired with four fully upholstered counter chairs featuring tailored canvas covers and brushed brass-tone accents, this set perfectly balances casual and formal elements for an inviting and stylish dining experience.Crafted of oak and acacia veneers; acacia, mango, Asian hardwood solids; and engineered woods</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>• Crafted of oak and acacia veneers; acacia, mango, Asian hardwood solids; and engineered woods
 • Set includes the Garland Counter Dining Table and four Garland Counter Chairs. Each item also sold separately.
@@ -2764,26 +2045,6 @@
 • Counter Chair: 19.5W x 23D x 41H</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>GA500-C5PC</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-5-piece-counter-dining-set/</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>SS-GA500-C5PC-1.jpg;SS-GA500-C5PC-altview1.jpg;SS-GA500-C5PC-altview2.jpg;SS-GA500-C5PC-altview3.jpg;SS-GA500-C5PC-altview4.jpg;SS-GA500-C5PC-altview5.jpg;SS-GA500-C5PC-altview6.jpg;SS-GA500-C5PC-altview7.jpg;SS-GA500-C5PC-altview8.jpg;SS-GA500-C5PC-altview9.jpg;SS-GA500-C5PC-altview10.jpg;SS-GA500-C5PC-altview11.jpg;SS-GA500-C5PC-altview12.jpg;SS-GA500-C5PC-altview13.jpg;SS-GA500-C5PC-altview14.jpg;SS-GA500-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2808,12 +2069,12 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Sophisticated yet relaxed, the Garland Dining Collection embodies California Casual style with a distressed greige finish and clean, crisp lines. The Garland Table extends to 88 inches with an 18-inch leaf, seating up to eight comfortably. It pairs beautifully with fully upholstered Parsons chairs in tightly tailored eggshell fabric, accented with brass for a mix of casual and formal design. Complete the look with the Sideboard, featuring tasteful hardware and hidden storage. Warm and inviting, the Garland Collection is perfect for effortless entertaining.</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>• Constructed of oak and acacia veneers, solid Asian hardwoods and engineered wood
 • Table Top extends from 70 to 88 inches with the insertion of the included 18-inch leaf
@@ -2827,26 +2088,6 @@
 • The wood is hand-stained in a natural multi-step greige finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>GA500T-D5PC</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-5-piece-dining-set-distressed-greige-finish/</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>SS-GA500T-D5PC-1.jpg;SS-GA500T-D5PC-altview1.jpg;SS-GA500T-D5PC-altview2.jpg;SS-GA500T-D5PC-altview3.jpg;SS-GA500T-D5PC-altview4.jpg;SS-GA500T-D5PC-altview5.jpg;SS-GA500T-D5PC-altview6.jpg;SS-GA500T-D5PC-altview7.jpg;SS-GA500T-D5PC-altview8.jpg;SS-GA500T-D5PC-altview9.jpg;SS-GA500T-D5PC-altview10.jpg;SS-GA500T-D5PC-altview11.jpg;SS-GA500T-D5PC-altview12.jpg;SS-GA500T-D5PC-altview13.jpg;SS-GA500T-D5PC-altview14.jpg;SS-GA500T-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2871,12 +2112,12 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Sophisticated and elegant but with a casual accent, the Garland Dining Collection is built to shine in any environment.A distressed toffee finish blends with a sophisticated modern profile in a relaxed style-blending design marked by clean, crisp lines. The Garland Table comes with an 18-inch leaf that extends the table to 88 inches to seat up to eight comfortably and marries beautifully with the fully upholstered Parsons Chairs in a tightly tailored canvas cover with a brass accent, mixing casual and formal designs in a relaxed but elegant design. Pair these beauties with the Sideboard with a tasteful hardware treatment for an ultra-clean presentation that also offers plenty of hidden storage. Seat all of your family and friends in a comfortable but elegant dining presentation with the Garland Dining Collection</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of acacia veneers, solid Asian hardwoods and engineered wood
 • Table Top extends from 70 to 88 inches with the insertion of the included 18-inch leaf
@@ -2889,26 +2130,6 @@
 • Toffee finish</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>GA500-5PC</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-5-piece-dining-set/</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>SS-GA500-5PC-1.jpg;SS-GA500-5PC-altview1.jpg;SS-GA500-5PC-altview2.jpg;SS-GA500-5PC-altview3.jpg;SS-GA500-5PC-altview4.jpg;SS-GA500-5PC-altview5.jpg;SS-GA500-5PC-altview6.jpg;SS-GA500-5PC-altview7.jpg;SS-GA500-5PC-altview8.jpg;SS-GA500-5PC-altview9.jpg;SS-GA500-5PC-altview10.jpg;SS-GA500-5PC-altview11.jpg;SS-GA500-5PC-altview12.jpg;SS-GA500-5PC-altview13.jpg;SS-GA500-5PC-altview14.jpg;SS-GA500-5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2933,12 +2154,12 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>The Garland Curio brings cool sophistication to any space. At 70 inches tall, this transitional design showcases a lustrous distressed grieve finish with clear, beveled, wood-rimmed glass doors for timeless style. Inside, three spacious shelves provide ample room for storing or displaying china, collectibles, or décor. Subtle distressing and rub-through accents soften the look, offering rustic elegance with a relaxed feel. Perfect for dining rooms, living spaces, or offices, the Garland Curio, Greige Finish blends beauty and function for stylish storage.</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of acacia veneers, solid Asian hardwoods and engineered wood
 • Kiln-dried wood helps prevent warping, splitting and cracking
@@ -2951,26 +2172,6 @@
 • The wood is hand-stained in a natural multi-step distressed griege finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>GA500TC</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-curio-greige-finish/</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>SS-GA500TC-1.jpg;SS-GA500TC-altview1.jpg;SS-GA500TC-altview2.jpg;SS-GA500TC-altview3.jpg;SS-GA500TC-altview4.jpg;SS-GA500TC-altview5.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2995,12 +2196,12 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>The Garland Curio brings warmth and character to any space. At 70 inches tall, this transitional design showcases a lustrous toffee finish with clear, beveled, wood-rimmed glass doors for timeless style. Inside, three spacious shelves provide ample room for storing or displaying china, collectibles, or décor. Subtle distressing and rub-through accents soften the look, offering rustic elegance with a relaxed feel. Perfect for dining rooms, living spaces, or offices, the Garland Curio blends beauty and function for stylish storage.</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of acacia veneers, solid Asian hardwoods and engineered wood
 • Kiln-dried wood helps prevent warping, splitting and cracking
@@ -3013,26 +2214,6 @@
 • The wood is hand-stained in a natural multi-step toffee finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>GA500C</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-curio/</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>SS-GA500C-1.jpg;SS-GA500C-altview1.jpg;SS-GA500C-altview2.jpg;SS-GA500C-altview3.jpg;SS-GA500C-altview4.jpg;SS-GA500C-altview5.jpg;SS-GA500C-altview6.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3057,12 +2238,12 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>The Garland Server marries a modern silohuette with a relaxed, lightly distressed toffee finish in a dining side piece with the perfect casually elegant style of today’s dining rooms. A modern plinth base and tastefully appointed satin brass hardware creates extremely clean lines that displays the natural beauty of the wood expertly. Three drawers and a door allow for plenty of storage base of any dining area in a neat, beautiful package that can stand on its own or can be paired with the matching Garland dining collection.</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>• Constructed of veneers, solids and engineered woods
 • Three deep drawers and one door
@@ -3071,36 +2252,16 @@
 • Toffee finish</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>GA500SV</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-server/</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>SS-GA500SV-1.jpg;SS-GA500SV-altview1.jpg;SS-GA500SV-altview2.jpg;SS-GA500SV-altview3.jpg;SS-GA500SV-altview4.jpg;SS-GA500SV-altview5.jpg;SS-GA500SV-altview6.jpg;SS-GA500SV-altview7.jpg;SS-GA500SV-altview8.jpg;SS-GA500SV-altview9.jpg;SS-GA500SV-altview10.jpg;SS-GA500SV-altview11.jpg;SS-GA500SV-altview12.jpg;SS-GA500SV-altview13.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SS-MM500K-D5PC</t>
+          <t>SS-GA500TSV</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Magnolia 5-Piece 72-108-inch Dining Set</t>
+          <t>Garland 64″ Sideboard, Greige Finish</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -3112,15 +2273,53 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>The Garland Sideboard in distressed greige finish brings California Casual style to the dining room with clean lines, a modern plinth base, and tasteful hardware. Three drawers and a door provide practical storage that pairs with the matching Garland dining collection.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>• Constructed of veneers, solids and engineered woods
+• Three deep drawers and one door
+• Metal side drawer guides
+• Medium distressing
+• Distressed greige finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SS-MM500K-D5PC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Magnolia 5-Piece 72-108-inch Dining Set</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>A blend of farmhouse finished and substantial proportions combine in the simple sophistication of the Magnolia dining collection. This 5-piece set contrasts black spindle back chairs with a black table base in a striking combination of neutrals. A naturally finished top unites the different aspects of this generously scaled dining set. The dining table centerpiece of the set starts at 72-inches but expands to a full 108-inches in an instant with the addition of the 2-18-inch leaves for a table that easily accommodates 10 guests for dinner. The clean lines and crisp finishes create a light and airy set perfect for larger dining areas.</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>• Set includes Magnolia 72-108-inch Dining Table and 4 Magnolia dining chairs. Each item also sold separately
 • Crafted from Oak veneers with Acacia and Asian hardwood solids and engineered woods
@@ -3140,56 +2339,36 @@
 • The wood is hand-stained in a natural multi-step natural and black two-tone finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>MM500K-D5PC</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-5-piece-72-108-inch-dining-set/</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>SS-MM500K-D5PC-1.jpg;SS-MM500K-D5PC-altview1.jpg;SS-MM500K-D5PC-altview2.jpg;SS-MM500K-D5PC-altview3.jpg;SS-MM500K-D5PC-altview4.jpg;SS-MM500K-D5PC-altview5.jpg;SS-MM500K-D5PC-altview6.jpg;SS-MM500K-D5PC-altview7.jpg;SS-MM500K-D5PC-altview8.jpg;SS-MM500K-D5PC-altview9.jpg;SS-MM500K-D5PC-altview10.jpg;SS-MM500K-D5PC-altview11.jpg;SS-MM500K-D5PC-altview12.jpg;SS-MM500K-D5PC-altview13.jpg;SS-MM500K-D5PC-altview14.jpg;SS-MM500K-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>SS-MM600K-D5PC</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Magnolia 5-Piece 80-96″ Dining Set with Side Chair</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>The Magnolia 80-96″ Dining Set exudes modern sophistication. The dining table boasts bold, clean lines and an expandable top, adorned with a striking ebony stain and gold accents. Accommodating up to eight guests, it effortlessly extends from 80 to 96 inches with the included 16-inch leaf. Paired with the Magnolia Side Chair, this upholstered seat offers tailored elegance with side welting and a linen-look polyester cover for easy cleaning. Guests will relish the 4-inch cushioned seat atop the solid wood twin scissor leg base. Elevate your dining space with this blend of comfort and beauty.</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>• Crafted of Asian hardwood solids, foam, 100% polyester fabric and engineered woods
 • Set includes the 80-96″ Magnolia Dining Table w/18″ leaf and 4 Upholstered Side Chairs. Each item also sold separately.
@@ -3204,56 +2383,36 @@
 • The wood is hand-stained in a natural multi-step ebony finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>MM600K-D5PC</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-5-piece-80-96-dining-set-with-side-chair/</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>SS-MM600K-D5PC-1.jpg;SS-MM600K-D5PC-altview1.jpg;SS-MM600K-D5PC-altview2.jpg;SS-MM600K-D5PC-altview3.jpg;SS-MM600K-D5PC-altview4.jpg;SS-MM600K-D5PC-altview5.jpg;SS-MM600K-D5PC-altview6.jpg;SS-MM600K-D5PC-altview7.jpg;SS-MM600K-D5PC-altview8.jpg;SS-MM600K-D5PC-altview9.jpg;SS-MM600K-D5PC-altview10.jpg;SS-MM600K-D5PC-altview11.jpg;SS-MM600K-D5PC-altview12.jpg;SS-MM600K-D5PC-altview13.jpg;SS-MM600K-D5PC-altview14.jpg;SS-MM600K-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>SS-MM520K-D5PC</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Magnolia 52-inch Round 5-Piece Dining Set, Black</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Indulge in the refined allure of the Magnolia Dining Set. This set transforms your dining area with its bold black finish, tastefully highlighted with weathered sand accents for a neutral yet captivating aesthetic. The centerpiece, a 52-inch round table, offers an intimate dining experience for up to six people. Surrounding this are solid wood side chairs, their elegance matched by comfort, and featuring beautifully tapered tubular legs. This Magnolia set is not just furniture; it’s a statement of style, a mingling of luxury and homeliness that’s sure to impress.</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>• Set includes the 52-inch Round Black Magnolia Dining Table and 4 Magnolia Upholstered Side Chairs, Each item also sold separately.
 • Crafted from Asian veneers, Asian hardwood solids and engineered woods
@@ -3268,56 +2427,36 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>MM520K-D5PC</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-52-inch-round-5-piece-dining-set-blac/</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>SS-MM520K-D5PC-1.jpg;SS-MM520K-D5PC-altview1.jpg;SS-MM520K-D5PC-altview2.jpg;SS-MM520K-D5PC-altview3.jpg;SS-MM520K-D5PC-altview4.jpg;SS-MM520K-D5PC-altview5.jpg;SS-MM520K-D5PC-altview6.jpg;SS-MM520K-D5PC-altview7.jpg;SS-MM520K-D5PC-altview8.jpg;SS-MM520K-D5PC-altview9.jpg;SS-MM520K-D5PC-altview10.jpg;SS-MM520K-D5PC-altview11.jpg;SS-MM520K-D5PC-altview12.jpg;SS-MM520K-D5PC-altview13.jpg;SS-MM520K-D5PC-altview14.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>SS-MM5454K-D5PC</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Magnolia 54-inch Round 5-Piece Dining Set</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Modern meets farmhouse in the Magnolia 54-inch Round 5-Piece Dining Set. Large yet intimate, it’s perfect for morning breakfasts or supper club gatherings. The sand and black finish, combined with canted legs forming a sled base, creates a sleek and flowing design. Paired with four solid wood farmhouse chairs, each featuring a shaped solid wood seat, this set remains authentic to its origins while adding a touch of comfort. The Magnolia table comfortably seats six, making it an ideal choice for any dining space.</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>• Crafted of solid Asian hardwoods, oak veneers and engineered woods
 • The 5-piece set includes the Magnolia black and sand 54-inch round Dining Table and 4 Magnolia Side Chairs. Each item also sold separately.
@@ -3334,56 +2473,36 @@
 Side Chair: 20″W x 23″D x 40.25″H</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>MM5454K-D5PC</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-54-inch-round-5-piece-dining-set/</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>SS-MM5454K-D5PC-1.jpg;SS-MM5454K-D5PC-altview1.jpg;SS-MM5454K-D5PC-altview2.jpg;SS-MM5454K-D5PC-altview3.jpg;SS-MM5454K-D5PC-altview4.jpg;SS-MM5454K-D5PC-altview5.jpg;SS-MM5454K-D5PC-altview6.jpg;SS-MM5454K-D5PC-altview7.jpg;SS-MM5454K-D5PC-altview8.jpg;SS-MM5454K-D5PC-altview9.jpg;SS-MM5454K-D5PC-altview10.jpg;SS-MM5454K-D5PC-altview11.jpg;SS-MM5454K-D5PC-altview12.jpg;SS-MM5454K-D5PC-altview13.jpg;SS-MM5454K-D5PC-altview14.jpg;SS-MM5454K-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>SS-MM500-D7PC</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Magnolia 7-Piece 72-108-inch Dining Set</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>A blend of farmhouse finished and substantial proportions combine in the simple sophistication of the Magnolia dining collection. This 7-piece set contrasts black spindle back chairs with a white table base and Server in a striking combination of neutrals. A natural finish unites the different aspects of this generously scaled dining set. The dining table centerpiece of the set starts at 72-inches but expands to a full 108-inches in an instant with the addition of the 2-18-inch leaves for a table that easily accommodates 10 guests for dinner. The clean lines and crisp finishes create a light and airy set perfect for larger dining areas.</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>• Set includes Magnolia 72-108-inch Dining Table and 6 Magnolia dining chairs. Each item also sold separately
 • Crafted from Acacia and Asian hardwood solids, engineered woods and Oak veneers
@@ -3403,57 +2522,37 @@
 • White and natural two-tone finish</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>MM500-D7PC</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-7-piece-72-108-inch-dining-set/</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>SS-MM500-D7PC-1.jpg;SS-MM500-D7PC-altview1.jpg;SS-MM500-D7PC-altview2.jpg;SS-MM500-D7PC-altview3.jpg;SS-MM500-D7PC-altview4.jpg;SS-MM500-D7PC-altview5.jpg;SS-MM500-D7PC-altview6.jpg;SS-MM500-D7PC-altview7.jpg;SS-MM500-D7PC-altview8.jpg;SS-MM500-D7PC-altview9.jpg;SS-MM500-D7PC-altview10.jpg;SS-MM500-D7PC-altview11.jpg;SS-MM500-D7PC-altview12.jpg;SS-MM500-D7PC-altview13.jpg;SS-MM500-D7PC-altview14.jpg;SS-MM500-D7PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>SS-MM520KSV</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Magnolia Cathedral Doored Server, Black</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>A masterpiece of versatility and style, the Magnolia Server reveals a world of display possibilities behind beautiful Cathedral glass doors. Hand-stained in a striking ebony finish with a contrasting weathered sand interior, this cabinet features adjustable shelves and hidden cable management for a seamless transition from a dining room sideboard, to a living room entertainment center, or even a stunning hallway console
  The clean lines and modern style of the Magnolia Server adds elegance, sophistication and storage to any room in a home.</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>• Crafted from Asian veneers, Asian hardwood solids and engineered woods
 • Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
@@ -3464,56 +2563,36 @@
 • The wood is hand-stained in a natural multi-step ebony finish with weathered sand interior to highlight the interior of the case while offering a beautiful contrast</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>MM520KSV</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-cathedral-doored-server-black/</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>SS-MM520KSV-1.jpg;SS-MM520KSV-altview1.jpg;SS-MM520KSV-altview2.jpg;SS-MM520KSV-altview3.jpg;SS-MM520KSV-altview4.jpg;SS-MM520KSV-altview5.jpg;SS-MM520KSV-altview6.jpg;SS-MM520KSV-altview7.jpg;SS-MM520KSV-altview8.jpg;SS-MM520KSV-altview9.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>SS-MM520TSV</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Magnolia Cathedral Doored Server, Weathered Sand</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>A masterpiece of versatility and style, the Magnolia Server reveals a world of display possibilities behind beautiful Cathedral glass doors. Hand-stained in a striking weathered sand finish with a contrasting black interior, this cabinet features adjustable shelves and hidden cable management for a seamless transition from a dining room sideboard, to a living room entertainment center, or even a stunning hallway console The clean lines and modern style of the Magnolia Server adds elegance, sophistication and storage to any room in a home.</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>• Crafted from oak veneers, Asian hardwood solids and engineered woods
 • Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
@@ -3527,56 +2606,36 @@
 • The black accented interior and weathered sand exterior allows seamless style integration with all elements of the Magnolia collection</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>MM520TSV</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-cathedral-doored-server-dusty-blue-copy/</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>SS-MM520TSV-1.jpg;SS-MM520TSV-altview1.jpg;SS-MM520TSV-altview2.jpg;SS-MM520TSV-altview3.jpg;SS-MM520TSV-altview4.jpg;SS-MM520TSV-altview5.jpg;SS-MM520TSV-altview6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>SS-MM520BSV</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Magnolia Cathedral Doored Server, Dusty Blue Finish</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>A masterpiece of style and versatility, the Magnolia Server transforms any room with its bold dusty blue finish and weathered sand interior. Elegant Cathedral glass doors reveal adjustable shelves for display, while hidden cable management ensures seamless integration. Whether as a sideboard, entertainment center, or hallway console, it blends practicality with sophistication. Clean lines and thoughtful details enhance both style and storage, making it a refined choice for any home—offering modern elegance with functionality in every setting.</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>• Crafted from oak veneers, Asian hardwood solids and engineered woods
 • Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
@@ -3589,91 +2648,16 @@
 • Adjustable levelers add stability on uneven floors</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>MM520BSV</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-cathedral-doored-server-dusty-blue/</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>SS-MM520BSV-1.jpg;SS-MM520BSV-altview1.jpg;SS-MM520BSV-altview2.jpg;SS-MM520BSV-altview3.jpg;SS-MM520BSV-altview4.jpg;SS-MM520BSV-altview5.jpg;SS-MM520BSV-altview6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>SS-NP600-C5PC-S</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Napa 5-Piece Counter Dining Set, Sand</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>A grandly scaled counter dining collection with modern farmhouse styling, Napa features a Counter Table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable. Pair with the Napa Server to complete the ultimate in contemporary dining design.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>• Set includes Counter Table &amp; 4 Counter Chairs. Each item also sold separately.
-• Weathered Sand finish</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>NP600-C5PC-S</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-5-piece-counter-dining-set/</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>SS-NP600-C5PC-S-1.jpg;SS-NP600-C5PC-S-altview1.jpg;SS-NP600-C5PC-S-altview2.jpg;SS-NP600-C5PC-S-altview3.jpg;SS-NP600-C5PC-S-altview4.jpg;SS-NP600-C5PC-S-altview5.jpg;SS-NP600-C5PC-S-altview6.jpg;SS-NP600-C5PC-S-altview7.jpg;SS-NP600-C5PC-S-altview8.jpg;SS-NP600-C5PC-S-altview9.jpg;SS-NP600-C5PC-S-altview10.jpg;SS-NP600-C5PC-S-altview11.jpg;SS-NP600-C5PC-S-altview12.jpg;SS-NP600-C5PC-S-altview13.jpg;SS-NP600-C5PC-S-altview14.jpg;SS-NP600-C5PC-S-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SS-NP500-D5PC-S</t>
+          <t>SS-NP600-C5PC-S</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Napa 5-Piece 72-108-inch Dining Set, Sand</t>
+          <t>Napa 5-Piece Counter Dining Set, Sand</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -3688,12 +2672,47 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>A grandly scaled counter dining collection with modern farmhouse styling, Napa features a Counter Table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable. Pair with the Napa Server to complete the ultimate in contemporary dining design.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>• Set includes Counter Table &amp; 4 Counter Chairs. Each item also sold separately.
+• Weathered Sand finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SS-NP500-D5PC-S</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Napa 5-Piece 72-108-inch Dining Set, Sand</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Napa is a grandly scaled California casual collection with ample dining space for everyone. With its beautiful plank-effect top and two 18-inch leaves, it can accommodate up to ten people and offers a light and airy weathered sand finish. The double pedestal base has exposed tenons and pairs gracefully with the cushioned seat of the Schoolhouse Side Chair. Comfortable and stylish, Napa offers large-scale dining in a fresh look.</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>• Crafted of mango and Asian hardwoods, mango veneers and engineered hardwoods
 • Side Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
@@ -3707,56 +2726,36 @@
 • The wood is hand-stained in a natural multi-step weathered sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>NP500-D5PC-S</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-5-piece-dining-set-sandtable-4-side-chairs/</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>SS-NP500-D5PC-S-1.jpg;SS-NP500-D5PC-S-altview1.jpg;SS-NP500-D5PC-S-altview2.jpg;SS-NP500-D5PC-S-altview3.jpg;SS-NP500-D5PC-S-altview4.jpg;SS-NP500-D5PC-S-altview5.jpg;SS-NP500-D5PC-S-altview6.jpg;SS-NP500-D5PC-S-altview7.jpg;SS-NP500-D5PC-S-altview8.jpg;SS-NP500-D5PC-S-altview9.jpg;SS-NP500-D5PC-S-altview10.jpg;SS-NP500-D5PC-S-altview11.jpg;SS-NP500-D5PC-S-altview12.jpg;SS-NP500-D5PC-S-altview13.jpg;SS-NP500-D5PC-S-altview14.jpg;SS-NP500-D5PC-S-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>SS-NP500-5PC</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Napa 5-Piece Dining Set</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>A grandly scaled dining collection with modern farmhouse styling, Napa features a dining table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed tenons and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable.</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>• Constructed of mango and Asian hardwoods, mango veneers and engineered hardwoods
 • Side Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
@@ -3767,56 +2766,36 @@
 • Dusky cedar finish</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>NP500-5PC</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-6-piece-dining-settable-6-side-chairs/</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>SS-NP500-5PC-1.jpg;SS-NP500-5PC-altview1.jpg;SS-NP500-5PC-altview2.jpg;SS-NP500-5PC-altview3.jpg;SS-NP500-5PC-altview4.jpg;SS-NP500-5PC-altview5.jpg;SS-NP500-5PC-altview6.jpg;SS-NP500-5PC-altview7.jpg;SS-NP500-5PC-altview8.jpg;SS-NP500-5PC-altview9.jpg;SS-NP500-5PC-altview10.jpg;SS-NP500-5PC-altview11.jpg;SS-NP500-5PC-altview12.jpg;SS-NP500-5PC-altview13.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>SS-NP600-5PC</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Napa 5-Piece Counter Dining Set</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>A grandly scaled counter dining collection with modern farmhouse styling, Napa features a Counter Table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable. Pair with the Napa Server to complete the ultimate in contemporary dining design.</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>• Constructed of mango and Asian hardwoods, mango veneers and engineered hardwoods
 • Counter Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
@@ -3827,56 +2806,36 @@
 • Dusky cedar finish</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>NP600-5PC</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-7-piece-counter-dining-setcounter-table-6-counter-chairs/</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>SS-NP600-5PC-1.jpg;SS-NP600-5PC-altview1.jpg;SS-NP600-5PC-altview2.jpg;SS-NP600-5PC-altview3.jpg;SS-NP600-5PC-altview4.jpg;SS-NP600-5PC-altview5.jpg;SS-NP600-5PC-altview6.jpg;SS-NP600-5PC-altview7.jpg;SS-NP600-5PC-altview8.jpg;SS-NP600-5PC-altview9.jpg;SS-NP600-5PC-altview10.jpg;SS-NP600-5PC-altview11.jpg;SS-NP600-5PC-altview12.jpg;SS-NP600-5PC-altview13.jpg;SS-NP600-5PC-altview14.jpg;SS-NP600-5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>SS-NP5007PC</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Napa 7-Piece Dining Set</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>A grandly scaled dining collection with modern farmhouse styling, Napa features a dining table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed tenons and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable. Upholstered Captains Chairs add a more elegant presentation with an outside wooden ladderback treatment that looks as good from the back as the front.</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>• Constructed of mango and Asian hardwoods, mango veneers and engineered hardwoods
 • Side Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
@@ -3887,56 +2846,36 @@
 • Dusky cedar finish</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>NP5007PC</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-7-piece-dining-settable-2-upholstered-4-side-chairs/</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>SS-NP5007PC-1.jpg;SS-NP5007PC-altview1.jpg;SS-NP5007PC-altview2.jpg;SS-NP5007PC-altview3.jpg;SS-NP5007PC-altview4.jpg;SS-NP5007PC-altview5.jpg;SS-NP5007PC-altview6.jpg;SS-NP5007PC-altview7.jpg;SS-NP5007PC-altview8.jpg;SS-NP5007PC-altview9.jpg;SS-NP5007PC-altview10.jpg;SS-NP5007PC-altview11.jpg;SS-NP5007PC-altview12.jpg;SS-NP5007PC-altview13.jpg;SS-NP5007PC-altview14.jpg;SS-NP5007PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>SS-NP500SV</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Napa Server</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Napa presents contemporary styling in a Server that adds display and space to any living area. This functional Server has a warm dusky cedar finish that is perfect for home environments. Two shelves for wine storage are accented with a glass top so you can show off your collection and the piece comes along with two additional drawers and two glass front doors for additional storage and display. The sleek modern lines are accented with a relaxed silhouette that allows it to be dressed up or down to your preference.</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>• Constructed of mango and Asian hardwoods, mango veneers, and engineered hardwoods
 • Two glass doors, two drawers, and two shelves with removable bottle storage inserts
@@ -3946,56 +2885,36 @@
 • Dusky cedar finish</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>NP500SV</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-server/</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>SS-NP500SV-1.jpg;SS-NP500SV-altview1.jpg;SS-NP500SV-altview2.jpg;SS-NP500SV-altview3.jpg;SS-NP500SV-altview4.jpg;SS-NP500SV-altview5.jpg;SS-NP500SV-altview6.jpg;SS-NP500SV-altview7.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>SS-RED500K-D5PC</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Reid 5-Piece Dining Set, Black Finish with Saddle Brown Vegan Leather</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>The Reid 5-Piece Dining Set blends modern style with everyday versatility, featuring the Reid 77–95″ Dining Table and four coordinating side chairs. The table expands with an 18-inch leaf to seat up to eight and showcases a deep black finish for a neutral accent to any room. Reid chairs add tailored comfort with box-pleat seats, foam cushioning, and easy-care saddle brown vegan leather. An exposed webbed back and angled seat provide relaxed support, making this set ideal for dining, entertaining, or casual gatherings.</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of ash veneers, solid Asian hardwoods, vegan leather, foam and engineered woods
 • 5-Piece Set includes the Reid 77-95″ Dining Table with 18-inch leaf and 4 Reid Saddle Brown Vegan Leather Side Chairs. Each item also sold separately.
@@ -4013,56 +2932,36 @@
 • Cleaning Code: W — Easy-care vegan leather wipes clean with mild soap and water, offering durable style that stands up to everyday use and spills.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>RED500K-D5PC</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/reid-5-piece-dining-set-black-finish-with-saddle-brown-vegan-leather/</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>SS-RED500K-D5PC-1.jpg;SS-RED500K-D5PC-altview1.jpg;SS-RED500K-D5PC-altview2.jpg;SS-RED500K-D5PC-altview3.jpg;SS-RED500K-D5PC-altview4.jpg;SS-RED500K-D5PC-altview5.jpg;SS-RED500K-D5PC-altview6.jpg;SS-RED500K-D5PC-altview7.jpg;SS-RED500K-D5PC-altview8.jpg;SS-RED500K-D5PC-altview9.jpg;SS-RED500K-D5PC-altview10.jpg;SS-RED500K-D5PC-altview11.jpg;SS-RED500K-D5PC-altview12.jpg;SS-RED500K-D5PC-altview13.jpg;SS-RED500K-D5PC-altview14.jpg;SS-RED500K-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>SS-RED500-D5PC</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Reid 5-Piece 77-95″ Dining Set, Sand Finish with Camel Vegan Leather</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>The Reid 5-Piece Dining Set blends modern style with everyday versatility, featuring the Reid 77–95″ Dining Table and four coordinating side chairs. The table expands with an 18-inch leaf to seat up to eight and showcases a light sand finish that highlights natural wood grain. Reid chairs add tailored comfort with box-pleat seats, foam cushioning, and easy-care camel vegan leather. An exposed webbed back and angled seat provide relaxed support, making this set ideal for dining, entertaining, or casual gatherings.</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of ash veneers, solid Asian hardwoods, vegan leather, foam and engineered woods
 • 5-Piece Set includes the Reid 77-95″ Dining Table with 18-inch leaf and 4 Reid Camel Vegan Leather Side Chairs. Each item also sold separately.
@@ -4080,56 +2979,36 @@
 • Cleaning Code: W — Easy-care vegan leather wipes clean with mild soap and water, offering durable style that stands up to everyday use and spills.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>RED500-D5PC</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/reid-5-piece-dining-set-sand-finish-with-camel-vegan-leather/</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>SS-RED500-D5PC-1.jpg;SS-RED500-D5PC-altview1.jpg;SS-RED500-D5PC-altview2.jpg;SS-RED500-D5PC-altview3.jpg;SS-RED500-D5PC-altview4.jpg;SS-RED500-D5PC-altview5.jpg;SS-RED500-D5PC-altview6.jpg;SS-RED500-D5PC-altview7.jpg;SS-RED500-D5PC-altview8.jpg;SS-RED500-D5PC-altview9.jpg;SS-RED500-D5PC-altview10.jpg;SS-RED500-D5PC-altview11.jpg;SS-RED500-D5PC-altview12.jpg;SS-RED500-D5PC-altview13.jpg;SS-RED500-D5PC-altview14.jpg;SS-RED500-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>SS-RED500KSV</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Reid 60″ Server, Black Finish</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>The Reid 60″ Server offers a modern take on a versatile dining and entertainment piece. Its rich midnight black finish over ash veneers delivers a bold, refined look for any room. Two glass doors provide display, storage, and easy remote access, while two adjustable interior shelves customize space for décor or electronics. Convenient charging is built in with two electric outlets plus USB-A and USB-C ports on the outer upper back, paired with a wire escape for organized cords. Clean lines complete the look overall.</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of ash veneers, solid Asian hardwoods and engineered woods
 • Kiln-dried wood helps prevent warping, splitting and cracking
@@ -4144,56 +3023,36 @@
 • Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>RED500KSV</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/reid-60-server-black-finish/</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>SS-RED500KSV-1.jpg;SS-RED500KSV-altview1.jpg;SS-RED500KSV-altview2.jpg;SS-RED500KSV-altview3.jpg;SS-RED500KSV-altview4.jpg;SS-RED500KSV-altview5.jpg;SS-RED500KSV-altview6.jpg;SS-RED500KSV-altview7.jpg;SS-RED500KSV-altview8.jpg;SS-RED500KSV-altview9.jpg;SS-RED500KSV-altview10.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>SS-RED500TSV</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Reid 60″ Server, Sand Finish</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>The Reid 60″ Server offers a modern take on a versatile dining and entertainment piece. Its light, airy sand finish over ash veneers brings a fresh, open feel to any room. Two glass doors provide display, storage, and easy remote access, while two adjustable interior shelves customize space for décor or electronics. Convenient charging is built in with two electric outlets plus USB-A and USB-C ports on the outer upper back, paired with a wire escape for organized cords. Clean lines complete the look overall.</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>• Expertly crafted of ash veneers, solid Asian hardwoods and engineered woods
 • Kiln-dried wood helps prevent warping, splitting and cracking
@@ -4209,56 +3068,36 @@
 • Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>RED500TSV</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/reid-60-server-sand-finish/</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>SS-RED500TSV-1.jpg;SS-RED500TSV-altview1.jpg;SS-RED500TSV-altview2.jpg;SS-RED500TSV-altview3.jpg;SS-RED500TSV-altview4.jpg;SS-RED500TSV-altview5.jpg;SS-RED500TSV-altview6.jpg;SS-RED500TSV-altview7.jpg;SS-RED500TSV-altview8.jpg;SS-RED500TSV-altview9.jpg;SS-RED500TSV-altview10.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>SS-RL600K-GT-C6PC</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Rylie 6-PIece Counter Game Dining Set, Black Finish</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>Dive into a mix of classic fun and modern chic with the Rylie Folding Game Counter Dining Set. This sleek black set features swivel Captain’s Chairs in sand vegan leather, accented with stylish copper nailheads. The star is the removable game top, decked out with 16 cupholders and eight chip holders for ultimate game nights. Post-play, it transforms into a charming dining spot. Crafted from durable oak veneers and hardwoods, this set seats four comfortably and assembles easily, making it a perfect blend of form and function.</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>• Set includes the Rylie Folding Game Top, the Rylie 48-inch Counter Dining Table and 4 Rylie Counter Captains Chairs. All in black finish with sand vegan leather. Each item also sold separately..
 • Expertly crafted of oak veneers, poplar and Asian hardwood solids and engineered woods, foam and vegan leather
@@ -4281,56 +3120,36 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>RL600K-GT-C6PC</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/rylie-6-piece-counter-game-dining-set-black-finish/</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>SS-RL600K-GT-C6PC-1.jpg;SS-RL600K-GT-C6PC-altview1.jpg;SS-RL600K-GT-C6PC-altview2.jpg;SS-RL600K-GT-C6PC-altview3.jpg;SS-RL600K-GT-C6PC-altview4.jpg;SS-RL600K-GT-C6PC-altview5.jpg;SS-RL600K-GT-C6PC-altview6.jpg;SS-RL600K-GT-C6PC-altview7.jpg;SS-RL600K-GT-C6PC-altview8.jpg;SS-RL600K-GT-C6PC-altview9.jpg;SS-RL600K-GT-C6PC-altview10.jpg;SS-RL600K-GT-C6PC-altview11.jpg;SS-RL600K-GT-C6PC-altview12.jpg;SS-RL600K-GT-C6PC-altview13.jpg;SS-RL600K-GT-C6PC-altview14.jpg;SS-RL600K-GT-C6PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>SS-RL600N-GT-C6PC</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Rylie 6-Piece Counter Game Dining Set, Natural Finish</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Dive into a mix of classic fun and modern chic with the Rylie Folding Game Counter Dining Set. This natural finished set features swivel Captain’s Chairs in camel vegan leather, accented with stylish copper nailheads. The star is the removable game top, decked out with 16 cupholders and eight chip holders for ultimate game nights. Post-play, it transforms into a charming dining spot. Crafted from durable oak veneers and hardwoods, this set seats four comfortably and assembles easily, making it a perfect blend of form and function.</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>• Set includes the Rylie Folding Game Top, the Rylie 48-inch Counter Dining Table and 4 Rylie Counter Captains Chairs. All in natural finish with camel vegan leather. Each item also sold separately..
 • Expertly crafted of oak veneers, poplar and Asian hardwood solids and engineered woods, foam and vegan leather
@@ -4353,57 +3172,37 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>RL600N-GT-C6PC</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/rylie-6-piece-counter-game-dining-set-natural-finish/</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>SS-RL600N-GT-C6PC-1.jpg;SS-RL600N-GT-C6PC-altview1.jpg;SS-RL600N-GT-C6PC-altview2.jpg;SS-RL600N-GT-C6PC-altview3.jpg;SS-RL600N-GT-C6PC-altview4.jpg;SS-RL600N-GT-C6PC-altview5.jpg;SS-RL600N-GT-C6PC-altview6.jpg;SS-RL600N-GT-C6PC-altview7.jpg;SS-RL600N-GT-C6PC-altview8.jpg;SS-RL600N-GT-C6PC-altview9.jpg;SS-RL600N-GT-C6PC-altview10.jpg;SS-RL600N-GT-C6PC-altview11.jpg;SS-RL600N-GT-C6PC-altview12.jpg;SS-RL600N-GT-C6PC-altview13.jpg;SS-RL600N-GT-C6PC-altview14.jpg;SS-RL600N-GT-C6PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>SS-RL500K-GT-D6PC</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Rylie 6-Piece Game Dining Set, Black Finish</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Get ready for game night with the Rylie Black Finish 6-Piece Game Dining Set! This set includes a 48-inch round table with a folding game top and four comfy castered Captain’s chairs in sand vegan leather, jazzed up with copper nailhead trim. The folding game top offers eight stations with dual cupholders and chip holders. When the games are done, remove the top, tuck it away in its carry case, and you’ve got a sleek dining table ready for four.
  The glossy black finish gives it a modern edge, perfect for any room. Each piece is crafted from oak veneers, poplar, and Asian hardwoods, kiln-dried to avoid warping or mildew. The pinwheel oak veneer pattern on the table adds elegance, making it great for dining or working. The chairs, with full rotation and solid wood legs, are stylish and practical.</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>• Set includes the Rylie 48-inch round table top, the Rylie Trestle Table Base, Folding Game Table Top and 4 Black Captains Chair. Each item also sold separately.
 • Crafted of oak veneers, poplar and Asian hardwood solids and engineered woods
@@ -4423,57 +3222,37 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>RL500K-GT-D6PC</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/rylie-6-piece-game-dining-set-black-finish/</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>SS-RL500K-GT-D6PC-1.jpg;SS-RL500K-GT-D6PC-altview1.jpg;SS-RL500K-GT-D6PC-altview2.jpg;SS-RL500K-GT-D6PC-altview3.jpg;SS-RL500K-GT-D6PC-altview4.jpg;SS-RL500K-GT-D6PC-altview5.jpg;SS-RL500K-GT-D6PC-altview6.jpg;SS-RL500K-GT-D6PC-altview7.jpg;SS-RL500K-GT-D6PC-altview8.jpg;SS-RL500K-GT-D6PC-altview9.jpg;SS-RL500K-GT-D6PC-altview10.jpg;SS-RL500K-GT-D6PC-altview11.jpg;SS-RL500K-GT-D6PC-altview12.jpg;SS-RL500K-GT-D6PC-altview13.jpg;SS-RL500K-GT-D6PC-altview14.jpg;SS-RL500K-GT-D6PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>SS-RL500N-GT-D6PC</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Rylie 6-Piece Game Dining Set, Natural Finish</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>The Rylie 6-piece Game Dining Set presents a versatile ensemble for both game nights and stylish dining. This set includes the Rylie Folding Game Table Top, a 48-inch round Dining Table, and four Rylie castered Captain’s Chairs in a natural finish with camel vegan leather. Each piece, available separately, is crafted from oak veneers, poplar, and Asian hardwoods, ensuring durability and resistance to warping or mildew.
  The game top, featuring 16 cupholders and eight chip holders, easily transforms your dining table into a multi-player game station. Post-game, simply store the top in its carry bag to reveal a stunning dining surface with an inlaid pinwheel oak veneer pattern. The table’s natural finish highlights the wood’s grain, creating a warm, inviting setting for up to four people. The chairs, with full rotation casters, offer seamless mobility and comfort, accented with copper nailhead trim for an elegant touch. This set combines practicality with elegance, ideal for any home. Easy assembly with all tools included.</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>• Set includes the Rylie Folding Game Table Top, the Rylie 48-inch round Dining Table and 4 Rylie castered Captains Chairs in natural finish with camel vegan leather. Each item also sold separately.
 • Crafted of oak veneers, poplar and Asian hardwood solids and engineered woods
@@ -4494,56 +3273,36 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>RL500N-GT-D6PC</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/rylie-6-piece-game-dining-set-natural-finish/</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>SS-RL500N-GT-D6PC-1.jpg;SS-RL500N-GT-D6PC-altview1.jpg;SS-RL500N-GT-D6PC-altview2.jpg;SS-RL500N-GT-D6PC-altview3.jpg;SS-RL500N-GT-D6PC-altview4.jpg;SS-RL500N-GT-D6PC-altview5.jpg;SS-RL500N-GT-D6PC-altview6.jpg;SS-RL500N-GT-D6PC-altview7.jpg;SS-RL500N-GT-D6PC-altview8.jpg;SS-RL500N-GT-D6PC-altview9.jpg;SS-RL500N-GT-D6PC-altview10.jpg;SS-RL500N-GT-D6PC-altview11.jpg;SS-RL500N-GT-D6PC-altview12.jpg;SS-RL500N-GT-D6PC-altview13.jpg;SS-RL500N-GT-D6PC-altview14.jpg;SS-RL500N-GT-D6PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>SS-TU5050GTB500AB5PC</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Tournament Game Table and Chairs, 6-Piece, Black</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>Enjoy both game night and dining nights with this dual-purpose dining and game table. The 48-inch round table comes in a medium cherry finish and can accommodate four comfortably for dining. The table easily converts to a game table with the addition of the game table-top that is available in black faux-leather (as shown) or brown faux-leather. The game top folds and stores easily and the table goes back to a dining table. The upholstered.faux-leather captain’s chair is castered for easy mobility and comes in a wide range of colors perfect for every decor.</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>• Game Table and Chairs Set includes Table, Black Game Top, &amp; 4 Captain’s Chairs
 • The table is constructed of hardwood solids and cherry veneers
@@ -4553,56 +3312,36 @@
 • Medium cherry finish</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>TU5050GTB500AB5PC</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/tournament-6-piece-game-table-set-black-chairsgame-table-black-game-top-4-captains-chairs/</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>SS-TU5050GTB500AB5PC-1.jpg;SS-TU5050GTB500AB5PC-altview1.jpg;SS-TU5050GTB500AB5PC-altview2.jpg;SS-TU5050GTB500AB5PC-altview3.jpg;SS-TU5050GTB500AB5PC-altview4.jpg;SS-TU5050GTB500AB5PC-altview5.jpg;SS-TU5050GTB500AB5PC-altview6.jpg;SS-TU5050GTB500AB5PC-altview7.jpg;SS-TU5050GTB500AB5PC-altview8.jpg;SS-TU5050GTB500AB5PC-altview9.jpg;SS-TU5050GTB500AB5PC-altview10.jpg;SS-TU5050GTB500AB5PC-altview11.jpg;SS-TU5050GTB500AB5PC-altview12.jpg;SS-TU5050GTB500AB5PC-altview13.jpg;SS-TU5050GTB500AB5PC-altview14.jpg;SS-TU5050GTB500AB5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>SS-TU5050GT500A5PC</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Tournament, Game Table and Chairs, 6-Piece, Brown</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Enjoy both game night and dining nights with this dual-purpose dining and game table. The 48-inch round table comes in a medium cherry finish and can accommodate four comfortably for dining. The table easily converts to a game table with the addition of the game table-top that is available in brown faux-leather (as shown) or black faux-leather. The game top folds and stores easily and the table goes back to a dining table. The upholstered.faux-leather captain’s chair is castered for easy mobility and comes in a wide range of colors perfect for every decor.</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>• Game Table and Chairs Set includes Table, Brown Game Top and 4 Captain’s Chairs. Each item also sold separately.
 • The table is constructed of hardwood solids and cherry veneers
@@ -4612,52 +3351,32 @@
 • Medium cherry finish</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>TU5050GT500A5PC</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/tournament-6-piece-game-table-set-brown-chairsgame-table-brown-game-top-4-captains-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>SS-TU5050GT500A5PC-1.jpg;SS-TU5050GT500A5PC-altview1.jpg;SS-TU5050GT500A5PC-altview2.jpg;SS-TU5050GT500A5PC-altview3.jpg;SS-TU5050GT500A5PC-altview4.jpg;SS-TU5050GT500A5PC-altview5.jpg;SS-TU5050GT500A5PC-altview6.jpg;SS-TU5050GT500A5PC-altview7.jpg;SS-TU5050GT500A5PC-altview8.jpg;SS-TU5050GT500A5PC-altview9.jpg;SS-TU5050GT500A5PC-altview10.jpg;SS-TU5050GT500A5PC-altview11.jpg;SS-TU5050GT500A5PC-altview12.jpg;SS-TU5050GT500A5PC-altview13.jpg;SS-TU5050GT500A5PC-altview14.jpg;SS-TU5050GT500A5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>SS-JS-VEN500T-D5PC</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Ventura 5-Piece Round Dining Set</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>• CURRENT CATALOG FLIP CATALOG
 • VIRTUAL SHOWROOM OCTOBER 2024
@@ -4688,52 +3407,32 @@
 • FURNITURE CARE</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>JS-VEN500T-D5PC</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/ventura-5-piece-round-dining-set/</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>SS-JS-VEN500T-D5PC-1.jpg;SS-JS-VEN500T-D5PC-altview1.jpg;SS-JS-VEN500T-D5PC-altview2.jpg;SS-JS-VEN500T-D5PC-altview3.jpg;SS-JS-VEN500T-D5PC-altview4.jpg;SS-JS-VEN500T-D5PC-altview5.jpg;SS-JS-VEN500T-D5PC-altview6.jpg;SS-JS-VEN500T-D5PC-altview7.jpg;SS-JS-VEN500T-D5PC-altview8.jpg;SS-JS-VEN500T-D5PC-altview9.jpg;SS-JS-VEN500T-D5PC-altview10.jpg;SS-JS-VEN500T-D5PC-altview11.jpg;SS-JS-VEN500T-D5PC-altview12.jpg;SS-JS-VEN500T-D5PC-altview13.jpg;SS-JS-VEN500T-D5PC-altview14.jpg;SS-JS-VEN500T-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>SS-JS-VEN500SV</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Ventura Server</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>• CURRENT CATALOG FLIP CATALOG
 • VIRTUAL SHOWROOM OCTOBER 2024
@@ -4766,57 +3465,37 @@
 • FURNITURE CARE</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>JS-VEN500SV</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/ventura-server/</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>SS-JS-VEN500SV-1.jpg;SS-JS-VEN500SV-altview1.jpg;SS-JS-VEN500SV-altview2.jpg;SS-JS-VEN500SV-altview3.jpg;SS-JS-VEN500SV-altview4.jpg;SS-JS-VEN500SV-altview5.jpg;SS-JS-VEN500SV-altview6.jpg;SS-JS-VEN500SV-altview7.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>SS-BUR500NSV</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Burlington Cathedral Doored Server</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>A masterpiece of versatility and style, the Burlington Server reveals a world of display possibilities behind beautiful Cathedral glass doors. Hand-stained in a striking cocoa finish with a contrasting black interior, this cabinet features adjustable shelves and hidden cable management for a seamless transition from a dining room sideboard, to a living room entertainment center, or even a stunning hallway console 
  The clean lines and modern style of the Burlington Server adds elegance, sophistication and storage to any room in a home.</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>• Crafted from Oak veneers, Asian hardwood solids and engineered woods
 • Wire Escape back allows this cabinet to double as a media console
@@ -4826,26 +3505,6 @@
 • Wire escape back with notched shelves ensures organized cable management and a clutter-free appearance
 • With wire management and cathedral glass doors, the Server can work as a dining room Server, a living room entertainment piece or a hallway or foyer console.
 • The wood is hand-stained in a natural multi-step cocoa finish with black  interior to highlight the interior of the case while offering a beautiful contrast</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>BUR500NSV</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/burlington-cathedral-doored-server/</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>SS-BUR500NSV-1.jpg;SS-BUR500NSV-altview1.jpg;SS-BUR500NSV-altview2.jpg;SS-BUR500NSV-altview3.jpg;SS-BUR500NSV-altview4.jpg;SS-BUR500NSV-altview5.jpg;SS-BUR500NSV-altview6.jpg</t>
         </is>
       </c>
     </row>
@@ -4860,68 +3519,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>productcode</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>productname</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>productprice</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>productweight</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>freeshipping</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>productdescription</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>techspecs</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>vendor_sku</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>volusion_images</t>
         </is>
       </c>
     </row>
@@ -4970,26 +3619,6 @@
 • Experience leather-like luxury at an affordable price with the easy-care dark brown vegan leather cover on the chair</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CBR500-GT-D6PC</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/cambridge-6-piece-dining-set-with-folding-removable-game-top/</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SS-CBR500-GT-D6PC-1.jpg;SS-CBR500-GT-D6PC-altview1.jpg;SS-CBR500-GT-D6PC-altview2.jpg;SS-CBR500-GT-D6PC-altview3.jpg;SS-CBR500-GT-D6PC-altview4.jpg;SS-CBR500-GT-D6PC-altview5.jpg;SS-CBR500-GT-D6PC-altview6.jpg;SS-CBR500-GT-D6PC-altview7.jpg;SS-CBR500-GT-D6PC-altview8.jpg;SS-CBR500-GT-D6PC-altview9.jpg;SS-CBR500-GT-D6PC-altview10.jpg;SS-CBR500-GT-D6PC-altview11.jpg;SS-CBR500-GT-D6PC-altview12.jpg;SS-CBR500-GT-D6PC-altview13.jpg;SS-CBR500-GT-D6PC-altview14.jpg;SS-CBR500-GT-D6PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5030,26 +3659,6 @@
 • Medium cherry finish</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TU5050GTB500AG-5PC</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/game-table-and-chairs-tournament-6-piece-gray/</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SS-TU5050GTB500AG-5PC-1.jpg;SS-TU5050GTB500AG-5PC-altview1.jpg;SS-TU5050GTB500AG-5PC-altview2.jpg;SS-TU5050GTB500AG-5PC-altview3.jpg;SS-TU5050GTB500AG-5PC-altview4.jpg;SS-TU5050GTB500AG-5PC-altview5.jpg;SS-TU5050GTB500AG-5PC-altview6.jpg;SS-TU5050GTB500AG-5PC-altview7.jpg;SS-TU5050GTB500AG-5PC-altview8.jpg;SS-TU5050GTB500AG-5PC-altview9.jpg;SS-TU5050GTB500AG-5PC-altview10.jpg;SS-TU5050GTB500AG-5PC-altview11.jpg;SS-TU5050GTB500AG-5PC-altview12.jpg;SS-TU5050GTB500AG-5PC-altview13.jpg;SS-TU5050GTB500AG-5PC-altview14.jpg;SS-TU5050GTB500AG-5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5088,26 +3697,6 @@
 • Shown with Teal Chairs, other chair colors also available
 • Each item is also sold individually: Tournament Teal Chair , Tournament Dining Table , and Tournament Brown Game Table Top .
 • Medium cherry finish</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>TU5050GTB500AT-5PC</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/game-table-and-chairs-tournament-6-piece-teal/</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>SS-TU5050GTB500AT-5PC-1.jpg;SS-TU5050GTB500AT-5PC-altview1.jpg;SS-TU5050GTB500AT-5PC-altview2.jpg;SS-TU5050GTB500AT-5PC-altview3.jpg;SS-TU5050GTB500AT-5PC-altview4.jpg;SS-TU5050GTB500AT-5PC-altview5.jpg;SS-TU5050GTB500AT-5PC-altview6.jpg;SS-TU5050GTB500AT-5PC-altview7.jpg;SS-TU5050GTB500AT-5PC-altview8.jpg;SS-TU5050GTB500AT-5PC-altview9.jpg;SS-TU5050GTB500AT-5PC-altview10.jpg;SS-TU5050GTB500AT-5PC-altview11.jpg;SS-TU5050GTB500AT-5PC-altview12.jpg;SS-TU5050GTB500AT-5PC-altview13.jpg;SS-TU5050GTB500AT-5PC-altview14.jpg;SS-TU5050GTB500AT-5PC-altview15.jpg</t>
         </is>
       </c>
     </row>
@@ -5162,26 +3751,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>RL600K-GT-C6PC</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/rylie-6-piece-counter-game-dining-set-black-finish/</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>SS-RL600K-GT-C6PC-1.jpg;SS-RL600K-GT-C6PC-altview1.jpg;SS-RL600K-GT-C6PC-altview2.jpg;SS-RL600K-GT-C6PC-altview3.jpg;SS-RL600K-GT-C6PC-altview4.jpg;SS-RL600K-GT-C6PC-altview5.jpg;SS-RL600K-GT-C6PC-altview6.jpg;SS-RL600K-GT-C6PC-altview7.jpg;SS-RL600K-GT-C6PC-altview8.jpg;SS-RL600K-GT-C6PC-altview9.jpg;SS-RL600K-GT-C6PC-altview10.jpg;SS-RL600K-GT-C6PC-altview11.jpg;SS-RL600K-GT-C6PC-altview12.jpg;SS-RL600K-GT-C6PC-altview13.jpg;SS-RL600K-GT-C6PC-altview14.jpg;SS-RL600K-GT-C6PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5234,26 +3803,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>RL600N-GT-C6PC</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/rylie-6-piece-counter-game-dining-set-natural-finish/</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SS-RL600N-GT-C6PC-1.jpg;SS-RL600N-GT-C6PC-altview1.jpg;SS-RL600N-GT-C6PC-altview2.jpg;SS-RL600N-GT-C6PC-altview3.jpg;SS-RL600N-GT-C6PC-altview4.jpg;SS-RL600N-GT-C6PC-altview5.jpg;SS-RL600N-GT-C6PC-altview6.jpg;SS-RL600N-GT-C6PC-altview7.jpg;SS-RL600N-GT-C6PC-altview8.jpg;SS-RL600N-GT-C6PC-altview9.jpg;SS-RL600N-GT-C6PC-altview10.jpg;SS-RL600N-GT-C6PC-altview11.jpg;SS-RL600N-GT-C6PC-altview12.jpg;SS-RL600N-GT-C6PC-altview13.jpg;SS-RL600N-GT-C6PC-altview14.jpg;SS-RL600N-GT-C6PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5302,26 +3851,6 @@
 • Fabric Content: in 69% polyurethane, 28% polyester and 3% viscose
 • Adjustable levelers add stability on uneven surfaces.
 • Easy Assembly, all tools included</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>RL500K-GT-D6PC</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/rylie-6-piece-game-dining-set-black-finish/</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SS-RL500K-GT-D6PC-1.jpg;SS-RL500K-GT-D6PC-altview1.jpg;SS-RL500K-GT-D6PC-altview2.jpg;SS-RL500K-GT-D6PC-altview3.jpg;SS-RL500K-GT-D6PC-altview4.jpg;SS-RL500K-GT-D6PC-altview5.jpg;SS-RL500K-GT-D6PC-altview6.jpg;SS-RL500K-GT-D6PC-altview7.jpg;SS-RL500K-GT-D6PC-altview8.jpg;SS-RL500K-GT-D6PC-altview9.jpg;SS-RL500K-GT-D6PC-altview10.jpg;SS-RL500K-GT-D6PC-altview11.jpg;SS-RL500K-GT-D6PC-altview12.jpg;SS-RL500K-GT-D6PC-altview13.jpg;SS-RL500K-GT-D6PC-altview14.jpg;SS-RL500K-GT-D6PC-altview15.jpg</t>
         </is>
       </c>
     </row>
@@ -5375,26 +3904,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>RL500N-GT-D6PC</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/rylie-6-piece-game-dining-set-natural-finish/</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>SS-RL500N-GT-D6PC-1.jpg;SS-RL500N-GT-D6PC-altview1.jpg;SS-RL500N-GT-D6PC-altview2.jpg;SS-RL500N-GT-D6PC-altview3.jpg;SS-RL500N-GT-D6PC-altview4.jpg;SS-RL500N-GT-D6PC-altview5.jpg;SS-RL500N-GT-D6PC-altview6.jpg;SS-RL500N-GT-D6PC-altview7.jpg;SS-RL500N-GT-D6PC-altview8.jpg;SS-RL500N-GT-D6PC-altview9.jpg;SS-RL500N-GT-D6PC-altview10.jpg;SS-RL500N-GT-D6PC-altview11.jpg;SS-RL500N-GT-D6PC-altview12.jpg;SS-RL500N-GT-D6PC-altview13.jpg;SS-RL500N-GT-D6PC-altview14.jpg;SS-RL500N-GT-D6PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5434,26 +3943,6 @@
 • Medium cherry finish</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>TU5050GTB500AB5PC</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/tournament-6-piece-game-table-set-black-chairsgame-table-black-game-top-4-captains-chairs/</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>SS-TU5050GTB500AB5PC-1.jpg;SS-TU5050GTB500AB5PC-altview1.jpg;SS-TU5050GTB500AB5PC-altview2.jpg;SS-TU5050GTB500AB5PC-altview3.jpg;SS-TU5050GTB500AB5PC-altview4.jpg;SS-TU5050GTB500AB5PC-altview5.jpg;SS-TU5050GTB500AB5PC-altview6.jpg;SS-TU5050GTB500AB5PC-altview7.jpg;SS-TU5050GTB500AB5PC-altview8.jpg;SS-TU5050GTB500AB5PC-altview9.jpg;SS-TU5050GTB500AB5PC-altview10.jpg;SS-TU5050GTB500AB5PC-altview11.jpg;SS-TU5050GTB500AB5PC-altview12.jpg;SS-TU5050GTB500AB5PC-altview13.jpg;SS-TU5050GTB500AB5PC-altview14.jpg;SS-TU5050GTB500AB5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5491,26 +3980,6 @@
 • Attractive pedestal base with beaded and fluted design elements and scrolled bun feet
 • Shown with Brown faux-leather Captain’s Chairs, other colors available
 • Medium cherry finish</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>game</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>TU5050GT500A5PC</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/tournament-6-piece-game-table-set-brown-chairsgame-table-brown-game-top-4-captains-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>SS-TU5050GT500A5PC-1.jpg;SS-TU5050GT500A5PC-altview1.jpg;SS-TU5050GT500A5PC-altview2.jpg;SS-TU5050GT500A5PC-altview3.jpg;SS-TU5050GT500A5PC-altview4.jpg;SS-TU5050GT500A5PC-altview5.jpg;SS-TU5050GT500A5PC-altview6.jpg;SS-TU5050GT500A5PC-altview7.jpg;SS-TU5050GT500A5PC-altview8.jpg;SS-TU5050GT500A5PC-altview9.jpg;SS-TU5050GT500A5PC-altview10.jpg;SS-TU5050GT500A5PC-altview11.jpg;SS-TU5050GT500A5PC-altview12.jpg;SS-TU5050GT500A5PC-altview13.jpg;SS-TU5050GT500A5PC-altview14.jpg;SS-TU5050GT500A5PC-altview15.jpg</t>
         </is>
       </c>
     </row>
@@ -5525,75 +3994,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>productcode</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>productname</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>productprice</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>productweight</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>freeshipping</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>productdescription</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>techspecs</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>vendor_sku</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>volusion_images</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SS-VCM420WTN-C5PC-1</t>
+          <t>SS-VCM420WTN-C5PC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5613,12 +4072,7 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-16" data-testid="conversation-turn-34" data-scroll-anchor="true" data-turn="assistant"&gt;
- Meet the Artemis 54-inch square marble counter set—where modern design feels easy and inviting. The double pedestal base brings bold architectural style, while the casual sand finish keeps the look relaxed and livable. A sleek white marble top adds just the right touch of elegance. Paired with plush brown velvet counter chairs, each designed with a perfect pitch for a comfortable seat, it’s made for gathering. At a comfortable 36″ height, it offers easy entry, lasting durability, and effortless everyday style.</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
@@ -5638,26 +4092,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>VCM420WTN-C5PC-1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-sand-finish-w-4-brown-velvet-counter-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SS-VCM420WTN-C5PC-1-1.jpg;SS-VCM420WTN-C5PC-1-altview1.jpg;SS-VCM420WTN-C5PC-1-altview2.jpg;SS-VCM420WTN-C5PC-1-altview3.jpg;SS-VCM420WTN-C5PC-1-altview4.jpg;SS-VCM420WTN-C5PC-1-altview5.jpg;SS-VCM420WTN-C5PC-1-altview6.jpg;SS-VCM420WTN-C5PC-1-altview7.jpg;SS-VCM420WTN-C5PC-1-altview8.jpg;SS-VCM420WTN-C5PC-1-altview9.jpg;SS-VCM420WTN-C5PC-1-altview10.jpg;SS-VCM420WTN-C5PC-1-altview11.jpg;SS-VCM420WTN-C5PC-1-altview12.jpg;SS-VCM420WTN-C5PC-1-altview13.jpg;SS-VCM420WTN-C5PC-1-altview14.jpg;SS-VCM420WTN-C5PC-1-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5682,12 +4116,7 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-16" data-testid="conversation-turn-34" data-scroll-anchor="true" data-turn="assistant"&gt;
- Meet the Artemis 54-inch square marble counter set—where modern design feels easy and inviting. The double pedestal base brings bold architectural style, while the casual sand finish keeps the look relaxed and livable. A sleek white marble top adds just the right touch of elegance. Paired with plush green velvet counter chairs, each designed with a perfect pitch for a comfortable seat, it’s made for gathering. At a comfortable 36″ height, it offers easy entry, lasting durability, and effortless everyday style.</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
@@ -5707,26 +4136,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>VCM420WTE-C5PC</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-sand-finish-w-4-green-velvet-counter-chairs/</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>SS-VCM420WTE-C5PC-1.jpg;SS-VCM420WTE-C5PC-altview1.jpg;SS-VCM420WTE-C5PC-altview2.jpg;SS-VCM420WTE-C5PC-altview3.jpg;SS-VCM420WTE-C5PC-altview4.jpg;SS-VCM420WTE-C5PC-altview5.jpg;SS-VCM420WTE-C5PC-altview6.jpg;SS-VCM420WTE-C5PC-altview7.jpg;SS-VCM420WTE-C5PC-altview8.jpg;SS-VCM420WTE-C5PC-altview9.jpg;SS-VCM420WTE-C5PC-altview10.jpg;SS-VCM420WTE-C5PC-altview11.jpg;SS-VCM420WTE-C5PC-altview12.jpg;SS-VCM420WTE-C5PC-altview13.jpg;SS-VCM420WTE-C5PC-altview14.jpg;SS-VCM420WTE-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5751,12 +4160,7 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-15" data-testid="conversation-turn-32" data-scroll-anchor="true" data-turn="assistant"&gt;
- Sleek, sophisticated, and modern, the Artemis 54″ white marble 5-piece counter set delivers standout style with everyday versatility. The 54-inch square table seats up to eight while keeping conversation close and inviting. A substantial white marble top is beautifully softened by a sand finish double pedestal base for a relaxed yet elegant presentation. At a comfortable 36″ height, it’s perfect for dining, working, or gathering with easy entry and exit. Four beige chenille counter chairs add plush comfort, making it ideal for both daily living and entertaining.</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
@@ -5776,26 +4180,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>VCM540WTT-C5PC</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-tan-finish-w-4-beige-chenille-counter-chairs/</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>SS-VCM540WTT-C5PC-1.jpg;SS-VCM540WTT-C5PC-altview1.jpg;SS-VCM540WTT-C5PC-altview2.jpg;SS-VCM540WTT-C5PC-altview3.jpg;SS-VCM540WTT-C5PC-altview4.jpg;SS-VCM540WTT-C5PC-altview5.jpg;SS-VCM540WTT-C5PC-altview6.jpg;SS-VCM540WTT-C5PC-altview7.jpg;SS-VCM540WTT-C5PC-altview8.jpg;SS-VCM540WTT-C5PC-altview9.jpg;SS-VCM540WTT-C5PC-altview10.jpg;SS-VCM540WTT-C5PC-altview11.jpg;SS-VCM540WTT-C5PC-altview12.jpg;SS-VCM540WTT-C5PC-altview13.jpg;SS-VCM540WTT-C5PC-altview14.jpg;SS-VCM540WTT-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5820,12 +4204,7 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-12" data-testid="conversation-turn-26" data-scroll-anchor="true" data-turn="assistant"&gt;
- Sleek, sophisticated, and modern, the Artemis 54″ white marble 5-piece counter set delivers standout style and everyday function. The 54-inch square white marble table seats up to eight while keeping conversation close and inviting. A substantial 3″ marble-look top and bold black base create a high-end presence. Four black vegan leather counter chairs, accented with silver nailhead trim, add crisp contrast and tailored appeal, while supportive seating and sturdy construction ensure lasting comfort, durability, and performance for dining and entertaining alike.</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>• Crafted with 8mm white marble veneered top, Birch veneers, Asian hardwood solids, engineered woods, 100% polyester cover and foam.
@@ -5845,26 +4224,6 @@
 • The wood is hand-stained in a natural multi-step black finish</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>VCM540WKK-C5PC</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-with-4-artemis-black-vegan-leather-counter-chairs/</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>SS-VCM540WKK-C5PC-1.jpg;SS-VCM540WKK-C5PC-altview1.jpg;SS-VCM540WKK-C5PC-altview2.jpg;SS-VCM540WKK-C5PC-altview3.jpg;SS-VCM540WKK-C5PC-altview4.jpg;SS-VCM540WKK-C5PC-altview5.jpg;SS-VCM540WKK-C5PC-altview6.jpg;SS-VCM540WKK-C5PC-altview7.jpg;SS-VCM540WKK-C5PC-altview8.jpg;SS-VCM540WKK-C5PC-altview9.jpg;SS-VCM540WKK-C5PC-altview10.jpg;SS-VCM540WKK-C5PC-altview11.jpg;SS-VCM540WKK-C5PC-altview12.jpg;SS-VCM540WKK-C5PC-altview13.jpg;SS-VCM540WKK-C5PC-altview14.jpg;SS-VCM540WKK-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5889,12 +4248,7 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-12" data-testid="conversation-turn-26" data-scroll-anchor="true" data-turn="assistant"&gt;
- Sleek, sophisticated, and modern, the Artemis 54″ White Marble 5-piece counter set delivers standout style and everyday function. The 54-inch square white marble table comfortably seats up to eight while keeping conversation close and inviting. A substantial 3″ marble-look top and bold black base create a high-end presence. Four white vegan leather counter chairs, accented with silver nailhead trim, add crisp contrast and tailored appeal, while supportive seating and sturdy construction ensure lasting comfort, durability, and performance for dining and entertaining alike.</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>• Crafted with 8mm white marble veneered top, Birch veneers, Asian hardwood solids, engineered woods, 100% polyester cover and foam.
@@ -5914,26 +4268,6 @@
 • The wood is hand-stained in a natural multi-step black finish</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>VCM540WKW-C5PC</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-with-4-artemis-white-vegan-leather-counter-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>SS-VCM540WKW-C5PC-1.jpg;SS-VCM540WKW-C5PC-altview1.jpg;SS-VCM540WKW-C5PC-altview2.jpg;SS-VCM540WKW-C5PC-altview3.jpg;SS-VCM540WKW-C5PC-altview4.jpg;SS-VCM540WKW-C5PC-altview5.jpg;SS-VCM540WKW-C5PC-altview6.jpg;SS-VCM540WKW-C5PC-altview7.jpg;SS-VCM540WKW-C5PC-altview8.jpg;SS-VCM540WKW-C5PC-altview9.jpg;SS-VCM540WKW-C5PC-altview10.jpg;SS-VCM540WKW-C5PC-altview11.jpg;SS-VCM540WKW-C5PC-altview12.jpg;SS-VCM540WKW-C5PC-altview13.jpg;SS-VCM540WKW-C5PC-altview14.jpg;SS-VCM540WKW-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5958,12 +4292,7 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-12" data-testid="conversation-turn-26" data-scroll-anchor="true" data-turn="assistant"&gt;
- Sleek, sophisticated, and modern, the Artemis 54″ White Marble 5-piece counter set makes a striking statement. The 54-inch square white marble table seats up to eight comfortably while maintaining an intimate, conversation-friendly feel. A substantial 3″ marble-look top pairs seamlessly with a deep black wood base for bold appeal. Gray chenille counter chairs offer plush, supportive comfort with a perfectly pitched seat, while front and side stretchers add stability and a built-in footrest invites you to relax and stay awhile.</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>• Crafted with 8mm white marble veneered top, Birch veneers, Asian hardwood solids, engineered woods, 100% polyester cover and foam.
@@ -5984,26 +4313,6 @@
 • The wood is hand-stained in a natural multi-step black finish</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>VCM540WKG-C5PC</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-54-square-white-marble-counter-table-with-4-gray-chenille-counter-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>SS-VCM540WKG-C5PC-1.jpg;SS-VCM540WKG-C5PC-altview1.jpg;SS-VCM540WKG-C5PC-altview2.jpg;SS-VCM540WKG-C5PC-altview3.jpg;SS-VCM540WKG-C5PC-altview4.jpg;SS-VCM540WKG-C5PC-altview5.jpg;SS-VCM540WKG-C5PC-altview6.jpg;SS-VCM540WKG-C5PC-altview7.jpg;SS-VCM540WKG-C5PC-altview8.jpg;SS-VCM540WKG-C5PC-altview9.jpg;SS-VCM540WKG-C5PC-altview10.jpg;SS-VCM540WKG-C5PC-altview11.jpg;SS-VCM540WKG-C5PC-altview12.jpg;SS-VCM540WKG-C5PC-altview13.jpg;SS-VCM540WKG-C5PC-altview14.jpg;SS-VCM540WKG-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6049,26 +4358,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>VCM420GKK-D5PC</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-gray-marble-table-black-finish-w-4-black-vegan-leather-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>SS-VCM420GKK-D5PC-1.jpg;SS-VCM420GKK-D5PC-altview1.jpg;SS-VCM420GKK-D5PC-altview2.jpg;SS-VCM420GKK-D5PC-altview3.jpg;SS-VCM420GKK-D5PC-altview4.jpg;SS-VCM420GKK-D5PC-altview5.jpg;SS-VCM420GKK-D5PC-altview6.jpg;SS-VCM420GKK-D5PC-altview7.jpg;SS-VCM420GKK-D5PC-altview8.jpg;SS-VCM420GKK-D5PC-altview9.jpg;SS-VCM420GKK-D5PC-altview10.jpg;SS-VCM420GKK-D5PC-altview11.jpg;SS-VCM420GKK-D5PC-altview12.jpg;SS-VCM420GKK-D5PC-altview13.jpg;SS-VCM420GKK-D5PC-altview14.jpg;SS-VCM420GKK-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6114,26 +4403,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>VCM420GKG-D5PC</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-gray-marble-table-black-finish-w-4-gray-chenille-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>SS-VCM420GKG-D5PC-1.jpg;SS-VCM420GKG-D5PC-altview1.jpg;SS-VCM420GKG-D5PC-altview2.jpg;SS-VCM420GKG-D5PC-altview3.jpg;SS-VCM420GKG-D5PC-altview4.jpg;SS-VCM420GKG-D5PC-altview5.jpg;SS-VCM420GKG-D5PC-altview6.jpg;SS-VCM420GKG-D5PC-altview7.jpg;SS-VCM420GKG-D5PC-altview8.jpg;SS-VCM420GKG-D5PC-altview9.jpg;SS-VCM420GKG-D5PC-altview10.jpg;SS-VCM420GKG-D5PC-altview11.jpg;SS-VCM420GKG-D5PC-altview12.jpg;SS-VCM420GKG-D5PC-altview13.jpg;SS-VCM420GKG-D5PC-altview14.jpg;SS-VCM420GKG-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6179,26 +4448,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>VCM420GKW-D5PC</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-gray-marble-table-black-finish-w-4-white-vegan-leather-chairs-copy/</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>SS-VCM420GKW-D5PC-1.jpg;SS-VCM420GKW-D5PC-altview1.jpg;SS-VCM420GKW-D5PC-altview2.jpg;SS-VCM420GKW-D5PC-altview3.jpg;SS-VCM420GKW-D5PC-altview4.jpg;SS-VCM420GKW-D5PC-altview5.jpg;SS-VCM420GKW-D5PC-altview6.jpg;SS-VCM420GKW-D5PC-altview7.jpg;SS-VCM420GKW-D5PC-altview8.jpg;SS-VCM420GKW-D5PC-altview9.jpg;SS-VCM420GKW-D5PC-altview10.jpg;SS-VCM420GKW-D5PC-altview11.jpg;SS-VCM420GKW-D5PC-altview12.jpg;SS-VCM420GKW-D5PC-altview13.jpg;SS-VCM420GKW-D5PC-altview14.jpg;SS-VCM420GKW-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6244,26 +4493,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>VCM420KK-D5PC</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-black-finish-w-4-black-vegan-leather-chairs/</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>SS-VCM420KK-D5PC-1.jpg;SS-VCM420KK-D5PC-altview1.jpg;SS-VCM420KK-D5PC-altview2.jpg;SS-VCM420KK-D5PC-altview3.jpg;SS-VCM420KK-D5PC-altview4.jpg;SS-VCM420KK-D5PC-altview5.jpg;SS-VCM420KK-D5PC-altview6.jpg;SS-VCM420KK-D5PC-altview7.jpg;SS-VCM420KK-D5PC-altview8.jpg;SS-VCM420KK-D5PC-altview9.jpg;SS-VCM420KK-D5PC-altview10.jpg;SS-VCM420KK-D5PC-altview11.jpg;SS-VCM420KK-D5PC-altview12.jpg;SS-VCM420KK-D5PC-altview13.jpg;SS-VCM420KK-D5PC-altview14.jpg;SS-VCM420KK-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6309,26 +4538,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>VCM420KG-D5PC</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-black-finish-w-4-gray-chenille-chairs/</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>SS-VCM420KG-D5PC-1.jpg;SS-VCM420KG-D5PC-altview1.jpg;SS-VCM420KG-D5PC-altview2.jpg;SS-VCM420KG-D5PC-altview3.jpg;SS-VCM420KG-D5PC-altview4.jpg;SS-VCM420KG-D5PC-altview5.jpg;SS-VCM420KG-D5PC-altview6.jpg;SS-VCM420KG-D5PC-altview7.jpg;SS-VCM420KG-D5PC-altview8.jpg;SS-VCM420KG-D5PC-altview9.jpg;SS-VCM420KG-D5PC-altview10.jpg;SS-VCM420KG-D5PC-altview11.jpg;SS-VCM420KG-D5PC-altview12.jpg;SS-VCM420KG-D5PC-altview13.jpg;SS-VCM420KG-D5PC-altview14.jpg;SS-VCM420KG-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6374,26 +4583,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>VCM420KW-D5PC</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-black-finish-w-4-white-vegan-leather-chairs/</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>SS-VCM420KW-D5PC-1.jpg;SS-VCM420KW-D5PC-altview1.jpg;SS-VCM420KW-D5PC-altview2.jpg;SS-VCM420KW-D5PC-altview3.jpg;SS-VCM420KW-D5PC-altview4.jpg;SS-VCM420KW-D5PC-altview5.jpg;SS-VCM420KW-D5PC-altview6.jpg;SS-VCM420KW-D5PC-altview7.jpg;SS-VCM420KW-D5PC-altview8.jpg;SS-VCM420KW-D5PC-altview9.jpg;SS-VCM420KW-D5PC-altview10.jpg;SS-VCM420KW-D5PC-altview11.jpg;SS-VCM420KW-D5PC-altview12.jpg;SS-VCM420KW-D5PC-altview13.jpg;SS-VCM420KW-D5PC-altview14.jpg;SS-VCM420KW-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6439,26 +4628,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>VCM420TT-D5PC</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-tan-finish-w-4-beige-chenille-chairs/</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>SS-VCM420TT-D5PC-1.jpg;SS-VCM420TT-D5PC-altview1.jpg;SS-VCM420TT-D5PC-altview2.jpg;SS-VCM420TT-D5PC-altview3.jpg;SS-VCM420TT-D5PC-altview4.jpg;SS-VCM420TT-D5PC-altview5.jpg;SS-VCM420TT-D5PC-altview6.jpg;SS-VCM420TT-D5PC-altview7.jpg;SS-VCM420TT-D5PC-altview8.jpg;SS-VCM420TT-D5PC-altview9.jpg;SS-VCM420TT-D5PC-altview10.jpg;SS-VCM420TT-D5PC-altview11.jpg;SS-VCM420TT-D5PC-altview12.jpg;SS-VCM420TT-D5PC-altview13.jpg;SS-VCM420TT-D5PC-altview14.jpg;SS-VCM420TT-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6483,12 +4652,7 @@
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>*]:pointer-events-auto scroll-mt-[calc(var(--header-height)+min(200px,max(70px,20svh)))]" dir="auto" data-turn-id="request-WEB:8796e8fa-a44d-47e4-a72d-59f28c9d7412-16" data-testid="conversation-turn-34" data-scroll-anchor="true" data-turn="assistant"&gt;
- Meet the Artemis 54-inch square marble counter set—where modern design feels easy and inviting. The double pedestal base brings bold architectural style, while the casual sand finish keeps the look relaxed and livable. A sleek white marble top adds just the right touch of elegance. Paired with plush brown velvet counter chairs, each designed with a perfect pitch for a comfortable seat, it’s made for gathering. At a comfortable 36″ height, it offers easy entry, lasting durability, and effortless everyday style.</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
@@ -6508,26 +4672,6 @@
 • The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>VCM420WTN-C5PC</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/artemis-5-piece-70-rect-white-marble-table-tan-finish-w-4-brown-velvet-chairs/</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>SS-VCM420WTN-C5PC-1.jpg;SS-VCM420WTN-C5PC-altview1.jpg;SS-VCM420WTN-C5PC-altview2.jpg;SS-VCM420WTN-C5PC-altview3.jpg;SS-VCM420WTN-C5PC-altview4.jpg;SS-VCM420WTN-C5PC-altview5.jpg;SS-VCM420WTN-C5PC-altview6.jpg;SS-VCM420WTN-C5PC-altview7.jpg;SS-VCM420WTN-C5PC-altview8.jpg;SS-VCM420WTN-C5PC-altview9.jpg;SS-VCM420WTN-C5PC-altview10.jpg;SS-VCM420WTN-C5PC-altview11.jpg;SS-VCM420WTN-C5PC-altview12.jpg;SS-VCM420WTN-C5PC-altview13.jpg;SS-VCM420WTN-C5PC-altview14.jpg;SS-VCM420WTN-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6576,26 +4720,6 @@
 • Table measurements: 54″W x 54″D x 30″H
 • Chair measurements: 21″W x 22″D x 35.25″H
 • Easy Assembly, all tools included</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ABR5454K-D5PC</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-5-piece-54-round-dining-table-set-copy/</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>SS-ABR5454K-D5PC-1.jpg;SS-ABR5454K-D5PC-altview1.jpg;SS-ABR5454K-D5PC-altview2.jpg;SS-ABR5454K-D5PC-altview3.jpg;SS-ABR5454K-D5PC-altview4.jpg;SS-ABR5454K-D5PC-altview5.jpg;SS-ABR5454K-D5PC-altview6.jpg;SS-ABR5454K-D5PC-altview7.jpg;SS-ABR5454K-D5PC-altview8.jpg;SS-ABR5454K-D5PC-altview9.jpg;SS-ABR5454K-D5PC-altview10.jpg;SS-ABR5454K-D5PC-altview11.jpg;SS-ABR5454K-D5PC-altview12.jpg;SS-ABR5454K-D5PC-altview13.jpg;SS-ABR5454K-D5PC-altview14.jpg;SS-ABR5454K-D5PC-altview15.jpg</t>
         </is>
       </c>
     </row>
@@ -6649,26 +4773,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ABR5454N-4US-D5PC</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-5-piece-54-round-dining-table-set-driftwood/</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>SS-ABR5454N-4US-D5PC-1.jpg;SS-ABR5454N-4US-D5PC-altview1.jpg;SS-ABR5454N-4US-D5PC-altview2.jpg;SS-ABR5454N-4US-D5PC-altview3.jpg;SS-ABR5454N-4US-D5PC-altview4.jpg;SS-ABR5454N-4US-D5PC-altview5.jpg;SS-ABR5454N-4US-D5PC-altview6.jpg;SS-ABR5454N-4US-D5PC-altview7.jpg;SS-ABR5454N-4US-D5PC-altview8.jpg;SS-ABR5454N-4US-D5PC-altview9.jpg;SS-ABR5454N-4US-D5PC-altview10.jpg;SS-ABR5454N-4US-D5PC-altview11.jpg;SS-ABR5454N-4US-D5PC-altview12.jpg;SS-ABR5454N-4US-D5PC-altview13.jpg;SS-ABR5454N-4US-D5PC-altview14.jpg;SS-ABR5454N-4US-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6718,26 +4822,6 @@
 • Table measurements: 54″W x 54″D x 30″H
 • Chair measurements: 23.5″W x 23.75″D x 38.25″H in
 • Easy Assembly, all tools included</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ABR5454K-4US-D5PC</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-5-piece-54-round-dining-table-set/</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>SS-ABR5454K-4US-D5PC-1.jpg;SS-ABR5454K-4US-D5PC-altview1.jpg;SS-ABR5454K-4US-D5PC-altview2.jpg;SS-ABR5454K-4US-D5PC-altview3.jpg;SS-ABR5454K-4US-D5PC-altview4.jpg;SS-ABR5454K-4US-D5PC-altview5.jpg;SS-ABR5454K-4US-D5PC-altview6.jpg;SS-ABR5454K-4US-D5PC-altview7.jpg;SS-ABR5454K-4US-D5PC-altview8.jpg;SS-ABR5454K-4US-D5PC-altview9.jpg;SS-ABR5454K-4US-D5PC-altview10.jpg;SS-ABR5454K-4US-D5PC-altview11.jpg;SS-ABR5454K-4US-D5PC-altview12.jpg;SS-ABR5454K-4US-D5PC-altview13.jpg;SS-ABR5454K-4US-D5PC-altview14.jpg;SS-ABR5454K-4US-D5PC-altview15.jpg</t>
         </is>
       </c>
     </row>
@@ -6794,26 +4878,6 @@
 • Counter Chair: 23W x 19.5D x 41.75H</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ABR400N-C5PC</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-5-piece-59-5-counter-dining-set-driftwood-finish/</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>SS-ABR400N-C5PC-1.jpg;SS-ABR400N-C5PC-altview1.jpg;SS-ABR400N-C5PC-altview2.jpg;SS-ABR400N-C5PC-altview3.jpg;SS-ABR400N-C5PC-altview4.jpg;SS-ABR400N-C5PC-altview5.jpg;SS-ABR400N-C5PC-altview6.jpg;SS-ABR400N-C5PC-altview7.jpg;SS-ABR400N-C5PC-altview8.jpg;SS-ABR400N-C5PC-altview9.jpg;SS-ABR400N-C5PC-altview10.jpg;SS-ABR400N-C5PC-altview11.jpg;SS-ABR400N-C5PC-altview12.jpg;SS-ABR400N-C5PC-altview13.jpg;SS-ABR400N-C5PC-altview14.jpg;SS-ABR400N-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6865,26 +4929,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ABR500K-2US-D7PC</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-black-7-piece-dining-set/</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SS-ABR500K-2US-D7PC-1.jpg;SS-ABR500K-2US-D7PC-altview1.jpg;SS-ABR500K-2US-D7PC-altview2.jpg;SS-ABR500K-2US-D7PC-altview3.jpg;SS-ABR500K-2US-D7PC-altview4.jpg;SS-ABR500K-2US-D7PC-altview5.jpg;SS-ABR500K-2US-D7PC-altview6.jpg;SS-ABR500K-2US-D7PC-altview7.jpg;SS-ABR500K-2US-D7PC-altview8.jpg;SS-ABR500K-2US-D7PC-altview9.jpg;SS-ABR500K-2US-D7PC-altview10.jpg;SS-ABR500K-2US-D7PC-altview11.jpg;SS-ABR500K-2US-D7PC-altview12.jpg;SS-ABR500K-2US-D7PC-altview13.jpg;SS-ABR500K-2US-D7PC-altview14.jpg;SS-ABR500K-2US-D7PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6927,26 +4971,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ABR500KSV</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-server-black/</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>SS-ABR500KSV-1.jpg;SS-ABR500KSV-altview1.jpg;SS-ABR500KSV-altview2.jpg;SS-ABR500KSV-altview3.jpg;SS-ABR500KSV-altview4.jpg;SS-ABR500KSV-altview5.jpg;SS-ABR500KSV-altview6.jpg;SS-ABR500KSV-altview7.jpg;SS-ABR500KSV-altview8.jpg;SS-ABR500KSV-altview9.jpg;SS-ABR500KSV-altview10.jpg;SS-ABR500KSV-altview11.jpg;SS-ABR500KSV-altview12.jpg;SS-ABR500KSV-altview13.jpg;SS-ABR500KSV-altview14.jpg;SS-ABR500KSV-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6987,26 +5011,6 @@
 • Plastic glides help protect floors from mars or scratches
 • 2000 lb. weight capacity ensures durability and reliable support.
 • Easy Assembly, all tools included</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ABR500NSV</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-server-brown/</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>SS-ABR500NSV-1.jpg;SS-ABR500NSV-altview1.jpg;SS-ABR500NSV-altview2.jpg;SS-ABR500NSV-altview3.jpg;SS-ABR500NSV-altview4.jpg;SS-ABR500NSV-altview5.jpg;SS-ABR500NSV-altview6.jpg;SS-ABR500NSV-altview7.jpg;SS-ABR500NSV-altview8.jpg;SS-ABR500NSV-altview9.jpg;SS-ABR500NSV-altview10.jpg;SS-ABR500NSV-altview11.jpg;SS-ABR500NSV-altview12.jpg;SS-ABR500NSV-altview13.jpg;SS-ABR500NSV-altview14.jpg</t>
         </is>
       </c>
     </row>
@@ -7061,26 +5065,6 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ABR500N-2US-D7PC</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/aubrey-waxed-driftwood-7-piece-78-96-dining-set/</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>SS-ABR500N-2US-D7PC-1.jpg;SS-ABR500N-2US-D7PC-altview1.jpg;SS-ABR500N-2US-D7PC-altview2.jpg;SS-ABR500N-2US-D7PC-altview3.jpg;SS-ABR500N-2US-D7PC-altview4.jpg;SS-ABR500N-2US-D7PC-altview5.jpg;SS-ABR500N-2US-D7PC-altview6.jpg;SS-ABR500N-2US-D7PC-altview7.jpg;SS-ABR500N-2US-D7PC-altview8.jpg;SS-ABR500N-2US-D7PC-altview9.jpg;SS-ABR500N-2US-D7PC-altview10.jpg;SS-ABR500N-2US-D7PC-altview11.jpg;SS-ABR500N-2US-D7PC-altview12.jpg;SS-ABR500N-2US-D7PC-altview13.jpg;SS-ABR500N-2US-D7PC-altview14.jpg;SS-ABR500N-2US-D7PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7124,26 +5108,6 @@
 • Seating: Table seats up to six people.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>COL500KW-D5PC</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-5-piece-52-round-white-marble-dining-set-black-finish/</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>SS-COL500KW-D5PC-1.jpg;SS-COL500KW-D5PC-altview1.jpg;SS-COL500KW-D5PC-altview2.jpg;SS-COL500KW-D5PC-altview3.jpg;SS-COL500KW-D5PC-altview4.jpg;SS-COL500KW-D5PC-altview5.jpg;SS-COL500KW-D5PC-altview6.jpg;SS-COL500KW-D5PC-altview7.jpg;SS-COL500KW-D5PC-altview8.jpg;SS-COL500KW-D5PC-altview9.jpg;SS-COL500KW-D5PC-altview10.jpg;SS-COL500KW-D5PC-altview11.jpg;SS-COL500KW-D5PC-altview12.jpg;SS-COL500KW-D5PC-altview13.jpg;SS-COL500KW-D5PC-altview14.jpg;SS-COL500KW-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7187,26 +5151,6 @@
 • Seating: Table seats up to six people.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>COL500NW-D5PC</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-5-piece-52-round-white-marble-dining-set-toffee-finish/</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>SS-COL500NW-D5PC-1.jpg;SS-COL500NW-D5PC-altview1.jpg;SS-COL500NW-D5PC-altview2.jpg;SS-COL500NW-D5PC-altview3.jpg;SS-COL500NW-D5PC-altview4.jpg;SS-COL500NW-D5PC-altview5.jpg;SS-COL500NW-D5PC-altview6.jpg;SS-COL500NW-D5PC-altview7.jpg;SS-COL500NW-D5PC-altview8.jpg;SS-COL500NW-D5PC-altview9.jpg;SS-COL500NW-D5PC-altview10.jpg;SS-COL500NW-D5PC-altview11.jpg;SS-COL500NW-D5PC-altview12.jpg;SS-COL500NW-D5PC-altview13.jpg;SS-COL500NW-D5PC-altview14.jpg;SS-COL500NW-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7245,26 +5189,6 @@
 • The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
 • The 52-inch round dining table seats four people comfortably
 • The chair is solidly constructed using solid wood legs reinforced with mortise-and-tenon joinery and corner blocks for exceptional stability, and elegance while ensuring the chair’s durability and reliable support for its 300 lb. weight capacity. The chair’s 2.5″ upholstered seat is cushioned with 1.2 lb. density foam to create a comfortable and delightful dining experience while the wood trimmed back provides a touch of timeless elegance while safeguarding against wear and tear. The 100% polyester fabric cover in a vanilla boucle weave provides a durable and easy-to-clean surface that resists stains and spills.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>COL500K-5PC</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-5-piece-dining-set-black/</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>SS-COL500K-5PC-1.jpg;SS-COL500K-5PC-altview1.jpg;SS-COL500K-5PC-altview2.jpg;SS-COL500K-5PC-altview3.jpg;SS-COL500K-5PC-altview4.jpg;SS-COL500K-5PC-altview5.jpg;SS-COL500K-5PC-altview6.jpg;SS-COL500K-5PC-altview7.jpg;SS-COL500K-5PC-altview8.jpg;SS-COL500K-5PC-altview9.jpg;SS-COL500K-5PC-altview10.jpg;SS-COL500K-5PC-altview11.jpg;SS-COL500K-5PC-altview12.jpg;SS-COL500K-5PC-altview13.jpg;SS-COL500K-5PC-altview14.jpg;SS-COL500K-5PC-altview15.jpg</t>
         </is>
       </c>
     </row>
@@ -7313,26 +5237,6 @@
 • The chair’s 300 lb. weight capacity ensures durability and reliable support</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>COL500N-5PC</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-5-piece-dining-set-brown/</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>SS-COL500N-5PC-1.jpg;SS-COL500N-5PC-altview1.jpg;SS-COL500N-5PC-altview2.jpg;SS-COL500N-5PC-altview3.jpg;SS-COL500N-5PC-altview4.jpg;SS-COL500N-5PC-altview5.jpg;SS-COL500N-5PC-altview6.jpg;SS-COL500N-5PC-altview7.jpg;SS-COL500N-5PC-altview8.jpg;SS-COL500N-5PC-altview9.jpg;SS-COL500N-5PC-altview10.jpg;SS-COL500N-5PC-altview11.jpg;SS-COL500N-5PC-altview12.jpg;SS-COL500N-5PC-altview13.jpg;SS-COL500N-5PC-altview14.jpg;SS-COL500N-5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7374,26 +5278,6 @@
 • 2000 lb. weight capacity ensures durability and reliable support.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>COL500KSV</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-server-black/</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>SS-COL500KSV-1.jpg;SS-COL500KSV-altview1.jpg;SS-COL500KSV-altview2.jpg;SS-COL500KSV-altview3.jpg;SS-COL500KSV-altview4.jpg;SS-COL500KSV-altview5.jpg;SS-COL500KSV-altview6.jpg;SS-COL500KSV-altview7.jpg;SS-COL500KSV-altview8.jpg;SS-COL500KSV-altview9.jpg;SS-COL500KSV-altview10.jpg;SS-COL500KSV-altview11.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7435,26 +5319,6 @@
 • 2000 lb. weight capacity ensures durability and reliable support.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>COL500NSV</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-server-brown/</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>SS-COL500NSV-1.jpg;SS-COL500NSV-altview1.jpg;SS-COL500NSV-altview2.jpg;SS-COL500NSV-altview3.jpg;SS-COL500NSV-altview4.jpg;SS-COL500NSV-altview5.jpg;SS-COL500NSV-altview6.jpg;SS-COL500NSV-altview7.jpg;SS-COL500NSV-altview8.jpg;SS-COL500NSV-altview9.jpg;SS-COL500NSV-altview10.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7496,26 +5360,6 @@
 • 200 lb. weight capacity ensures durability and reliable support.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>COL500ESV</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-server-green-finish/</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>SS-COL500ESV-1.jpg;SS-COL500ESV-altview1.jpg;SS-COL500ESV-altview2.jpg;SS-COL500ESV-altview3.jpg;SS-COL500ESV-altview4.jpg;SS-COL500ESV-altview5.jpg;SS-COL500ESV-altview6.jpg;SS-COL500ESV-altview7.jpg;SS-COL500ESV-altview8.jpg;SS-COL500ESV-altview9.jpg;SS-COL500ESV-altview10.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7555,26 +5399,6 @@
 • Natural, hand-stained wood in a multi-step Ivory finish
 • Satin brass hardware adds an elegant accessory to the front of the case
 • 200 lb. weight capacity ensures durability and reliable support.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>COL500WSV</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/colvin-server-white/</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>SS-COL500WSV-1.jpg;SS-COL500WSV-altview1.jpg;SS-COL500WSV-altview2.jpg;SS-COL500WSV-altview3.jpg;SS-COL500WSV-altview4.jpg;SS-COL500WSV-altview5.jpg;SS-COL500WSV-altview6.jpg;SS-COL500WSV-altview7.jpg;SS-COL500WSV-altview8.jpg;SS-COL500WSV-altview9.jpg;SS-COL500WSV-altview10.jpg;SS-COL500WSV-altview11.jpg</t>
         </is>
       </c>
     </row>
@@ -7622,26 +5446,6 @@
 • Counter Chair: 19.5W x 23D x 41H</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>GA500T-C5PC</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-5-piece-counter-dining-set-greige-finish/</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>SS-GA500T-C5PC-1.jpg;SS-GA500T-C5PC-altview1.jpg;SS-GA500T-C5PC-altview2.jpg;SS-GA500T-C5PC-altview3.jpg;SS-GA500T-C5PC-altview4.jpg;SS-GA500T-C5PC-altview5.jpg;SS-GA500T-C5PC-altview6.jpg;SS-GA500T-C5PC-altview7.jpg;SS-GA500T-C5PC-altview8.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7687,26 +5491,6 @@
 • Counter Chair: 19.5W x 23D x 41H</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>GA500-C5PC</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-5-piece-counter-dining-set/</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>SS-GA500-C5PC-1.jpg;SS-GA500-C5PC-altview1.jpg;SS-GA500-C5PC-altview2.jpg;SS-GA500-C5PC-altview3.jpg;SS-GA500-C5PC-altview4.jpg;SS-GA500-C5PC-altview5.jpg;SS-GA500-C5PC-altview6.jpg;SS-GA500-C5PC-altview7.jpg;SS-GA500-C5PC-altview8.jpg;SS-GA500-C5PC-altview9.jpg;SS-GA500-C5PC-altview10.jpg;SS-GA500-C5PC-altview11.jpg;SS-GA500-C5PC-altview12.jpg;SS-GA500-C5PC-altview13.jpg;SS-GA500-C5PC-altview14.jpg;SS-GA500-C5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7750,26 +5534,6 @@
 • The wood is hand-stained in a natural multi-step greige finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>GA500T-D5PC</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-5-piece-dining-set-distressed-greige-finish/</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>SS-GA500T-D5PC-1.jpg;SS-GA500T-D5PC-altview1.jpg;SS-GA500T-D5PC-altview2.jpg;SS-GA500T-D5PC-altview3.jpg;SS-GA500T-D5PC-altview4.jpg;SS-GA500T-D5PC-altview5.jpg;SS-GA500T-D5PC-altview6.jpg;SS-GA500T-D5PC-altview7.jpg;SS-GA500T-D5PC-altview8.jpg;SS-GA500T-D5PC-altview9.jpg;SS-GA500T-D5PC-altview10.jpg;SS-GA500T-D5PC-altview11.jpg;SS-GA500T-D5PC-altview12.jpg;SS-GA500T-D5PC-altview13.jpg;SS-GA500T-D5PC-altview14.jpg;SS-GA500T-D5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7812,26 +5576,6 @@
 • Toffee finish</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>GA500-5PC</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-5-piece-dining-set/</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>SS-GA500-5PC-1.jpg;SS-GA500-5PC-altview1.jpg;SS-GA500-5PC-altview2.jpg;SS-GA500-5PC-altview3.jpg;SS-GA500-5PC-altview4.jpg;SS-GA500-5PC-altview5.jpg;SS-GA500-5PC-altview6.jpg;SS-GA500-5PC-altview7.jpg;SS-GA500-5PC-altview8.jpg;SS-GA500-5PC-altview9.jpg;SS-GA500-5PC-altview10.jpg;SS-GA500-5PC-altview11.jpg;SS-GA500-5PC-altview12.jpg;SS-GA500-5PC-altview13.jpg;SS-GA500-5PC-altview14.jpg;SS-GA500-5PC-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7874,26 +5618,6 @@
 • The wood is hand-stained in a natural multi-step distressed griege finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>GA500TC</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-curio-greige-finish/</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>SS-GA500TC-1.jpg;SS-GA500TC-altview1.jpg;SS-GA500TC-altview2.jpg;SS-GA500TC-altview3.jpg;SS-GA500TC-altview4.jpg;SS-GA500TC-altview5.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7936,26 +5660,6 @@
 • The wood is hand-stained in a natural multi-step toffee finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>GA500C</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-curio/</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>SS-GA500C-1.jpg;SS-GA500C-altview1.jpg;SS-GA500C-altview2.jpg;SS-GA500C-altview3.jpg;SS-GA500C-altview4.jpg;SS-GA500C-altview5.jpg;SS-GA500C-altview6.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7994,36 +5698,16 @@
 • Toffee finish</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>GA500SV</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/garland-server/</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>SS-GA500SV-1.jpg;SS-GA500SV-altview1.jpg;SS-GA500SV-altview2.jpg;SS-GA500SV-altview3.jpg;SS-GA500SV-altview4.jpg;SS-GA500SV-altview5.jpg;SS-GA500SV-altview6.jpg;SS-GA500SV-altview7.jpg;SS-GA500SV-altview8.jpg;SS-GA500SV-altview9.jpg;SS-GA500SV-altview10.jpg;SS-GA500SV-altview11.jpg;SS-GA500SV-altview12.jpg;SS-GA500SV-altview13.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SS-MM500K-D5PC</t>
+          <t>SS-GA500TSV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Magnolia 5-Piece 72-108-inch Dining Set</t>
+          <t>Garland 64″ Sideboard, Greige Finish</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -8035,15 +5719,53 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Out of Stock</t>
+          <t>Available</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>The Garland Sideboard in distressed greige finish brings California Casual style to the dining room with clean lines, a modern plinth base, and tasteful hardware. Three drawers and a door provide practical storage that pairs with the matching Garland dining collection.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>• Constructed of veneers, solids and engineered woods
+• Three deep drawers and one door
+• Metal side drawer guides
+• Medium distressing
+• Distressed greige finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SS-MM500K-D5PC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Magnolia 5-Piece 72-108-inch Dining Set</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>A blend of farmhouse finished and substantial proportions combine in the simple sophistication of the Magnolia dining collection. This 5-piece set contrasts black spindle back chairs with a black table base in a striking combination of neutrals. A naturally finished top unites the different aspects of this generously scaled dining set. The dining table centerpiece of the set starts at 72-inches but expands to a full 108-inches in an instant with the addition of the 2-18-inch leaves for a table that easily accommodates 10 guests for dinner. The clean lines and crisp finishes create a light and airy set perfect for larger dining areas.</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>• Set includes Magnolia 72-108-inch Dining Table and 4 Magnolia dining chairs. Each item also sold separately
 • Crafted from Oak veneers with Acacia and Asian hardwood solids and engineered woods
@@ -8063,56 +5785,36 @@
 • The wood is hand-stained in a natural multi-step natural and black two-tone finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>MM500K-D5PC</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-5-piece-72-108-inch-dining-set/</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>SS-MM500K-D5PC-1.jpg;SS-MM500K-D5PC-altview1.jpg;SS-MM500K-D5PC-altview2.jpg;SS-MM500K-D5PC-altview3.jpg;SS-MM500K-D5PC-altview4.jpg;SS-MM500K-D5PC-altview5.jpg;SS-MM500K-D5PC-altview6.jpg;SS-MM500K-D5PC-altview7.jpg;SS-MM500K-D5PC-altview8.jpg;SS-MM500K-D5PC-altview9.jpg;SS-MM500K-D5PC-altview10.jpg;SS-MM500K-D5PC-altview11.jpg;SS-MM500K-D5PC-altview12.jpg;SS-MM500K-D5PC-altview13.jpg;SS-MM500K-D5PC-altview14.jpg;SS-MM500K-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>SS-MM600K-D5PC</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Magnolia 5-Piece 80-96″ Dining Set with Side Chair</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>The Magnolia 80-96″ Dining Set exudes modern sophistication. The dining table boasts bold, clean lines and an expandable top, adorned with a striking ebony stain and gold accents. Accommodating up to eight guests, it effortlessly extends from 80 to 96 inches with the included 16-inch leaf. Paired with the Magnolia Side Chair, this upholstered seat offers tailored elegance with side welting and a linen-look polyester cover for easy cleaning. Guests will relish the 4-inch cushioned seat atop the solid wood twin scissor leg base. Elevate your dining space with this blend of comfort and beauty.</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>• Crafted of Asian hardwood solids, foam, 100% polyester fabric and engineered woods
 • Set includes the 80-96″ Magnolia Dining Table w/18″ leaf and 4 Upholstered Side Chairs. Each item also sold separately.
@@ -8127,56 +5829,36 @@
 • The wood is hand-stained in a natural multi-step ebony finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>MM600K-D5PC</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-5-piece-80-96-dining-set-with-side-chair/</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>SS-MM600K-D5PC-1.jpg;SS-MM600K-D5PC-altview1.jpg;SS-MM600K-D5PC-altview2.jpg;SS-MM600K-D5PC-altview3.jpg;SS-MM600K-D5PC-altview4.jpg;SS-MM600K-D5PC-altview5.jpg;SS-MM600K-D5PC-altview6.jpg;SS-MM600K-D5PC-altview7.jpg;SS-MM600K-D5PC-altview8.jpg;SS-MM600K-D5PC-altview9.jpg;SS-MM600K-D5PC-altview10.jpg;SS-MM600K-D5PC-altview11.jpg;SS-MM600K-D5PC-altview12.jpg;SS-MM600K-D5PC-altview13.jpg;SS-MM600K-D5PC-altview14.jpg;SS-MM600K-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>SS-MM520K-D5PC</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Magnolia 52-inch Round 5-Piece Dining Set, Black</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>Indulge in the refined allure of the Magnolia Dining Set. This set transforms your dining area with its bold black finish, tastefully highlighted with weathered sand accents for a neutral yet captivating aesthetic. The centerpiece, a 52-inch round table, offers an intimate dining experience for up to six people. Surrounding this are solid wood side chairs, their elegance matched by comfort, and featuring beautifully tapered tubular legs. This Magnolia set is not just furniture; it’s a statement of style, a mingling of luxury and homeliness that’s sure to impress.</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>• Set includes the 52-inch Round Black Magnolia Dining Table and 4 Magnolia Upholstered Side Chairs, Each item also sold separately.
 • Crafted from Asian veneers, Asian hardwood solids and engineered woods
@@ -8191,56 +5873,36 @@
 • Easy Assembly, all tools included</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>MM520K-D5PC</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-52-inch-round-5-piece-dining-set-blac/</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>SS-MM520K-D5PC-1.jpg;SS-MM520K-D5PC-altview1.jpg;SS-MM520K-D5PC-altview2.jpg;SS-MM520K-D5PC-altview3.jpg;SS-MM520K-D5PC-altview4.jpg;SS-MM520K-D5PC-altview5.jpg;SS-MM520K-D5PC-altview6.jpg;SS-MM520K-D5PC-altview7.jpg;SS-MM520K-D5PC-altview8.jpg;SS-MM520K-D5PC-altview9.jpg;SS-MM520K-D5PC-altview10.jpg;SS-MM520K-D5PC-altview11.jpg;SS-MM520K-D5PC-altview12.jpg;SS-MM520K-D5PC-altview13.jpg;SS-MM520K-D5PC-altview14.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>SS-MM5454K-D5PC</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Magnolia 54-inch Round 5-Piece Dining Set</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Modern meets farmhouse in the Magnolia 54-inch Round 5-Piece Dining Set. Large yet intimate, it’s perfect for morning breakfasts or supper club gatherings. The sand and black finish, combined with canted legs forming a sled base, creates a sleek and flowing design. Paired with four solid wood farmhouse chairs, each featuring a shaped solid wood seat, this set remains authentic to its origins while adding a touch of comfort. The Magnolia table comfortably seats six, making it an ideal choice for any dining space.</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>• Crafted of solid Asian hardwoods, oak veneers and engineered woods
 • The 5-piece set includes the Magnolia black and sand 54-inch round Dining Table and 4 Magnolia Side Chairs. Each item also sold separately.
@@ -8257,56 +5919,36 @@
 Side Chair: 20″W x 23″D x 40.25″H</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>MM5454K-D5PC</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-54-inch-round-5-piece-dining-set/</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>SS-MM5454K-D5PC-1.jpg;SS-MM5454K-D5PC-altview1.jpg;SS-MM5454K-D5PC-altview2.jpg;SS-MM5454K-D5PC-altview3.jpg;SS-MM5454K-D5PC-altview4.jpg;SS-MM5454K-D5PC-altview5.jpg;SS-MM5454K-D5PC-altview6.jpg;SS-MM5454K-D5PC-altview7.jpg;SS-MM5454K-D5PC-altview8.jpg;SS-MM5454K-D5PC-altview9.jpg;SS-MM5454K-D5PC-altview10.jpg;SS-MM5454K-D5PC-altview11.jpg;SS-MM5454K-D5PC-altview12.jpg;SS-MM5454K-D5PC-altview13.jpg;SS-MM5454K-D5PC-altview14.jpg;SS-MM5454K-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>SS-MM500-D7PC</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Magnolia 7-Piece 72-108-inch Dining Set</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>A blend of farmhouse finished and substantial proportions combine in the simple sophistication of the Magnolia dining collection. This 7-piece set contrasts black spindle back chairs with a white table base and Server in a striking combination of neutrals. A natural finish unites the different aspects of this generously scaled dining set. The dining table centerpiece of the set starts at 72-inches but expands to a full 108-inches in an instant with the addition of the 2-18-inch leaves for a table that easily accommodates 10 guests for dinner. The clean lines and crisp finishes create a light and airy set perfect for larger dining areas.</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>• Set includes Magnolia 72-108-inch Dining Table and 6 Magnolia dining chairs. Each item also sold separately
 • Crafted from Acacia and Asian hardwood solids, engineered woods and Oak veneers
@@ -8326,57 +5968,37 @@
 • White and natural two-tone finish</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>MM500-D7PC</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-7-piece-72-108-inch-dining-set/</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>SS-MM500-D7PC-1.jpg;SS-MM500-D7PC-altview1.jpg;SS-MM500-D7PC-altview2.jpg;SS-MM500-D7PC-altview3.jpg;SS-MM500-D7PC-altview4.jpg;SS-MM500-D7PC-altview5.jpg;SS-MM500-D7PC-altview6.jpg;SS-MM500-D7PC-altview7.jpg;SS-MM500-D7PC-altview8.jpg;SS-MM500-D7PC-altview9.jpg;SS-MM500-D7PC-altview10.jpg;SS-MM500-D7PC-altview11.jpg;SS-MM500-D7PC-altview12.jpg;SS-MM500-D7PC-altview13.jpg;SS-MM500-D7PC-altview14.jpg;SS-MM500-D7PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>SS-MM520KSV</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Magnolia Cathedral Doored Server, Black</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>A masterpiece of versatility and style, the Magnolia Server reveals a world of display possibilities behind beautiful Cathedral glass doors. Hand-stained in a striking ebony finish with a contrasting weathered sand interior, this cabinet features adjustable shelves and hidden cable management for a seamless transition from a dining room sideboard, to a living room entertainment center, or even a stunning hallway console
  The clean lines and modern style of the Magnolia Server adds elegance, sophistication and storage to any room in a home.</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>• Crafted from Asian veneers, Asian hardwood solids and engineered woods
 • Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
@@ -8387,56 +6009,36 @@
 • The wood is hand-stained in a natural multi-step ebony finish with weathered sand interior to highlight the interior of the case while offering a beautiful contrast</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>MM520KSV</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-cathedral-doored-server-black/</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>SS-MM520KSV-1.jpg;SS-MM520KSV-altview1.jpg;SS-MM520KSV-altview2.jpg;SS-MM520KSV-altview3.jpg;SS-MM520KSV-altview4.jpg;SS-MM520KSV-altview5.jpg;SS-MM520KSV-altview6.jpg;SS-MM520KSV-altview7.jpg;SS-MM520KSV-altview8.jpg;SS-MM520KSV-altview9.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>SS-MM520TSV</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Magnolia Cathedral Doored Server, Weathered Sand</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>A masterpiece of versatility and style, the Magnolia Server reveals a world of display possibilities behind beautiful Cathedral glass doors. Hand-stained in a striking weathered sand finish with a contrasting black interior, this cabinet features adjustable shelves and hidden cable management for a seamless transition from a dining room sideboard, to a living room entertainment center, or even a stunning hallway console The clean lines and modern style of the Magnolia Server adds elegance, sophistication and storage to any room in a home.</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>• Crafted from oak veneers, Asian hardwood solids and engineered woods
 • Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
@@ -8450,56 +6052,36 @@
 • The black accented interior and weathered sand exterior allows seamless style integration with all elements of the Magnolia collection</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>MM520TSV</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-cathedral-doored-server-dusty-blue-copy/</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>SS-MM520TSV-1.jpg;SS-MM520TSV-altview1.jpg;SS-MM520TSV-altview2.jpg;SS-MM520TSV-altview3.jpg;SS-MM520TSV-altview4.jpg;SS-MM520TSV-altview5.jpg;SS-MM520TSV-altview6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>SS-MM520BSV</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Magnolia Cathedral Doored Server, Dusty Blue Finish</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>A masterpiece of style and versatility, the Magnolia Server transforms any room with its bold dusty blue finish and weathered sand interior. Elegant Cathedral glass doors reveal adjustable shelves for display, while hidden cable management ensures seamless integration. Whether as a sideboard, entertainment center, or hallway console, it blends practicality with sophistication. Clean lines and thoughtful details enhance both style and storage, making it a refined choice for any home—offering modern elegance with functionality in every setting.</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>• Crafted from oak veneers, Asian hardwood solids and engineered woods
 • Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
@@ -8512,91 +6094,16 @@
 • Adjustable levelers add stability on uneven floors</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>MM520BSV</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/magnolia-cathedral-doored-server-dusty-blue/</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>SS-MM520BSV-1.jpg;SS-MM520BSV-altview1.jpg;SS-MM520BSV-altview2.jpg;SS-MM520BSV-altview3.jpg;SS-MM520BSV-altview4.jpg;SS-MM520BSV-altview5.jpg;SS-MM520BSV-altview6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SS-NP600-C5PC-S</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Napa 5-Piece Counter Dining Set, Sand</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>A grandly scaled counter dining collection with modern farmhouse styling, Napa features a Counter Table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable. Pair with the Napa Server to complete the ultimate in contemporary dining design.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>• Set includes Counter Table &amp; 4 Counter Chairs. Each item also sold separately.
-• Weathered Sand finish</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>NP600-C5PC-S</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-5-piece-counter-dining-set/</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>SS-NP600-C5PC-S-1.jpg;SS-NP600-C5PC-S-altview1.jpg;SS-NP600-C5PC-S-altview2.jpg;SS-NP600-C5PC-S-altview3.jpg;SS-NP600-C5PC-S-altview4.jpg;SS-NP600-C5PC-S-altview5.jpg;SS-NP600-C5PC-S-altview6.jpg;SS-NP600-C5PC-S-altview7.jpg;SS-NP600-C5PC-S-altview8.jpg;SS-NP600-C5PC-S-altview9.jpg;SS-NP600-C5PC-S-altview10.jpg;SS-NP600-C5PC-S-altview11.jpg;SS-NP600-C5PC-S-altview12.jpg;SS-NP600-C5PC-S-altview13.jpg;SS-NP600-C5PC-S-altview14.jpg;SS-NP600-C5PC-S-altview15.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SS-NP500-D5PC-S</t>
+          <t>SS-NP600-C5PC-S</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Napa 5-Piece 72-108-inch Dining Set, Sand</t>
+          <t>Napa 5-Piece Counter Dining Set, Sand</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -8613,10 +6120,45 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>A grandly scaled counter dining collection with modern farmhouse styling, Napa features a Counter Table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable. Pair with the Napa Server to complete the ultimate in contemporary dining design.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>• Set includes Counter Table &amp; 4 Counter Chairs. Each item also sold separately.
+• Weathered Sand finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SS-NP500-D5PC-S</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Napa 5-Piece 72-108-inch Dining Set, Sand</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>Napa is a grandly scaled California casual collection with ample dining space for everyone. With its beautiful plank-effect top and two 18-inch leaves, it can accommodate up to ten people and offers a light and airy weathered sand finish. The double pedestal base has exposed tenons and pairs gracefully with the cushioned seat of the Schoolhouse Side Chair. Comfortable and stylish, Napa offers large-scale dining in a fresh look.</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>• Crafted of mango and Asian hardwoods, mango veneers and engineered hardwoods
 • Side Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
@@ -8630,56 +6172,36 @@
 • The wood is hand-stained in a natural multi-step weathered sand finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>NP500-D5PC-S</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-5-piece-dining-set-sandtable-4-side-chairs/</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>SS-NP500-D5PC-S-1.jpg;SS-NP500-D5PC-S-altview1.jpg;SS-NP500-D5PC-S-altview2.jpg;SS-NP500-D5PC-S-altview3.jpg;SS-NP500-D5PC-S-altview4.jpg;SS-NP500-D5PC-S-altview5.jpg;SS-NP500-D5PC-S-altview6.jpg;SS-NP500-D5PC-S-altview7.jpg;SS-NP500-D5PC-S-altview8.jpg;SS-NP500-D5PC-S-altview9.jpg;SS-NP500-D5PC-S-altview10.jpg;SS-NP500-D5PC-S-altview11.jpg;SS-NP500-D5PC-S-altview12.jpg;SS-NP500-D5PC-S-altview13.jpg;SS-NP500-D5PC-S-altview14.jpg;SS-NP500-D5PC-S-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>SS-NP500-5PC</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Napa 5-Piece Dining Set</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>A grandly scaled dining collection with modern farmhouse styling, Napa features a dining table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed tenons and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable.</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>• Constructed of mango and Asian hardwoods, mango veneers and engineered hardwoods
 • Side Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
@@ -8690,56 +6212,36 @@
 • Dusky cedar finish</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>NP500-5PC</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-6-piece-dining-settable-6-side-chairs/</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>SS-NP500-5PC-1.jpg;SS-NP500-5PC-altview1.jpg;SS-NP500-5PC-altview2.jpg;SS-NP500-5PC-altview3.jpg;SS-NP500-5PC-altview4.jpg;SS-NP500-5PC-altview5.jpg;SS-NP500-5PC-altview6.jpg;SS-NP500-5PC-altview7.jpg;SS-NP500-5PC-altview8.jpg;SS-NP500-5PC-altview9.jpg;SS-NP500-5PC-altview10.jpg;SS-NP500-5PC-altview11.jpg;SS-NP500-5PC-altview12.jpg;SS-NP500-5PC-altview13.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>SS-NP600-5PC</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Napa 5-Piece Counter Dining Set</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>A grandly scaled counter dining collection with modern farmhouse styling, Napa features a Counter Table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable. Pair with the Napa Server to complete the ultimate in contemporary dining design.</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>• Constructed of mango and Asian hardwoods, mango veneers and engineered hardwoods
 • Counter Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
@@ -8750,56 +6252,36 @@
 • Dusky cedar finish</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>NP600-5PC</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-7-piece-counter-dining-setcounter-table-6-counter-chairs/</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>SS-NP600-5PC-1.jpg;SS-NP600-5PC-altview1.jpg;SS-NP600-5PC-altview2.jpg;SS-NP600-5PC-altview3.jpg;SS-NP600-5PC-altview4.jpg;SS-NP600-5PC-altview5.jpg;SS-NP600-5PC-altview6.jpg;SS-NP600-5PC-altview7.jpg;SS-NP600-5PC-altview8.jpg;SS-NP600-5PC-altview9.jpg;SS-NP600-5PC-altview10.jpg;SS-NP600-5PC-altview11.jpg;SS-NP600-5PC-altview12.jpg;SS-NP600-5PC-altview13.jpg;SS-NP600-5PC-altview14.jpg;SS-NP600-5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>SS-NP5007PC</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Napa 7-Piece Dining Set</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>A grandly scaled dining collection with modern farmhouse styling, Napa features a dining table with ample room for all visitors. The table has a beautiful plank-effect top and comes with two 18-inch leaves that expand it to a full 108-inches for seating of up to ten people. The double pedestal base has exposed tenons and pairs gracefully with the schoolhouse upholstered seat Side Chair for a group that is both stylish and comfortable. Upholstered Captains Chairs add a more elegant presentation with an outside wooden ladderback treatment that looks as good from the back as the front.</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>• Constructed of mango and Asian hardwoods, mango veneers and engineered hardwoods
 • Side Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
@@ -8810,56 +6292,36 @@
 • Dusky cedar finish</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>NP5007PC</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-7-piece-dining-settable-2-upholstered-4-side-chairs/</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>SS-NP5007PC-1.jpg;SS-NP5007PC-altview1.jpg;SS-NP5007PC-altview2.jpg;SS-NP5007PC-altview3.jpg;SS-NP5007PC-altview4.jpg;SS-NP5007PC-altview5.jpg;SS-NP5007PC-altview6.jpg;SS-NP5007PC-altview7.jpg;SS-NP5007PC-altview8.jpg;SS-NP5007PC-altview9.jpg;SS-NP5007PC-altview10.jpg;SS-NP5007PC-altview11.jpg;SS-NP5007PC-altview12.jpg;SS-NP5007PC-altview13.jpg;SS-NP5007PC-altview14.jpg;SS-NP5007PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>SS-NP500SV</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Napa Server</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>Napa presents contemporary styling in a Server that adds display and space to any living area. This functional Server has a warm dusky cedar finish that is perfect for home environments. Two shelves for wine storage are accented with a glass top so you can show off your collection and the piece comes along with two additional drawers and two glass front doors for additional storage and display. The sleek modern lines are accented with a relaxed silhouette that allows it to be dressed up or down to your preference.</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>• Constructed of mango and Asian hardwoods, mango veneers, and engineered hardwoods
 • Two glass doors, two drawers, and two shelves with removable bottle storage inserts
@@ -8869,56 +6331,36 @@
 • Dusky cedar finish</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>NP500SV</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/napa-server/</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>SS-NP500SV-1.jpg;SS-NP500SV-altview1.jpg;SS-NP500SV-altview2.jpg;SS-NP500SV-altview3.jpg;SS-NP500SV-altview4.jpg;SS-NP500SV-altview5.jpg;SS-NP500SV-altview6.jpg;SS-NP500SV-altview7.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>SS-RED500K-D5PC</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Reid 5-Piece Dining Set, Black Finish with Saddle Brown Vegan Leather</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>The Reid 5-Piece Dining Set blends modern style with everyday versatility, featuring the Reid 77–95″ Dining Table and four coordinating side chairs. The table expands with an 18-inch leaf to seat up to eight and showcases a deep black finish for a neutral accent to any room. Reid chairs add tailored comfort with box-pleat seats, foam cushioning, and easy-care saddle brown vegan leather. An exposed webbed back and angled seat provide relaxed support, making this set ideal for dining, entertaining, or casual gatherings.</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>• Expertly crafted of ash veneers, solid Asian hardwoods, vegan leather, foam and engineered woods
 • 5-Piece Set includes the Reid 77-95″ Dining Table with 18-inch leaf and 4 Reid Saddle Brown Vegan Leather Side Chairs. Each item also sold separately.
@@ -8936,56 +6378,36 @@
 • Cleaning Code: W — Easy-care vegan leather wipes clean with mild soap and water, offering durable style that stands up to everyday use and spills.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>RED500K-D5PC</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/reid-5-piece-dining-set-black-finish-with-saddle-brown-vegan-leather/</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>SS-RED500K-D5PC-1.jpg;SS-RED500K-D5PC-altview1.jpg;SS-RED500K-D5PC-altview2.jpg;SS-RED500K-D5PC-altview3.jpg;SS-RED500K-D5PC-altview4.jpg;SS-RED500K-D5PC-altview5.jpg;SS-RED500K-D5PC-altview6.jpg;SS-RED500K-D5PC-altview7.jpg;SS-RED500K-D5PC-altview8.jpg;SS-RED500K-D5PC-altview9.jpg;SS-RED500K-D5PC-altview10.jpg;SS-RED500K-D5PC-altview11.jpg;SS-RED500K-D5PC-altview12.jpg;SS-RED500K-D5PC-altview13.jpg;SS-RED500K-D5PC-altview14.jpg;SS-RED500K-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>SS-RED500-D5PC</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Reid 5-Piece 77-95″ Dining Set, Sand Finish with Camel Vegan Leather</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>The Reid 5-Piece Dining Set blends modern style with everyday versatility, featuring the Reid 77–95″ Dining Table and four coordinating side chairs. The table expands with an 18-inch leaf to seat up to eight and showcases a light sand finish that highlights natural wood grain. Reid chairs add tailored comfort with box-pleat seats, foam cushioning, and easy-care camel vegan leather. An exposed webbed back and angled seat provide relaxed support, making this set ideal for dining, entertaining, or casual gatherings.</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>• Expertly crafted of ash veneers, solid Asian hardwoods, vegan leather, foam and engineered woods
 • 5-Piece Set includes the Reid 77-95″ Dining Table with 18-inch leaf and 4 Reid Camel Vegan Leather Side Chairs. Each item also sold separately.
@@ -9003,56 +6425,36 @@
 • Cleaning Code: W — Easy-care vegan leather wipes clean with mild soap and water, offering durable style that stands up to everyday use and spills.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>RED500-D5PC</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/reid-5-piece-dining-set-sand-finish-with-camel-vegan-leather/</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>SS-RED500-D5PC-1.jpg;SS-RED500-D5PC-altview1.jpg;SS-RED500-D5PC-altview2.jpg;SS-RED500-D5PC-altview3.jpg;SS-RED500-D5PC-altview4.jpg;SS-RED500-D5PC-altview5.jpg;SS-RED500-D5PC-altview6.jpg;SS-RED500-D5PC-altview7.jpg;SS-RED500-D5PC-altview8.jpg;SS-RED500-D5PC-altview9.jpg;SS-RED500-D5PC-altview10.jpg;SS-RED500-D5PC-altview11.jpg;SS-RED500-D5PC-altview12.jpg;SS-RED500-D5PC-altview13.jpg;SS-RED500-D5PC-altview14.jpg;SS-RED500-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>SS-RED500KSV</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Reid 60″ Server, Black Finish</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>The Reid 60″ Server offers a modern take on a versatile dining and entertainment piece. Its rich midnight black finish over ash veneers delivers a bold, refined look for any room. Two glass doors provide display, storage, and easy remote access, while two adjustable interior shelves customize space for décor or electronics. Convenient charging is built in with two electric outlets plus USB-A and USB-C ports on the outer upper back, paired with a wire escape for organized cords. Clean lines complete the look overall.</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>• Expertly crafted of ash veneers, solid Asian hardwoods and engineered woods
 • Kiln-dried wood helps prevent warping, splitting and cracking
@@ -9067,56 +6469,36 @@
 • Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>RED500KSV</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/reid-60-server-black-finish/</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>SS-RED500KSV-1.jpg;SS-RED500KSV-altview1.jpg;SS-RED500KSV-altview2.jpg;SS-RED500KSV-altview3.jpg;SS-RED500KSV-altview4.jpg;SS-RED500KSV-altview5.jpg;SS-RED500KSV-altview6.jpg;SS-RED500KSV-altview7.jpg;SS-RED500KSV-altview8.jpg;SS-RED500KSV-altview9.jpg;SS-RED500KSV-altview10.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>SS-RED500TSV</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Reid 60″ Server, Sand Finish</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>The Reid 60″ Server offers a modern take on a versatile dining and entertainment piece. Its light, airy sand finish over ash veneers brings a fresh, open feel to any room. Two glass doors provide display, storage, and easy remote access, while two adjustable interior shelves customize space for décor or electronics. Convenient charging is built in with two electric outlets plus USB-A and USB-C ports on the outer upper back, paired with a wire escape for organized cords. Clean lines complete the look overall.</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>• Expertly crafted of ash veneers, solid Asian hardwoods and engineered woods
 • Kiln-dried wood helps prevent warping, splitting and cracking
@@ -9132,52 +6514,32 @@
 • Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>RED500TSV</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/reid-60-server-sand-finish/</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>SS-RED500TSV-1.jpg;SS-RED500TSV-altview1.jpg;SS-RED500TSV-altview2.jpg;SS-RED500TSV-altview3.jpg;SS-RED500TSV-altview4.jpg;SS-RED500TSV-altview5.jpg;SS-RED500TSV-altview6.jpg;SS-RED500TSV-altview7.jpg;SS-RED500TSV-altview8.jpg;SS-RED500TSV-altview9.jpg;SS-RED500TSV-altview10.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>SS-JS-VEN500T-D5PC</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Ventura 5-Piece Round Dining Set</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
         <is>
           <t>• CURRENT CATALOG FLIP CATALOG
 • VIRTUAL SHOWROOM OCTOBER 2024
@@ -9208,52 +6570,32 @@
 • FURNITURE CARE</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>dining</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>JS-VEN500T-D5PC</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/ventura-5-piece-round-dining-set/</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>SS-JS-VEN500T-D5PC-1.jpg;SS-JS-VEN500T-D5PC-altview1.jpg;SS-JS-VEN500T-D5PC-altview2.jpg;SS-JS-VEN500T-D5PC-altview3.jpg;SS-JS-VEN500T-D5PC-altview4.jpg;SS-JS-VEN500T-D5PC-altview5.jpg;SS-JS-VEN500T-D5PC-altview6.jpg;SS-JS-VEN500T-D5PC-altview7.jpg;SS-JS-VEN500T-D5PC-altview8.jpg;SS-JS-VEN500T-D5PC-altview9.jpg;SS-JS-VEN500T-D5PC-altview10.jpg;SS-JS-VEN500T-D5PC-altview11.jpg;SS-JS-VEN500T-D5PC-altview12.jpg;SS-JS-VEN500T-D5PC-altview13.jpg;SS-JS-VEN500T-D5PC-altview14.jpg;SS-JS-VEN500T-D5PC-altview15.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>SS-JS-VEN500SV</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Ventura Server</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
         <is>
           <t>• CURRENT CATALOG FLIP CATALOG
 • VIRTUAL SHOWROOM OCTOBER 2024
@@ -9286,57 +6628,37 @@
 • FURNITURE CARE</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>JS-VEN500SV</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/ventura-server/</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>SS-JS-VEN500SV-1.jpg;SS-JS-VEN500SV-altview1.jpg;SS-JS-VEN500SV-altview2.jpg;SS-JS-VEN500SV-altview3.jpg;SS-JS-VEN500SV-altview4.jpg;SS-JS-VEN500SV-altview5.jpg;SS-JS-VEN500SV-altview6.jpg;SS-JS-VEN500SV-altview7.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>SS-BUR500NSV</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Burlington Cathedral Doored Server</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>A masterpiece of versatility and style, the Burlington Server reveals a world of display possibilities behind beautiful Cathedral glass doors. Hand-stained in a striking cocoa finish with a contrasting black interior, this cabinet features adjustable shelves and hidden cable management for a seamless transition from a dining room sideboard, to a living room entertainment center, or even a stunning hallway console 
  The clean lines and modern style of the Burlington Server adds elegance, sophistication and storage to any room in a home.</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>• Crafted from Oak veneers, Asian hardwood solids and engineered woods
 • Wire Escape back allows this cabinet to double as a media console
@@ -9348,172 +6670,6 @@
 • The wood is hand-stained in a natural multi-step cocoa finish with black  interior to highlight the interior of the case while offering a beautiful contrast</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>BUR500NSV</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>https://stevesilver.com/product/burlington-cathedral-doored-server/</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>SS-BUR500NSV-1.jpg;SS-BUR500NSV-altview1.jpg;SS-BUR500NSV-altview2.jpg;SS-BUR500NSV-altview3.jpg;SS-BUR500NSV-altview4.jpg;SS-BUR500NSV-altview5.jpg;SS-BUR500NSV-altview6.jpg</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>productcode</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>productname</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>on_site</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SS-BUR500NSV</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Burlington Cathedral Doored Server</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CORRECT: BUR500 = Burlington (vendor SKU BUR500NSV). Live McCabe currently mislabels this code as Magnolia — rename title/description to Burlington and use stevesilver.com Burlington copy. Images refreshed from Burlington product page (not Magnolia MM520*).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SS-MM520KSV</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Magnolia Cathedral Doored Server, Black</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Magnolia server uses MM520* SKUs (not BUR500). Import as SS-MM520KSV. Do not map Magnolia images onto SS-BUR500NSV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SS-AUB500SV</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Auburn/Aubrey Server (on site)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Already on site. Title says Auburn; Steve Silver listing is Aubrey Server Black (SS-ABR500KSV). Current description incorrectly mentions expanding table — replace with Aubrey server copy. Images available under SS-ABR500KSV / synced to SS-AUB500SV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>KARINA-SIDEBOARD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Karina Sideboard</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Already on site. Not Burlington/Magnolia. Optional: rename to SS- style code on re-import.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SS-ABR500KSV</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Aubrey Server, Black (import row)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Correct Aubrey server SKU/format. Use to replace/fix SS-AUB500SV content, or import as new and retire SS-AUB500SV.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/vspfiles/imports/steve-silver-volusion/steve_silver_game_dining_server_import.xlsx
+++ b/vspfiles/imports/steve-silver-volusion/steve_silver_game_dining_server_import.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Artemis 5-Piece 70″ Rect Gray Marble Table, Black Finish w/4 Black Vegan Leather Chairs</t>
+          <t>Artemis 5-Piece 70" Rect Gray Marble Table, Black Finish w/4 Black Vegan Leather Chairs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -483,23 +483,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek gray marble top adds a refined touch. Paired with soft black vegan leather chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
+          <t>Meet the Artemis 70-inch marble top table-where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek gray marble top adds a refined touch. Paired with soft black vegan leather chairs, each with a perfectly pitched seat for comfort, it's made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>• Expertly crafted of gray marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
-• 5-piece set includes the Artemis 70″ Gray Marble Dining Table, Black Finish and 4 Artemis Black Vegan Leather Side Chairs. Each item also sold separately.
-• Kiln-dried wood helps prevent warping, splitting and cracking
-• The chairs are solidly constructed using mortise-and-tenon joinery, corner blocks, sturdy solid wood legs, and screwed joints, this piece delivers exceptional stability, longevity, and superior furniture integrity with a 250 lb. weight capacity ensures durability and reliable support for the chair.
-• The chair legs are hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
-• Plastic glides help prevent scratches or mars to floors
-• The chair’s sleek black vegan leather, made from 100% polyester, offers the look and feel of real leather with easy-care convenience.
-• Available in green velvet, brown velvet, beige chenille, gray chenille, gray vegan leather and black vegan leather; in counter and dining height sizes
-• Chairs are packed 2 per carton
-• Each marble top is crafted by nature with unique characteristics that vary slightly so no two pieces will be exactly alike
-• 70″ long table seats six comfortably
-• The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
+          <t>* Expertly crafted of gray marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
+* 5-piece set includes the Artemis 70" Gray Marble Dining Table, Black Finish and 4 Artemis Black Vegan Leather Side Chairs. Each item also sold separately.
+* Kiln-dried wood helps prevent warping, splitting and cracking
+* The chairs are solidly constructed using mortise-and-tenon joinery, corner blocks, sturdy solid wood legs, and screwed joints, this piece delivers exceptional stability, longevity, and superior furniture integrity with a 250 lb. weight capacity ensures durability and reliable support for the chair.
+* The chair legs are hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
+* Plastic glides help prevent scratches or mars to floors
+* The chair's sleek black vegan leather, made from 100% polyester, offers the look and feel of real leather with easy-care convenience.
+* Available in green velvet, brown velvet, beige chenille, gray chenille, gray vegan leather and black vegan leather; in counter and dining height sizes
+* Chairs are packed 2 per carton
+* Each marble top is crafted by nature with unique characteristics that vary slightly so no two pieces will be exactly alike
+* 70" long table seats six comfortably
+* The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Artemis 5-Piece 70″ Rect Gray Marble Table, Black Finish w/4 White Vegan Leather Chairs</t>
+          <t>Artemis 5-Piece 70" Rect Gray Marble Table, Black Finish w/4 White Vegan Leather Chairs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -528,23 +528,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek gray marble top adds a refined touch. Paired with soft white vegan leather chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
+          <t>Meet the Artemis 70-inch marble top table-where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek gray marble top adds a refined touch. Paired with soft white vegan leather chairs, each with a perfectly pitched seat for comfort, it's made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>• Expertly crafted of gray marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
-• 5-piece set includes the Artemis 70″ Gray Marble Dining Table, Black Finish and 4 Artemis White Vegan Leather Side Chairs. Each item also sold separately.
-• Kiln-dried wood helps prevent warping, splitting and cracking
-• The chairs are solidly constructed using mortise-and-tenon joinery, corner blocks, sturdy solid wood legs, and screwed joints, this piece delivers exceptional stability, longevity, and superior furniture integrity with a 250 lb. weight capacity ensures durability and reliable support for the chair.
-• The chair legs are hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
-• Plastic glides help prevent scratches or mars to floors
-• The chair’s sleek white vegan leather, made from 100% polyester, offers the look and feel of real leather with easy-care convenience.
-• Available in green velvet, brown velvet, beige chenille, gray chenille, white vegan leather and black vegan leather; in counter and dining height sizes
-• Chairs are packed 2 per carton
-• Each marble top is crafted by nature with unique characteristics that vary slightly so no two pieces will be exactly alike
-• 70″ long table seats six comfortably
-• The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
+          <t>* Expertly crafted of gray marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
+* 5-piece set includes the Artemis 70" Gray Marble Dining Table, Black Finish and 4 Artemis White Vegan Leather Side Chairs. Each item also sold separately.
+* Kiln-dried wood helps prevent warping, splitting and cracking
+* The chairs are solidly constructed using mortise-and-tenon joinery, corner blocks, sturdy solid wood legs, and screwed joints, this piece delivers exceptional stability, longevity, and superior furniture integrity with a 250 lb. weight capacity ensures durability and reliable support for the chair.
+* The chair legs are hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
+* Plastic glides help prevent scratches or mars to floors
+* The chair's sleek white vegan leather, made from 100% polyester, offers the look and feel of real leather with easy-care convenience.
+* Available in green velvet, brown velvet, beige chenille, gray chenille, white vegan leather and black vegan leather; in counter and dining height sizes
+* Chairs are packed 2 per carton
+* Each marble top is crafted by nature with unique characteristics that vary slightly so no two pieces will be exactly alike
+* 70" long table seats six comfortably
+* The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Artemis 5 Piece 70″ Rect White Marble Table, Black Finish w/4 Black Vegan Leather Chairs</t>
+          <t>Artemis 5 Piece 70" Rect White Marble Table, Black Finish w/4 Black Vegan Leather Chairs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -573,23 +573,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek white marble top adds a refined touch. Paired with soft black vegan leather chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
+          <t>Meet the Artemis 70-inch marble top table-where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek white marble top adds a refined touch. Paired with soft black vegan leather chairs, each with a perfectly pitched seat for comfort, it's made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
-• 5-piece set includes the Artemis 70″ White Marble Dining Table, Black Finish and 4 Artemis Black Vegan Leather Side Chairs. Each item also sold separately.
-• Kiln-dried wood helps prevent warping, splitting and cracking
-• The chairs are solidly constructed using mortise-and-tenon joinery, corner blocks, sturdy solid wood legs, and screwed joints, this piece delivers exceptional stability, longevity, and superior furniture integrity with a 250 lb. weight capacity ensures durability and reliable support for the chair.
-• The chair legs are hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
-• Plastic glides help prevent scratches or mars to floors
-• The chair’s sleek black vegan leather, made from 100% polyester, offers the look and feel of real leather with easy-care convenience.
-• Available in green velvet, brown velvet, beige chenille, gray chenille, white vegan leather and black vegan leather; in counter and dining height sizes
-• Chairs are packed 2 per carton
-• Each marble top is crafted by nature with unique characteristics that vary slightly so no two pieces will be exactly alike
-• 70″ long table seats six comfortably
-• The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
+          <t>* Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
+* 5-piece set includes the Artemis 70" White Marble Dining Table, Black Finish and 4 Artemis Black Vegan Leather Side Chairs. Each item also sold separately.
+* Kiln-dried wood helps prevent warping, splitting and cracking
+* The chairs are solidly constructed using mortise-and-tenon joinery, corner blocks, sturdy solid wood legs, and screwed joints, this piece delivers exceptional stability, longevity, and superior furniture integrity with a 250 lb. weight capacity ensures durability and reliable support for the chair.
+* The chair legs are hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
+* Plastic glides help prevent scratches or mars to floors
+* The chair's sleek black vegan leather, made from 100% polyester, offers the look and feel of real leather with easy-care convenience.
+* Available in green velvet, brown velvet, beige chenille, gray chenille, white vegan leather and black vegan leather; in counter and dining height sizes
+* Chairs are packed 2 per carton
+* Each marble top is crafted by nature with unique characteristics that vary slightly so no two pieces will be exactly alike
+* 70" long table seats six comfortably
+* The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Artemis 5-Piece 70″ Rect White Marble Table, Black Finish w/4 White Vegan Leather Chairs</t>
+          <t>Artemis 5-Piece 70" Rect White Marble Table, Black Finish w/4 White Vegan Leather Chairs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -618,23 +618,23 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meet the Artemis 70-inch marble top table—where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek white marble top adds a refined touch. Paired with soft white vegan leather chairs, each with a perfectly pitched seat for comfort, it’s made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
+          <t>Meet the Artemis 70-inch marble top table-where modern design feels both elegant and inviting. Its architectural base makes a bold statement, while the sophisticated black finish keeps the look relaxed and livable. The sleek white marble top adds a refined touch. Paired with soft white vegan leather chairs, each with a perfectly pitched seat for comfort, it's made for gathering. Built with solid wood legs and screwed corner joints, this set offers lasting durability with effortless style.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>• Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
-• 5-piece set includes the Artemis 70″ White Marble Dining Table, Black Finish and 4 Artemis White Vegan LeatherSide Chairs. Each item also sold separately.
-• Kiln-dried wood helps prevent warping, splitting and cracking
-• The chairs are solidly constructed using mortise-and-tenon joinery, corner blocks, sturdy solid wood legs, and screwed joints, this piece delivers exceptional stability, longevity, and superior furniture integrity with a 250 lb. weight capacity ensures durability and reliable support for the chair.
-• The chair legs are hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
-• Plastic glides help prevent scratches or mars to floors
-• The chair’s sleek white vegan leather, made from 100% polyester, offers the look and feel of real leather with easy-care convenience.
-• Available in green velvet, brown velvet, beige chenille, gray chenille, white vegan leather and black vegan leather; in counter and dining height sizes
-• Chairs are packed 2 per carton
-• Each marble top is crafted by nature with unique characteristics that vary slightly so no two pieces will be exactly alike
-• 70″ long table seats six comfortably
-• The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
+          <t>* Expertly crafted of white marble veneers, ash veneers, solid Asian hardwoods and engineered woods, 100% polyester and foam
+* 5-piece set includes the Artemis 70" White Marble Dining Table, Black Finish and 4 Artemis White Vegan LeatherSide Chairs. Each item also sold separately.
+* Kiln-dried wood helps prevent warping, splitting and cracking
+* The chairs are solidly constructed using mortise-and-tenon joinery, corner blocks, sturdy solid wood legs, and screwed joints, this piece delivers exceptional stability, longevity, and superior furniture integrity with a 250 lb. weight capacity ensures durability and reliable support for the chair.
+* The chair legs are hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
+* Plastic glides help prevent scratches or mars to floors
+* The chair's sleek white vegan leather, made from 100% polyester, offers the look and feel of real leather with easy-care convenience.
+* Available in green velvet, brown velvet, beige chenille, gray chenille, white vegan leather and black vegan leather; in counter and dining height sizes
+* Chairs are packed 2 per carton
+* Each marble top is crafted by nature with unique characteristics that vary slightly so no two pieces will be exactly alike
+* 70" long table seats six comfortably
+* The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aubrey 5-Piece 54″ Round Dining Table Set</t>
+          <t>Aubrey 5-Piece 54" Round Dining Table Set</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -670,21 +670,21 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>• Set includes the Aubrey 54-inch Black Dining Table with Driftwood Stretchers and 4 Aubrey Gray Vegan Leather Side Chairs. Each item also sold separately.
-• Styling details include the dining table with substantial canted 3″ squared posts with contrasting stretchers and exposed tenons that match all the other pieces in the Aubrey collection. Mix and match finishes and pieces within the collection for a custom look.
-• Cross stretchers provide sturdy support and stability for the 54″ Round Table
-• Built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
-• Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
-• Plastic glides keep the chair from scratching floor
-• Solidly constructed using mortise-and-tenon joinery and corner blocks for exceptional, longevity, and superior furniture integrity
-• The wood is hand-stained in a natural multi-step black finish with waxed driftwood accents that highlights the natural grain and knots of the wood.
-• Wire-brushed distressing adds depth and character to the chair, making it a truly unique and stylish addition to any space.
-• The chair has a 300 lb. weight capacity to ensure durability and reliable support.
-• Gray vegan leather cover is sleek, durable, and easy-care, adding sophistication to any setting
-• The 54-inch round table seats up to six people
-• Table measurements: 54″W x 54″D x 30″H
-• Chair measurements: 21″W x 22″D x 35.25″H
-• Easy Assembly, all tools included</t>
+          <t>* Set includes the Aubrey 54-inch Black Dining Table with Driftwood Stretchers and 4 Aubrey Gray Vegan Leather Side Chairs. Each item also sold separately.
+* Styling details include the dining table with substantial canted 3" squared posts with contrasting stretchers and exposed tenons that match all the other pieces in the Aubrey collection. Mix and match finishes and pieces within the collection for a custom look.
+* Cross stretchers provide sturdy support and stability for the 54" Round Table
+* Built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
+* Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
+* Plastic glides keep the chair from scratching floor
+* Solidly constructed using mortise-and-tenon joinery and corner blocks for exceptional, longevity, and superior furniture integrity
+* The wood is hand-stained in a natural multi-step black finish with waxed driftwood accents that highlights the natural grain and knots of the wood.
+* Wire-brushed distressing adds depth and character to the chair, making it a truly unique and stylish addition to any space.
+* The chair has a 300 lb. weight capacity to ensure durability and reliable support.
+* Gray vegan leather cover is sleek, durable, and easy-care, adding sophistication to any setting
+* The 54-inch round table seats up to six people
+* Table measurements: 54"W x 54"D x 30"H
+* Chair measurements: 21"W x 22"D x 35.25"H
+* Easy Assembly, all tools included</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aubrey 5-Piece 54″ Round Dining Table Set</t>
+          <t>Aubrey 5-Piece 54" Round Dining Table Set</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -720,22 +720,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>• Set includes the Aubrey 54-inch Black Dining Table with Driftwood Stretchers and 4 Aubrey Black Parsons Chairs. Each item also sold separately.
-• Styling details include the dining table with substantial canted 3″ squared posts with contrasting stretchers and exposed tenons that match all the other pieces in the Aubrey collection. Mix and match finishes and pieces within the collection for a custom look.
-• Cross stretchers provide sturdy support and stability for the 54″ Round Table
-• Built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
-• Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
-• Plastic glides keep the chair from scratching floor
-• Solidly constructed using mortise-and-tenon joinery and corner blocks for exceptional, longevity, and superior furniture integrity
-• The wood is hand-stained in a natural multi-step black finish with waxed driftwood accents that highlights the natural grain and knots of the wood.
-• Wire-brushed distressing adds depth and character to the chair, making it a truly unique and stylish addition to any space.
-• The chair has a 300 lb. weight capacity to ensure durability and reliable support.
-• The upholstered removable seat is built with 1.1 density foam to offer comfortable seating for the family that is easy to clean, with a versatile design that fits seamlessly into any space, enhancing both comfort and functionality.
-• The chair’s 100% polyester eggshell fabric cover provides a durable and easy-to-clean surface that resists stains and spills.
-• The 54-inch round table seats up to six people
-• Table measurements: 54″W x 54″D x 30″H
-• Chair measurements: 23.5″W x 23.75″D x 38.25″H in
-• Easy Assembly, all tools included</t>
+          <t>* Set includes the Aubrey 54-inch Black Dining Table with Driftwood Stretchers and 4 Aubrey Black Parsons Chairs. Each item also sold separately.
+* Styling details include the dining table with substantial canted 3" squared posts with contrasting stretchers and exposed tenons that match all the other pieces in the Aubrey collection. Mix and match finishes and pieces within the collection for a custom look.
+* Cross stretchers provide sturdy support and stability for the 54" Round Table
+* Built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
+* Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
+* Plastic glides keep the chair from scratching floor
+* Solidly constructed using mortise-and-tenon joinery and corner blocks for exceptional, longevity, and superior furniture integrity
+* The wood is hand-stained in a natural multi-step black finish with waxed driftwood accents that highlights the natural grain and knots of the wood.
+* Wire-brushed distressing adds depth and character to the chair, making it a truly unique and stylish addition to any space.
+* The chair has a 300 lb. weight capacity to ensure durability and reliable support.
+* The upholstered removable seat is built with 1.1 density foam to offer comfortable seating for the family that is easy to clean, with a versatile design that fits seamlessly into any space, enhancing both comfort and functionality.
+* The chair's 100% polyester eggshell fabric cover provides a durable and easy-to-clean surface that resists stains and spills.
+* The 54-inch round table seats up to six people
+* Table measurements: 54"W x 54"D x 30"H
+* Chair measurements: 23.5"W x 23.75"D x 38.25"H in
+* Easy Assembly, all tools included</t>
         </is>
       </c>
     </row>
@@ -769,16 +769,16 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>• Constructed of oak and acacia veneers, solid Asian hardwoods and engineered wood
-• Table Top extends from 70 to 88 inches with the insertion of the included 18-inch leaf
-• The Table features a faux plank top with rasping and threading distressing for a relaxed, sophisticated look
-• The Table seats up to eight people when fully extended
-• The chair features a 100% polyester eggshell fabric, offering a durable, easy-to-clean surface that resists stains and spills. A brushed brass accent on the back and distressed greige-finished solid wood legs add a touch of elegance and warmth.
-• The chair also works well as an office or guest chair
-• The optional Sideboard has three deep drawers and one door with metal side drawer glides for smooth operation
-• Set shown included dining table and four Side Chairs. Each piece also sold separately.
-• Oversized brushed brass-tone hardware adds a luxurious touch of elegance and char
-• The wood is hand-stained in a natural multi-step greige finish to highlight the natural grain and knots of the wood</t>
+          <t>* Constructed of oak and acacia veneers, solid Asian hardwoods and engineered wood
+* Table Top extends from 70 to 88 inches with the insertion of the included 18-inch leaf
+* The Table features a faux plank top with rasping and threading distressing for a relaxed, sophisticated look
+* The Table seats up to eight people when fully extended
+* The chair features a 100% polyester eggshell fabric, offering a durable, easy-to-clean surface that resists stains and spills. A brushed brass accent on the back and distressed greige-finished solid wood legs add a touch of elegance and warmth.
+* The chair also works well as an office or guest chair
+* The optional Sideboard has three deep drawers and one door with metal side drawer glides for smooth operation
+* Set shown included dining table and four Side Chairs. Each piece also sold separately.
+* Oversized brushed brass-tone hardware adds a luxurious touch of elegance and char
+* The wood is hand-stained in a natural multi-step greige finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
     </row>
@@ -812,15 +812,15 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>• Expertly crafted of acacia veneers, solid Asian hardwoods and engineered wood
-• Table Top extends from 70 to 88 inches with the insertion of the included 18-inch leaf
-• The Table features a faux plank top with rasping and threading distressing for a relaxed, sophisticated look
-• The Table seats up to eight people when fully extended
-• Chair features a relaxed canvas fabric cover application with brushed brass accent on back and distressed toffee finished solid wood legs
-• The chair also works well as an office or guest chair
-• The optional Sideboard has three deep drawers and one door with metal side drawer glides for smooth operation
-• Set shown included dining table and four Side Chairs. Each piece also sold separately.
-• Toffee finish</t>
+          <t>* Expertly crafted of acacia veneers, solid Asian hardwoods and engineered wood
+* Table Top extends from 70 to 88 inches with the insertion of the included 18-inch leaf
+* The Table features a faux plank top with rasping and threading distressing for a relaxed, sophisticated look
+* The Table seats up to eight people when fully extended
+* Chair features a relaxed canvas fabric cover application with brushed brass accent on back and distressed toffee finished solid wood legs
+* The chair also works well as an office or guest chair
+* The optional Sideboard has three deep drawers and one door with metal side drawer glides for smooth operation
+* Set shown included dining table and four Side Chairs. Each piece also sold separately.
+* Toffee finish</t>
         </is>
       </c>
     </row>
@@ -854,15 +854,15 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>• Expertly crafted of acacia veneers, solid Asian hardwoods and engineered wood
-• Kiln-dried wood helps prevent warping, splitting and cracking
-• Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
-• Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.
-• Oversized oil-rubbed brass hardware adds a luxurious touch of elegance and charm
-• Wood scoring and finish rubthrough technique adds a distressed look, enhancing the charm of the furniture with a vintage-inspired appeal.
-• Adjustable levelers add stability on uneven surfaces, protecting contents and enhancing usability
-• Tempered glass doors add durability and safety to the mirror, making it resistant to shattering and damage.
-• The wood is hand-stained in a natural multi-step distressed griege finish to highlight the natural grain and knots of the wood</t>
+          <t>* Expertly crafted of acacia veneers, solid Asian hardwoods and engineered wood
+* Kiln-dried wood helps prevent warping, splitting and cracking
+* Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
+* Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.
+* Oversized oil-rubbed brass hardware adds a luxurious touch of elegance and charm
+* Wood scoring and finish rubthrough technique adds a distressed look, enhancing the charm of the furniture with a vintage-inspired appeal.
+* Adjustable levelers add stability on uneven surfaces, protecting contents and enhancing usability
+* Tempered glass doors add durability and safety to the mirror, making it resistant to shattering and damage.
+* The wood is hand-stained in a natural multi-step distressed griege finish to highlight the natural grain and knots of the wood</t>
         </is>
       </c>
     </row>
@@ -891,16 +891,16 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The Garland Server marries a modern silohuette with a relaxed, lightly distressed toffee finish in a dining side piece with the perfect casually elegant style of today’s dining rooms. A modern plinth base and tastefully appointed satin brass hardware creates extremely clean lines that displays the natural beauty of the wood expertly. Three drawers and a door allow for plenty of storage base of any dining area in a neat, beautiful package that can stand on its own or can be paired with the matching Garland dining collection.</t>
+          <t>The Garland Server marries a modern silohuette with a relaxed, lightly distressed toffee finish in a dining side piece with the perfect casually elegant style of today's dining rooms. A modern plinth base and tastefully appointed satin brass hardware creates extremely clean lines that displays the natural beauty of the wood expertly. Three drawers and a door allow for plenty of storage base of any dining area in a neat, beautiful package that can stand on its own or can be paired with the matching Garland dining collection.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>• Constructed of veneers, solids and engineered woods
-• Three deep drawers and one door
-• Metal side drawer guides
-• Medium distressing
-• Toffee finish</t>
+          <t>* Constructed of veneers, solids and engineered woods
+* Three deep drawers and one door
+* Metal side drawer guides
+* Medium distressing
+* Toffee finish</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Garland 64″ Sideboard, Greige Finish</t>
+          <t>Garland 64" Sideboard, Greige Finish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -934,11 +934,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>• Constructed of veneers, solids and engineered woods
-• Three deep drawers and one door
-• Metal side drawer guides
-• Medium distressing
-• Distressed greige finish</t>
+          <t>* Constructed of veneers, solids and engineered woods
+* Three deep drawers and one door
+* Metal side drawer guides
+* Medium distressing
+* Distressed greige finish</t>
         </is>
       </c>
     </row>
@@ -967,24 +967,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Modern meets farmhouse in the Magnolia 54-inch Round 5-Piece Dining Set. Large yet intimate, it’s perfect for morning breakfasts or supper club gatherings. The sand and black finish, combined with canted legs forming a sled base, creates a sleek and flowing design. Paired with four solid wood farmhouse chairs, each featuring a shaped solid wood seat, this set remains authentic to its origins while adding a touch of comfort. The Magnolia table comfortably seats six, making it an ideal choice for any dining space.</t>
+          <t>Modern meets farmhouse in the Magnolia 54-inch Round 5-Piece Dining Set. Large yet intimate, it's perfect for morning breakfasts or supper club gatherings. The sand and black finish, combined with canted legs forming a sled base, creates a sleek and flowing design. Paired with four solid wood farmhouse chairs, each featuring a shaped solid wood seat, this set remains authentic to its origins while adding a touch of comfort. The Magnolia table comfortably seats six, making it an ideal choice for any dining space.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>• Crafted of solid Asian hardwoods, oak veneers and engineered woods
-• The 5-piece set includes the Magnolia black and sand 54-inch round Dining Table and 4 Magnolia Side Chairs. Each item also sold separately.
-• Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
-• The chair’s shaped wooden seat adds comfort without compromising classic farmhouse style
-• The chair is corner-blocked and secured with screws for exceptional durability
-• Plastic glides on the chair and table help prevent mars or scratches to floors
-• Built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience
-• The 54-inch table comfortably seats up to six, enhancing intimate dining experiences with a spacious yet cozy design.
-• The wood is hand-stained in a natural multi-step two-tone sand and black finish to highlight the natural grain and knots of the wood
-• Bottom sled stretchers on the table provide sturdy support and stability for the 54″ Round Table
-• Product Measurements;
- Table: 54″W x 54″D x 30″H
-Side Chair: 20″W x 23″D x 40.25″H</t>
+          <t>* Crafted of solid Asian hardwoods, oak veneers and engineered woods
+* The 5-piece set includes the Magnolia black and sand 54-inch round Dining Table and 4 Magnolia Side Chairs. Each item also sold separately.
+* Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
+* The chair's shaped wooden seat adds comfort without compromising classic farmhouse style
+* The chair is corner-blocked and secured with screws for exceptional durability
+* Plastic glides on the chair and table help prevent mars or scratches to floors
+* Built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience
+* The 54-inch table comfortably seats up to six, enhancing intimate dining experiences with a spacious yet cozy design.
+* The wood is hand-stained in a natural multi-step two-tone sand and black finish to highlight the natural grain and knots of the wood
+* Bottom sled stretchers on the table provide sturdy support and stability for the 54" Round Table
+* Product Measurements;
+ Table: 54"W x 54"D x 30"H
+Side Chair: 20"W x 23"D x 40.25"H</t>
         </is>
       </c>
     </row>
@@ -1018,16 +1018,16 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>• Crafted from oak veneers, Asian hardwood solids and engineered woods
-• Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
-• Contrasting weathered sand interior beautifully accents the interior with the contrasting ebony finished exterior
-• Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
-• Wire escape back with notched shelves ensures organized cable management and a clutter-free appearance
-• With wire management and cathedral glass doors, the Server can work as a dining room Server, a living room entertainment piece or a hallway or foyer console.
-• The wood is hand-stained in a natural multi-step weathered sand finish with black interior to highlight the interior of the case while offering a beautiful contrast
-• 200 lb. weight capacity ensures durability and reliable support.
-• Adjustable levelers add stability on uneven floors
-• The black accented interior and weathered sand exterior allows seamless style integration with all elements of the Magnolia collection</t>
+          <t>* Crafted from oak veneers, Asian hardwood solids and engineered woods
+* Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
+* Contrasting weathered sand interior beautifully accents the interior with the contrasting ebony finished exterior
+* Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
+* Wire escape back with notched shelves ensures organized cable management and a clutter-free appearance
+* With wire management and cathedral glass doors, the Server can work as a dining room Server, a living room entertainment piece or a hallway or foyer console.
+* The wood is hand-stained in a natural multi-step weathered sand finish with black interior to highlight the interior of the case while offering a beautiful contrast
+* 200 lb. weight capacity ensures durability and reliable support.
+* Adjustable levelers add stability on uneven floors
+* The black accented interior and weathered sand exterior allows seamless style integration with all elements of the Magnolia collection</t>
         </is>
       </c>
     </row>
@@ -1056,20 +1056,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A masterpiece of style and versatility, the Magnolia Server transforms any room with its bold dusty blue finish and weathered sand interior. Elegant Cathedral glass doors reveal adjustable shelves for display, while hidden cable management ensures seamless integration. Whether as a sideboard, entertainment center, or hallway console, it blends practicality with sophistication. Clean lines and thoughtful details enhance both style and storage, making it a refined choice for any home—offering modern elegance with functionality in every setting.</t>
+          <t>A masterpiece of style and versatility, the Magnolia Server transforms any room with its bold dusty blue finish and weathered sand interior. Elegant Cathedral glass doors reveal adjustable shelves for display, while hidden cable management ensures seamless integration. Whether as a sideboard, entertainment center, or hallway console, it blends practicality with sophistication. Clean lines and thoughtful details enhance both style and storage, making it a refined choice for any home-offering modern elegance with functionality in every setting.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>• Crafted from oak veneers, Asian hardwood solids and engineered woods
-• Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
-• Contrasting weathered sand interior beautifully accents the interior with the contrasting dusty blue finished exterior
-• Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
-• Wire escape back with notched shelves ensures organized cable management and a clutter-free appearance
-• With wire management and cathedral glass doors, the Server can work as a dining room Server, a living room entertainment piece or a hallway or foyer console.
-• The wood is hand-stained in a natural multi-step dusty blue finish with weathered sand interior to highlight the interior of the case while offering a beautiful contrast
-• 200 lb. weight capacity ensures durability and reliable support.
-• Adjustable levelers add stability on uneven floors</t>
+          <t>* Crafted from oak veneers, Asian hardwood solids and engineered woods
+* Cathedral glass door fronts offer a beautiful display area or excellent remote access for electronics
+* Contrasting weathered sand interior beautifully accents the interior with the contrasting dusty blue finished exterior
+* Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
+* Wire escape back with notched shelves ensures organized cable management and a clutter-free appearance
+* With wire management and cathedral glass doors, the Server can work as a dining room Server, a living room entertainment piece or a hallway or foyer console.
+* The wood is hand-stained in a natural multi-step dusty blue finish with weathered sand interior to highlight the interior of the case while offering a beautiful contrast
+* 200 lb. weight capacity ensures durability and reliable support.
+* Adjustable levelers add stability on uneven floors</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1103,13 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>• Constructed of mango and Asian hardwoods, mango veneers and engineered hardwoods
-• Side Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
-• The table has plank-effect top, double pedestal base with exposed tenons
-• Stretchers on the table base add to the stability and strength of the table
-• Table seats up to 10 with two 18-inch leaves inserted
-• Table extension slides use cables to guarantee a smooth, seamless leaf insert operation, reducing wear and safeguarding against potential jamming or misalignment
-• Dusky cedar finish</t>
+          <t>* Constructed of mango and Asian hardwoods, mango veneers and engineered hardwoods
+* Side Chair features schoolhouse design with shaped top rail and upholstered linen-colored seat for comfort
+* The table has plank-effect top, double pedestal base with exposed tenons
+* Stretchers on the table base add to the stability and strength of the table
+* Table seats up to 10 with two 18-inch leaves inserted
+* Table extension slides use cables to guarantee a smooth, seamless leaf insert operation, reducing wear and safeguarding against potential jamming or misalignment
+* Dusky cedar finish</t>
         </is>
       </c>
     </row>
@@ -1138,25 +1138,25 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The Reid 5-Piece Dining Set blends modern style with everyday versatility, featuring the Reid 77–95″ Dining Table and four coordinating side chairs. The table expands with an 18-inch leaf to seat up to eight and showcases a deep black finish for a neutral accent to any room. Reid chairs add tailored comfort with box-pleat seats, foam cushioning, and easy-care saddle brown vegan leather. An exposed webbed back and angled seat provide relaxed support, making this set ideal for dining, entertaining, or casual gatherings.</t>
+          <t>The Reid 5-Piece Dining Set blends modern style with everyday versatility, featuring the Reid 77-95" Dining Table and four coordinating side chairs. The table expands with an 18-inch leaf to seat up to eight and showcases a deep black finish for a neutral accent to any room. Reid chairs add tailored comfort with box-pleat seats, foam cushioning, and easy-care saddle brown vegan leather. An exposed webbed back and angled seat provide relaxed support, making this set ideal for dining, entertaining, or casual gatherings.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>• Expertly crafted of ash veneers, solid Asian hardwoods, vegan leather, foam and engineered woods
-• 5-Piece Set includes the Reid 77-95″ Dining Table with 18-inch leaf and 4 Reid Saddle Brown Vegan Leather Side Chairs. Each item also sold separately.
-• Table expands from 77″ to 95″ with included leaf to seat up to eight
-• Hand-stained multi-step sand finish highlights natural grain and knots
-• Experience affordable, leather-like luxury with the camel vegan leather chair from 20% polyurethane/80% polyester that’s easy to care for, comfortable, and adds a warm, rustic leather-like touch to your dining space.
-• Solid construction with mortise-and-tenon joinery, corner blocks, stretchers, and reinforced joints
-• Plastic glides help protect floors from scratches
-• 300 lb. weight capacity per chair for reliable support
-• Easy assembly with all tools included
-• Product Measurements:
+          <t>* Expertly crafted of ash veneers, solid Asian hardwoods, vegan leather, foam and engineered woods
+* 5-Piece Set includes the Reid 77-95" Dining Table with 18-inch leaf and 4 Reid Saddle Brown Vegan Leather Side Chairs. Each item also sold separately.
+* Table expands from 77" to 95" with included leaf to seat up to eight
+* Hand-stained multi-step sand finish highlights natural grain and knots
+* Experience affordable, leather-like luxury with the camel vegan leather chair from 20% polyurethane/80% polyester that's easy to care for, comfortable, and adds a warm, rustic leather-like touch to your dining space.
+* Solid construction with mortise-and-tenon joinery, corner blocks, stretchers, and reinforced joints
+* Plastic glides help protect floors from scratches
+* 300 lb. weight capacity per chair for reliable support
+* Easy assembly with all tools included
+* Product Measurements:
  Table: 77-95W x 40D x 30
-• Side Chair: 20W x 24.25D x 40H
-• Chair Fabric Content: 20% polyurethane, 80% polyester
-• Cleaning Code: W — Easy-care vegan leather wipes clean with mild soap and water, offering durable style that stands up to everyday use and spills.</t>
+* Side Chair: 20W x 24.25D x 40H
+* Chair Fabric Content: 20% polyurethane, 80% polyester
+* Cleaning Code: W - Easy-care vegan leather wipes clean with mild soap and water, offering durable style that stands up to everyday use and spills.</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reid 5-Piece 77-95″ Dining Set, Sand Finish with Camel Vegan Leather</t>
+          <t>Reid 5-Piece 77-95" Dining Set, Sand Finish with Camel Vegan Leather</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1185,25 +1185,25 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The Reid 5-Piece Dining Set blends modern style with everyday versatility, featuring the Reid 77–95″ Dining Table and four coordinating side chairs. The table expands with an 18-inch leaf to seat up to eight and showcases a light sand finish that highlights natural wood grain. Reid chairs add tailored comfort with box-pleat seats, foam cushioning, and easy-care camel vegan leather. An exposed webbed back and angled seat provide relaxed support, making this set ideal for dining, entertaining, or casual gatherings.</t>
+          <t>The Reid 5-Piece Dining Set blends modern style with everyday versatility, featuring the Reid 77-95" Dining Table and four coordinating side chairs. The table expands with an 18-inch leaf to seat up to eight and showcases a light sand finish that highlights natural wood grain. Reid chairs add tailored comfort with box-pleat seats, foam cushioning, and easy-care camel vegan leather. An exposed webbed back and angled seat provide relaxed support, making this set ideal for dining, entertaining, or casual gatherings.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>• Expertly crafted of ash veneers, solid Asian hardwoods, vegan leather, foam and engineered woods
-• 5-Piece Set includes the Reid 77-95″ Dining Table with 18-inch leaf and 4 Reid Camel Vegan Leather Side Chairs. Each item also sold separately.
-• Table expands from 77″ to 95″ with included leaf to seat up to eight
-• Hand-stained multi-step sand finish highlights natural grain and knots
-• Experience affordable, leather-like luxury with the camel vegan leather chair from 60% polyurethane/40% polyester that’s easy to care for, comfortable, and adds a warm, rustic leather-like touch to your dining space.
-• Solid construction with mortise-and-tenon joinery, corner blocks, stretchers, and reinforced joints
-• Plastic glides help protect floors from scratches
-• 300 lb. weight capacity per chair for reliable support
-• Easy assembly with all tools included
-• Product Measurements:
+          <t>* Expertly crafted of ash veneers, solid Asian hardwoods, vegan leather, foam and engineered woods
+* 5-Piece Set includes the Reid 77-95" Dining Table with 18-inch leaf and 4 Reid Camel Vegan Leather Side Chairs. Each item also sold separately.
+* Table expands from 77" to 95" with included leaf to seat up to eight
+* Hand-stained multi-step sand finish highlights natural grain and knots
+* Experience affordable, leather-like luxury with the camel vegan leather chair from 60% polyurethane/40% polyester that's easy to care for, comfortable, and adds a warm, rustic leather-like touch to your dining space.
+* Solid construction with mortise-and-tenon joinery, corner blocks, stretchers, and reinforced joints
+* Plastic glides help protect floors from scratches
+* 300 lb. weight capacity per chair for reliable support
+* Easy assembly with all tools included
+* Product Measurements:
  Table: 77-95W x 40D x 30
-• Side Chair: 20W x 24.25D x 40H
-• Chair Fabric Content: 60% polyurethane, 40% polyester
-• Cleaning Code: W — Easy-care vegan leather wipes clean with mild soap and water, offering durable style that stands up to everyday use and spills.</t>
+* Side Chair: 20W x 24.25D x 40H
+* Chair Fabric Content: 60% polyurethane, 40% polyester
+* Cleaning Code: W - Easy-care vegan leather wipes clean with mild soap and water, offering durable style that stands up to everyday use and spills.</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reid 60″ Server, Black Finish</t>
+          <t>Reid 60" Server, Black Finish</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The Reid 60″ Server offers a modern take on a versatile dining and entertainment piece. Its rich midnight black finish over ash veneers delivers a bold, refined look for any room. Two glass doors provide display, storage, and easy remote access, while two adjustable interior shelves customize space for décor or electronics. Convenient charging is built in with two electric outlets plus USB-A and USB-C ports on the outer upper back, paired with a wire escape for organized cords. Clean lines complete the look overall.</t>
+          <t>The Reid 60" Server offers a modern take on a versatile dining and entertainment piece. Its rich midnight black finish over ash veneers delivers a bold, refined look for any room. Two glass doors provide display, storage, and easy remote access, while two adjustable interior shelves customize space for décor or electronics. Convenient charging is built in with two electric outlets plus USB-A and USB-C ports on the outer upper back, paired with a wire escape for organized cords. Clean lines complete the look overall.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>• Expertly crafted of ash veneers, solid Asian hardwoods and engineered woods
-• Kiln-dried wood helps prevent warping, splitting and cracking
-• Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
-• A built-in wire escape with integrated electric and USB-A/C outlets on the upper outside back keeps cords organized and devices conveniently powered while maintaining a clean look.
-• Concealed European hinges offer clean front aesthetic while allowing the doors to open and close smoothly and quietly
-• Finished back allows for seamless placement in any space.
-• The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
-• Easy Assembly, all tools included
-• 200 lb. weight capacity ensures durability and reliable support.
-• Oversized brass colored hardware adds a luxurious touch of elegance and charm
-• Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.</t>
+          <t>* Expertly crafted of ash veneers, solid Asian hardwoods and engineered woods
+* Kiln-dried wood helps prevent warping, splitting and cracking
+* Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
+* A built-in wire escape with integrated electric and USB-A/C outlets on the upper outside back keeps cords organized and devices conveniently powered while maintaining a clean look.
+* Concealed European hinges offer clean front aesthetic while allowing the doors to open and close smoothly and quietly
+* Finished back allows for seamless placement in any space.
+* The wood is hand-stained in a natural multi-step black finish to highlight the natural grain and knots of the wood
+* Easy Assembly, all tools included
+* 200 lb. weight capacity ensures durability and reliable support.
+* Oversized brass colored hardware adds a luxurious touch of elegance and charm
+* Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reid 60″ Server, Sand Finish</t>
+          <t>Reid 60" Server, Sand Finish</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1276,23 +1276,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The Reid 60″ Server offers a modern take on a versatile dining and entertainment piece. Its light, airy sand finish over ash veneers brings a fresh, open feel to any room. Two glass doors provide display, storage, and easy remote access, while two adjustable interior shelves customize space for décor or electronics. Convenient charging is built in with two electric outlets plus USB-A and USB-C ports on the outer upper back, paired with a wire escape for organized cords. Clean lines complete the look overall.</t>
+          <t>The Reid 60" Server offers a modern take on a versatile dining and entertainment piece. Its light, airy sand finish over ash veneers brings a fresh, open feel to any room. Two glass doors provide display, storage, and easy remote access, while two adjustable interior shelves customize space for décor or electronics. Convenient charging is built in with two electric outlets plus USB-A and USB-C ports on the outer upper back, paired with a wire escape for organized cords. Clean lines complete the look overall.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>• Expertly crafted of ash veneers, solid Asian hardwoods and engineered woods
-• Kiln-dried wood helps prevent warping, splitting and cracking
-• Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
-• A built-in wire escape with integrated electric and USB-A/C outlets on the upper outside back keeps cords organized and devices conveniently powered while maintaining a clean look.
-• Adjustable levelers add stability on uneven floors
-• Concealed European hinges offer clean front aesthetic while allowing the doors to open and close smoothly and quietly
-• Finished back allows for seamless placement in any space.
-• The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood
-• Easy Assembly, all tools included
-• 200 lb. weight capacity ensures durability and reliable support.
-• Oversized brass colored hardware adds a luxurious touch of elegance and charm
-• Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.</t>
+          <t>* Expertly crafted of ash veneers, solid Asian hardwoods and engineered woods
+* Kiln-dried wood helps prevent warping, splitting and cracking
+* Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
+* A built-in wire escape with integrated electric and USB-A/C outlets on the upper outside back keeps cords organized and devices conveniently powered while maintaining a clean look.
+* Adjustable levelers add stability on uneven floors
+* Concealed European hinges offer clean front aesthetic while allowing the doors to open and close smoothly and quietly
+* Finished back allows for seamless placement in any space.
+* The wood is hand-stained in a natural multi-step sand finish to highlight the natural grain and knots of the wood
+* Easy Assembly, all tools included
+* 200 lb. weight capacity ensures durability and reliable support.
+* Oversized brass colored hardware adds a luxurious touch of elegance and charm
+* Includes anti-tip restraint kit for added safety and stability, helping prevent accidental tipping in busy or family spaces.</t>
         </is>
       </c>
     </row>
@@ -1321,30 +1321,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dive into a mix of classic fun and modern chic with the Rylie Folding Game Counter Dining Set. This natural finished set features swivel Captain’s Chairs in camel vegan leather, accented with stylish copper nailheads. The star is the removable game top, decked out with 16 cupholders and eight chip holders for ultimate game nights. Post-play, it transforms into a charming dining spot. Crafted from durable oak veneers and hardwoods, this set seats four comfortably and assembles easily, making it a perfect blend of form and function.</t>
+          <t>Dive into a mix of classic fun and modern chic with the Rylie Folding Game Counter Dining Set. This natural finished set features swivel Captain's Chairs in camel vegan leather, accented with stylish copper nailheads. The star is the removable game top, decked out with 16 cupholders and eight chip holders for ultimate game nights. Post-play, it transforms into a charming dining spot. Crafted from durable oak veneers and hardwoods, this set seats four comfortably and assembles easily, making it a perfect blend of form and function.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>• Set includes the Rylie Folding Game Top, the Rylie 48-inch Counter Dining Table and 4 Rylie Counter Captains Chairs. All in natural finish with camel vegan leather. Each item also sold separately..
-• Expertly crafted of oak veneers, poplar and Asian hardwood solids and engineered woods, foam and vegan leather
-• Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
-• The removable Folding Game Top has 16 cupholders and eight chip holders make for great multi-player game entertainment
-• Folding game top sits on top of the 48-inch round Rylie table for game night and then can be removed and stored in the included carry bag to use the table for dining
-• Four undertop felt-lined drawers offer additional storage for dining or game essentials
-• The 48-inch round table fosters a cozy, intimate setting, perfect for close-knit gatherings and conversations.
-• The 36-inch Counter Height Table offers versatility for dining or working, perfectly suited for standing activities.
-• Beautiful inlaid pinwheel oak veneer pattern creates a stunning work or dining surface
-• Table seats up to four comfortably
-• Adjustable levelers add stability on uneven surfaces.
-• 360-degree swivel mechanism provides greater mobility, reduces strain on the body, and adds an element of playfulness to your decor.
-• Built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
-• The camel colored vegan leather counter chair, accented with copper nailhead trim, offers a sophisticated look with the soft touch and durability of leather, yet is easy to maintain and resistant to wear and tear
-• The Counter Stool’s 24-inch high seat effortlessly complements 36-inch high counters, ensuring an ideal seating experience.
-• Front and side stretchers provide sturdy support and stability for the 24″ seat height counter stool
-• The wood is hand-stained in a multi-step natural glaze that beautifully highlights the natural grain and knots of the wood
-• Fabric Content: in 69% polyurethane, 28% polyester and 3% viscose
-• Easy Assembly, all tools included</t>
+          <t>* Set includes the Rylie Folding Game Top, the Rylie 48-inch Counter Dining Table and 4 Rylie Counter Captains Chairs. All in natural finish with camel vegan leather. Each item also sold separately..
+* Expertly crafted of oak veneers, poplar and Asian hardwood solids and engineered woods, foam and vegan leather
+* Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
+* The removable Folding Game Top has 16 cupholders and eight chip holders make for great multi-player game entertainment
+* Folding game top sits on top of the 48-inch round Rylie table for game night and then can be removed and stored in the included carry bag to use the table for dining
+* Four undertop felt-lined drawers offer additional storage for dining or game essentials
+* The 48-inch round table fosters a cozy, intimate setting, perfect for close-knit gatherings and conversations.
+* The 36-inch Counter Height Table offers versatility for dining or working, perfectly suited for standing activities.
+* Beautiful inlaid pinwheel oak veneer pattern creates a stunning work or dining surface
+* Table seats up to four comfortably
+* Adjustable levelers add stability on uneven surfaces.
+* 360-degree swivel mechanism provides greater mobility, reduces strain on the body, and adds an element of playfulness to your decor.
+* Built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
+* The camel colored vegan leather counter chair, accented with copper nailhead trim, offers a sophisticated look with the soft touch and durability of leather, yet is easy to maintain and resistant to wear and tear
+* The Counter Stool's 24-inch high seat effortlessly complements 36-inch high counters, ensuring an ideal seating experience.
+* Front and side stretchers provide sturdy support and stability for the 24" seat height counter stool
+* The wood is hand-stained in a multi-step natural glaze that beautifully highlights the natural grain and knots of the wood
+* Fabric Content: in 69% polyurethane, 28% polyester and 3% viscose
+* Easy Assembly, all tools included</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Get ready for game night with the Rylie Black Finish 6-Piece Game Dining Set! This set includes a 48-inch round table with a folding game top and four comfy castered Captain’s chairs in sand vegan leather, jazzed up with copper nailhead trim. The folding game top offers eight stations with dual cupholders and chip holders. When the games are done, remove the top, tuck it away in its carry case, and you’ve got a sleek dining table ready for four.
+          <t>Get ready for game night with the Rylie Black Finish 6-Piece Game Dining Set! This set includes a 48-inch round table with a folding game top and four comfy castered Captain's chairs in sand vegan leather, jazzed up with copper nailhead trim. The folding game top offers eight stations with dual cupholders and chip holders. When the games are done, remove the top, tuck it away in its carry case, and you've got a sleek dining table ready for four.
  The glossy black finish gives it a modern edge, perfect for any room. Each piece is crafted from oak veneers, poplar, and Asian hardwoods, kiln-dried to avoid warping or mildew. The pinwheel oak veneer pattern on the table adds elegance, making it great for dining or working. The chairs, with full rotation and solid wood legs, are stylish and practical.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>• Set includes the Rylie 48-inch round table top, the Rylie Trestle Table Base, Folding Game Table Top and 4 Black Captains Chair. Each item also sold separately.
-• Crafted of oak veneers, poplar and Asian hardwood solids and engineered woods
-• Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
-• Removable Folding Game Top has 16 cupholders and eight chip holders make for great multi-player game entertainment
-• Folding Game Top sits on top of the 48-inch round Rylie table for game night and then can be removed and stored in the included carry bag to use the table for dining
-• The 48-inch round table fosters a cozy, intimate setting, perfect for close-knit gatherings and conversations.
-• Beautiful inlaid pinwheel oak veneer pattern creates a stunning work or dining surface
-• Table seats up to four comfortably
-• Versatile side chair suitable for dining, office, or living areas, serving as a stylish accent piece
-• Fully rotating casters on the chair offer enhanced mobility and convenience, allowing for smooth, effortless movement across various floor surfaces
-• Chair is built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
-• The sand colored vegan leather chair, accented with copper nailhead trim, offers a sophisticated look with the soft touch and durability of leather, yet is easy to maintain and resistant to wear and tear
-• The wood is hand-stained in a natural multi-step glossy black finish to highlight the natural grain and knots of the wood
-• Fabric Content: in 69% polyurethane, 28% polyester and 3% viscose
-• Adjustable levelers add stability on uneven surfaces.
-• Easy Assembly, all tools included</t>
+          <t>* Set includes the Rylie 48-inch round table top, the Rylie Trestle Table Base, Folding Game Table Top and 4 Black Captains Chair. Each item also sold separately.
+* Crafted of oak veneers, poplar and Asian hardwood solids and engineered woods
+* Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
+* Removable Folding Game Top has 16 cupholders and eight chip holders make for great multi-player game entertainment
+* Folding Game Top sits on top of the 48-inch round Rylie table for game night and then can be removed and stored in the included carry bag to use the table for dining
+* The 48-inch round table fosters a cozy, intimate setting, perfect for close-knit gatherings and conversations.
+* Beautiful inlaid pinwheel oak veneer pattern creates a stunning work or dining surface
+* Table seats up to four comfortably
+* Versatile side chair suitable for dining, office, or living areas, serving as a stylish accent piece
+* Fully rotating casters on the chair offer enhanced mobility and convenience, allowing for smooth, effortless movement across various floor surfaces
+* Chair is built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
+* The sand colored vegan leather chair, accented with copper nailhead trim, offers a sophisticated look with the soft touch and durability of leather, yet is easy to maintain and resistant to wear and tear
+* The wood is hand-stained in a natural multi-step glossy black finish to highlight the natural grain and knots of the wood
+* Fabric Content: in 69% polyurethane, 28% polyester and 3% viscose
+* Adjustable levelers add stability on uneven surfaces.
+* Easy Assembly, all tools included</t>
         </is>
       </c>
     </row>
@@ -1423,29 +1423,29 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>The Rylie 6-piece Game Dining Set presents a versatile ensemble for both game nights and stylish dining. This set includes the Rylie Folding Game Table Top, a 48-inch round Dining Table, and four Rylie castered Captain’s Chairs in a natural finish with camel vegan leather. Each piece, available separately, is crafted from oak veneers, poplar, and Asian hardwoods, ensuring durability and resistance to warping or mildew.
- The game top, featuring 16 cupholders and eight chip holders, easily transforms your dining table into a multi-player game station. Post-game, simply store the top in its carry bag to reveal a stunning dining surface with an inlaid pinwheel oak veneer pattern. The table’s natural finish highlights the wood’s grain, creating a warm, inviting setting for up to four people. The chairs, with full rotation casters, offer seamless mobility and comfort, accented with copper nailhead trim for an elegant touch. This set combines practicality with elegance, ideal for any home. Easy assembly with all tools included.</t>
+          <t>The Rylie 6-piece Game Dining Set presents a versatile ensemble for both game nights and stylish dining. This set includes the Rylie Folding Game Table Top, a 48-inch round Dining Table, and four Rylie castered Captain's Chairs in a natural finish with camel vegan leather. Each piece, available separately, is crafted from oak veneers, poplar, and Asian hardwoods, ensuring durability and resistance to warping or mildew.
+ The game top, featuring 16 cupholders and eight chip holders, easily transforms your dining table into a multi-player game station. Post-game, simply store the top in its carry bag to reveal a stunning dining surface with an inlaid pinwheel oak veneer pattern. The table's natural finish highlights the wood's grain, creating a warm, inviting setting for up to four people. The chairs, with full rotation casters, offer seamless mobility and comfort, accented with copper nailhead trim for an elegant touch. This set combines practicality with elegance, ideal for any home. Easy assembly with all tools included.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>• Set includes the Rylie Folding Game Table Top, the Rylie 48-inch round Dining Table and 4 Rylie castered Captains Chairs in natural finish with camel vegan leather. Each item also sold separately.
-• Crafted of oak veneers, poplar and Asian hardwood solids and engineered woods
-• Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
-• Removable Folding Game Top has 16 cupholders and eight chip holders make for great multi-player game entertainment
-• Folding Game Top sits on top of the 48-inch round Rylie table for game night and then can be removed and stored in the included carry bag to use the table for dining
-• The 48-inch round table fosters a cozy, intimate setting, perfect for close-knit gatherings and conversations.
-• The wood is hand-stained in a natural multi-step natural finish that beautifully highlights the natural grain and knots of the wood
-• Beautiful inlaid pinwheel oak veneer pattern creates a stunning work or dining surface
-• Table seats up to four comfortably
-• Versatile side chair suitable for dining, office, or living areas, serving as a stylish accent piece
-• Fully rotating casters on the chair offer enhanced mobility and convenience, allowing for smooth, effortless movement across various floor surfaces
-• Chair is built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
-• The sand colored vegan leather chair, accented with copper nailhead trim, offers a sophisticated look with the soft touch and durability of leather, yet is easy to maintain and resistant to wear and tear
-• The wood is hand-stained in a natural multi-step glossy black finish to highlight the natural grain and knots of the wood
-• Fabric Content: in 69% polyurethane, 28% polyester and 3% viscose
-• Adjustable levelers add stability on uneven surfaces.
-• Easy Assembly, all tools included</t>
+          <t>* Set includes the Rylie Folding Game Table Top, the Rylie 48-inch round Dining Table and 4 Rylie castered Captains Chairs in natural finish with camel vegan leather. Each item also sold separately.
+* Crafted of oak veneers, poplar and Asian hardwood solids and engineered woods
+* Kiln-dried wood helps prevent warping, splitting, cracking and developing mildew.
+* Removable Folding Game Top has 16 cupholders and eight chip holders make for great multi-player game entertainment
+* Folding Game Top sits on top of the 48-inch round Rylie table for game night and then can be removed and stored in the included carry bag to use the table for dining
+* The 48-inch round table fosters a cozy, intimate setting, perfect for close-knit gatherings and conversations.
+* The wood is hand-stained in a natural multi-step natural finish that beautifully highlights the natural grain and knots of the wood
+* Beautiful inlaid pinwheel oak veneer pattern creates a stunning work or dining surface
+* Table seats up to four comfortably
+* Versatile side chair suitable for dining, office, or living areas, serving as a stylish accent piece
+* Fully rotating casters on the chair offer enhanced mobility and convenience, allowing for smooth, effortless movement across various floor surfaces
+* Chair is built with solid wood legs to ensure lasting durability, stability, and timeless elegance for every dining experience.
+* The sand colored vegan leather chair, accented with copper nailhead trim, offers a sophisticated look with the soft touch and durability of leather, yet is easy to maintain and resistant to wear and tear
+* The wood is hand-stained in a natural multi-step glossy black finish to highlight the natural grain and knots of the wood
+* Fabric Content: in 69% polyurethane, 28% polyester and 3% viscose
+* Adjustable levelers add stability on uneven surfaces.
+* Easy Assembly, all tools included</t>
         </is>
       </c>
     </row>
@@ -1480,14 +1480,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>• Crafted from Oak veneers, Asian hardwood solids and engineered woods
-• Wire Escape back allows this cabinet to double as a media console
-• Cathedral glass door fronts offer a beautiful display area or excellent remote access  for electronics
-• Contrasting black interior beautifully accents the interior with the contrasting cocoa finished exterior
-• Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
-• Wire escape back with notched shelves ensures organized cable management and a clutter-free appearance
-• With wire management and cathedral glass doors, the Server can work as a dining room Server, a living room entertainment piece or a hallway or foyer console.
-• The wood is hand-stained in a natural multi-step cocoa finish with black  interior to highlight the interior of the case while offering a beautiful contrast</t>
+          <t>* Crafted from Oak veneers, Asian hardwood solids and engineered woods
+* Wire Escape back allows this cabinet to double as a media console
+* Cathedral glass door fronts offer a beautiful display area or excellent remote access  for electronics
+* Contrasting black interior beautifully accents the interior with the contrasting cocoa finished exterior
+* Two adjustable shelves offer versatile storage options to accommodate items of different sizes and shapes.
+* Wire escape back with notched shelves ensures organized cable management and a clutter-free appearance
+* With wire management and cathedral glass doors, the Server can work as a dining room Server, a living room entertainment piece or a hallway or foyer console.
+* The wood is hand-stained in a natural multi-step cocoa finish with black  interior to highlight the interior of the case while offering a beautiful contrast</t>
         </is>
       </c>
     </row>
